--- a/data/derived/Combined_data.xlsx
+++ b/data/derived/Combined_data.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:HZ121"/>
+  <dimension ref="A1:IG121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="11" max="11" width="20.7109375" style="2" customWidth="1"/>
@@ -1535,6 +1535,41 @@
           <t>Substrate_index</t>
         </is>
       </c>
+      <c r="IA1" s="1" t="inlineStr">
+        <is>
+          <t>monitoring_int</t>
+        </is>
+      </c>
+      <c r="IB1" s="1" t="inlineStr">
+        <is>
+          <t>pair_id</t>
+        </is>
+      </c>
+      <c r="IC1" s="1" t="inlineStr">
+        <is>
+          <t>koura_present</t>
+        </is>
+      </c>
+      <c r="ID1" s="1" t="inlineStr">
+        <is>
+          <t>lunar_phase</t>
+        </is>
+      </c>
+      <c r="IE1" s="1" t="inlineStr">
+        <is>
+          <t>lunar_illumination</t>
+        </is>
+      </c>
+      <c r="IF1" s="1" t="inlineStr">
+        <is>
+          <t>lunar_name</t>
+        </is>
+      </c>
+      <c r="IG1" s="1" t="inlineStr">
+        <is>
+          <t>monitoring_quality</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1557,7 +1592,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Reef</t>
+          <t>Stone_pile</t>
         </is>
       </c>
       <c r="F2">
@@ -2202,6 +2237,33 @@
       </c>
       <c r="HZ2">
         <v>31.2</v>
+      </c>
+      <c r="IA2">
+        <v>0</v>
+      </c>
+      <c r="IB2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="IC2">
+        <v>1</v>
+      </c>
+      <c r="ID2">
+        <v>1.365433745565868</v>
+      </c>
+      <c r="IE2">
+        <v>0.3980389321744662</v>
+      </c>
+      <c r="IF2" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG2" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -2680,6 +2742,33 @@
       <c r="HZ3">
         <v>26.4</v>
       </c>
+      <c r="IA3">
+        <v>0</v>
+      </c>
+      <c r="IB3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="IC3">
+        <v>1</v>
+      </c>
+      <c r="ID3">
+        <v>1.365433745565868</v>
+      </c>
+      <c r="IE3">
+        <v>0.3980389321744662</v>
+      </c>
+      <c r="IF3" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG3" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2702,7 +2791,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Reef</t>
+          <t>Stone_pile</t>
         </is>
       </c>
       <c r="F4">
@@ -3287,6 +3376,33 @@
       </c>
       <c r="HZ4">
         <v>18</v>
+      </c>
+      <c r="IA4">
+        <v>0</v>
+      </c>
+      <c r="IB4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="IC4">
+        <v>0</v>
+      </c>
+      <c r="ID4">
+        <v>1.365433745565868</v>
+      </c>
+      <c r="IE4">
+        <v>0.3980389321744662</v>
+      </c>
+      <c r="IF4" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG4" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -3701,6 +3817,33 @@
       <c r="HZ5">
         <v>18</v>
       </c>
+      <c r="IA5">
+        <v>0</v>
+      </c>
+      <c r="IB5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="IC5">
+        <v>0</v>
+      </c>
+      <c r="ID5">
+        <v>1.365433745565868</v>
+      </c>
+      <c r="IE5">
+        <v>0.3980389321744662</v>
+      </c>
+      <c r="IF5" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG5" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3723,7 +3866,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Reef</t>
+          <t>Stone_pile</t>
         </is>
       </c>
       <c r="F6">
@@ -4343,6 +4486,33 @@
       </c>
       <c r="HZ6">
         <v>14.4</v>
+      </c>
+      <c r="IA6">
+        <v>0</v>
+      </c>
+      <c r="IB6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="IC6">
+        <v>1</v>
+      </c>
+      <c r="ID6">
+        <v>1.365433745565868</v>
+      </c>
+      <c r="IE6">
+        <v>0.3980389321744662</v>
+      </c>
+      <c r="IF6" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -4771,6 +4941,33 @@
       <c r="HZ7">
         <v>18</v>
       </c>
+      <c r="IA7">
+        <v>0</v>
+      </c>
+      <c r="IB7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="IC7">
+        <v>0</v>
+      </c>
+      <c r="ID7">
+        <v>1.365433745565868</v>
+      </c>
+      <c r="IE7">
+        <v>0.3980389321744662</v>
+      </c>
+      <c r="IF7" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG7" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4793,7 +4990,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Reef</t>
+          <t>Stone_pile</t>
         </is>
       </c>
       <c r="F8">
@@ -5377,6 +5574,33 @@
       </c>
       <c r="HZ8">
         <v>18</v>
+      </c>
+      <c r="IA8">
+        <v>0</v>
+      </c>
+      <c r="IB8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="IC8">
+        <v>0</v>
+      </c>
+      <c r="ID8">
+        <v>1.365433745565868</v>
+      </c>
+      <c r="IE8">
+        <v>0.3980389321744662</v>
+      </c>
+      <c r="IF8" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG8" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -5823,6 +6047,33 @@
       <c r="HZ9">
         <v>18</v>
       </c>
+      <c r="IA9">
+        <v>0</v>
+      </c>
+      <c r="IB9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="IC9">
+        <v>0</v>
+      </c>
+      <c r="ID9">
+        <v>1.365433745565868</v>
+      </c>
+      <c r="IE9">
+        <v>0.3980389321744662</v>
+      </c>
+      <c r="IF9" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG9" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5845,7 +6096,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Reef</t>
+          <t>Stone_pile</t>
         </is>
       </c>
       <c r="F10">
@@ -6454,6 +6705,33 @@
       </c>
       <c r="HZ10">
         <v>20.1</v>
+      </c>
+      <c r="IA10">
+        <v>0</v>
+      </c>
+      <c r="IB10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="IC10">
+        <v>0</v>
+      </c>
+      <c r="ID10">
+        <v>1.365433745565868</v>
+      </c>
+      <c r="IE10">
+        <v>0.3980389321744662</v>
+      </c>
+      <c r="IF10" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG10" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -6897,6 +7175,33 @@
       <c r="HZ11">
         <v>30</v>
       </c>
+      <c r="IA11">
+        <v>0</v>
+      </c>
+      <c r="IB11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="IC11">
+        <v>1</v>
+      </c>
+      <c r="ID11">
+        <v>1.365433745565868</v>
+      </c>
+      <c r="IE11">
+        <v>0.3980389321744662</v>
+      </c>
+      <c r="IF11" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7329,6 +7634,33 @@
       <c r="HZ12">
         <v>39.6</v>
       </c>
+      <c r="IA12">
+        <v>0</v>
+      </c>
+      <c r="IB12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="IC12">
+        <v>0</v>
+      </c>
+      <c r="ID12">
+        <v>1.790971166336796</v>
+      </c>
+      <c r="IE12">
+        <v>0.6092001226037329</v>
+      </c>
+      <c r="IF12" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG12" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7776,6 +8108,33 @@
       <c r="HZ13">
         <v>37.2</v>
       </c>
+      <c r="IA13">
+        <v>0</v>
+      </c>
+      <c r="IB13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="IC13">
+        <v>0</v>
+      </c>
+      <c r="ID13">
+        <v>1.790971166336796</v>
+      </c>
+      <c r="IE13">
+        <v>0.6092001226037329</v>
+      </c>
+      <c r="IF13" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG13" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8157,6 +8516,33 @@
       <c r="HZ14">
         <v>21.6</v>
       </c>
+      <c r="IA14">
+        <v>0</v>
+      </c>
+      <c r="IB14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="IC14">
+        <v>0</v>
+      </c>
+      <c r="ID14">
+        <v>1.790971166336796</v>
+      </c>
+      <c r="IE14">
+        <v>0.6092001226037329</v>
+      </c>
+      <c r="IF14" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG14" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8553,6 +8939,33 @@
       <c r="HZ15">
         <v>21</v>
       </c>
+      <c r="IA15">
+        <v>0</v>
+      </c>
+      <c r="IB15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="IC15">
+        <v>1</v>
+      </c>
+      <c r="ID15">
+        <v>1.790971166336796</v>
+      </c>
+      <c r="IE15">
+        <v>0.6092001226037329</v>
+      </c>
+      <c r="IF15" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG15" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9026,6 +9439,33 @@
       <c r="HZ16">
         <v>31.2</v>
       </c>
+      <c r="IA16">
+        <v>0</v>
+      </c>
+      <c r="IB16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="IC16">
+        <v>1</v>
+      </c>
+      <c r="ID16">
+        <v>1.790971166336796</v>
+      </c>
+      <c r="IE16">
+        <v>0.6092001226037329</v>
+      </c>
+      <c r="IF16" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG16" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9473,6 +9913,33 @@
       <c r="HZ17">
         <v>31.2</v>
       </c>
+      <c r="IA17">
+        <v>0</v>
+      </c>
+      <c r="IB17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="IC17">
+        <v>1</v>
+      </c>
+      <c r="ID17">
+        <v>1.790971166336796</v>
+      </c>
+      <c r="IE17">
+        <v>0.6092001226037329</v>
+      </c>
+      <c r="IF17" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG17" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9914,6 +10381,33 @@
       <c r="HZ18">
         <v>30</v>
       </c>
+      <c r="IA18">
+        <v>0</v>
+      </c>
+      <c r="IB18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="IC18">
+        <v>1</v>
+      </c>
+      <c r="ID18">
+        <v>1.790971166336796</v>
+      </c>
+      <c r="IE18">
+        <v>0.6092001226037329</v>
+      </c>
+      <c r="IF18" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG18" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10367,6 +10861,33 @@
       <c r="HZ19">
         <v>37.2</v>
       </c>
+      <c r="IA19">
+        <v>0</v>
+      </c>
+      <c r="IB19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="IC19">
+        <v>1</v>
+      </c>
+      <c r="ID19">
+        <v>1.790971166336796</v>
+      </c>
+      <c r="IE19">
+        <v>0.6092001226037329</v>
+      </c>
+      <c r="IF19" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG19" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -10825,6 +11346,33 @@
       <c r="HZ20">
         <v>34.2</v>
       </c>
+      <c r="IA20">
+        <v>0</v>
+      </c>
+      <c r="IB20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="IC20">
+        <v>1</v>
+      </c>
+      <c r="ID20">
+        <v>1.790971166336796</v>
+      </c>
+      <c r="IE20">
+        <v>0.6092001226037329</v>
+      </c>
+      <c r="IF20" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG20" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -11298,6 +11846,33 @@
       <c r="HZ21">
         <v>34.2</v>
       </c>
+      <c r="IA21">
+        <v>0</v>
+      </c>
+      <c r="IB21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="IC21">
+        <v>1</v>
+      </c>
+      <c r="ID21">
+        <v>1.790971166336796</v>
+      </c>
+      <c r="IE21">
+        <v>0.6092001226037329</v>
+      </c>
+      <c r="IF21" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG21" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -11320,7 +11895,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Reef</t>
+          <t>Stone_pile</t>
         </is>
       </c>
       <c r="F22">
@@ -11740,6 +12315,33 @@
       </c>
       <c r="HZ22">
         <v>31.2</v>
+      </c>
+      <c r="IA22">
+        <v>1</v>
+      </c>
+      <c r="IB22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="IC22">
+        <v>1</v>
+      </c>
+      <c r="ID22">
+        <v>0.1756807860302614</v>
+      </c>
+      <c r="IE22">
+        <v>0.007696109834573639</v>
+      </c>
+      <c r="IF22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG22" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -12177,6 +12779,33 @@
       <c r="HZ23">
         <v>26.4</v>
       </c>
+      <c r="IA23">
+        <v>1</v>
+      </c>
+      <c r="IB23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="IC23">
+        <v>1</v>
+      </c>
+      <c r="ID23">
+        <v>0.1756807860302614</v>
+      </c>
+      <c r="IE23">
+        <v>0.007696109834573639</v>
+      </c>
+      <c r="IF23" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG23" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -12199,7 +12828,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Reef</t>
+          <t>Stone_pile</t>
         </is>
       </c>
       <c r="F24">
@@ -12572,6 +13201,33 @@
       </c>
       <c r="HZ24">
         <v>18</v>
+      </c>
+      <c r="IA24">
+        <v>1</v>
+      </c>
+      <c r="IB24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="IC24">
+        <v>0</v>
+      </c>
+      <c r="ID24">
+        <v>0.1756807860302614</v>
+      </c>
+      <c r="IE24">
+        <v>0.007696109834573639</v>
+      </c>
+      <c r="IF24" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG24" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -13005,6 +13661,33 @@
       <c r="HZ25">
         <v>18</v>
       </c>
+      <c r="IA25">
+        <v>1</v>
+      </c>
+      <c r="IB25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="IC25">
+        <v>1</v>
+      </c>
+      <c r="ID25">
+        <v>0.1756807860302614</v>
+      </c>
+      <c r="IE25">
+        <v>0.007696109834573639</v>
+      </c>
+      <c r="IF25" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG25" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -13027,7 +13710,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Reef</t>
+          <t>Stone_pile</t>
         </is>
       </c>
       <c r="F26">
@@ -13431,6 +14114,33 @@
       </c>
       <c r="HZ26">
         <v>14.4</v>
+      </c>
+      <c r="IA26">
+        <v>1</v>
+      </c>
+      <c r="IB26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="IC26">
+        <v>1</v>
+      </c>
+      <c r="ID26">
+        <v>0.1756807860302614</v>
+      </c>
+      <c r="IE26">
+        <v>0.007696109834573639</v>
+      </c>
+      <c r="IF26" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG26" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -13491,6 +14201,11 @@
       <c r="O27">
         <v>0</v>
       </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>site filled with weed</t>
+        </is>
+      </c>
       <c r="Q27" t="inlineStr">
         <is>
           <t>1</t>
@@ -13879,6 +14594,33 @@
       </c>
       <c r="HZ27">
         <v>18</v>
+      </c>
+      <c r="IA27">
+        <v>1</v>
+      </c>
+      <c r="IB27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="IC27">
+        <v>1</v>
+      </c>
+      <c r="ID27">
+        <v>0.1756807860302614</v>
+      </c>
+      <c r="IE27">
+        <v>0.007696109834573639</v>
+      </c>
+      <c r="IF27" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG27" t="inlineStr">
+        <is>
+          <t>compromised</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -13902,7 +14644,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Reef</t>
+          <t>Stone_pile</t>
         </is>
       </c>
       <c r="F28">
@@ -14336,6 +15078,33 @@
       </c>
       <c r="HZ28">
         <v>18</v>
+      </c>
+      <c r="IA28">
+        <v>1</v>
+      </c>
+      <c r="IB28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="IC28">
+        <v>1</v>
+      </c>
+      <c r="ID28">
+        <v>0.1756807860302614</v>
+      </c>
+      <c r="IE28">
+        <v>0.007696109834573639</v>
+      </c>
+      <c r="IF28" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG28" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -14739,6 +15508,33 @@
       <c r="HZ29">
         <v>18</v>
       </c>
+      <c r="IA29">
+        <v>1</v>
+      </c>
+      <c r="IB29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="IC29">
+        <v>0</v>
+      </c>
+      <c r="ID29">
+        <v>0.1756807860302614</v>
+      </c>
+      <c r="IE29">
+        <v>0.007696109834573639</v>
+      </c>
+      <c r="IF29" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG29" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -14761,7 +15557,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Reef</t>
+          <t>Stone_pile</t>
         </is>
       </c>
       <c r="F30">
@@ -15160,6 +15956,33 @@
       </c>
       <c r="HZ30">
         <v>20.1</v>
+      </c>
+      <c r="IA30">
+        <v>1</v>
+      </c>
+      <c r="IB30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="IC30">
+        <v>1</v>
+      </c>
+      <c r="ID30">
+        <v>0.1756807860302614</v>
+      </c>
+      <c r="IE30">
+        <v>0.007696109834573639</v>
+      </c>
+      <c r="IF30" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG30" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -15618,6 +16441,33 @@
       <c r="HZ31">
         <v>30</v>
       </c>
+      <c r="IA31">
+        <v>1</v>
+      </c>
+      <c r="IB31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="IC31">
+        <v>1</v>
+      </c>
+      <c r="ID31">
+        <v>0.1756807860302614</v>
+      </c>
+      <c r="IE31">
+        <v>0.007696109834573639</v>
+      </c>
+      <c r="IF31" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG31" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -16036,6 +16886,33 @@
       <c r="HZ32">
         <v>39.6</v>
       </c>
+      <c r="IA32">
+        <v>1</v>
+      </c>
+      <c r="IB32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="IC32">
+        <v>1</v>
+      </c>
+      <c r="ID32">
+        <v>0.6012182068011893</v>
+      </c>
+      <c r="IE32">
+        <v>0.08767642431597361</v>
+      </c>
+      <c r="IF32" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG32" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -16487,6 +17364,33 @@
       <c r="HZ33">
         <v>37.2</v>
       </c>
+      <c r="IA33">
+        <v>1</v>
+      </c>
+      <c r="IB33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="IC33">
+        <v>1</v>
+      </c>
+      <c r="ID33">
+        <v>0.6012182068011893</v>
+      </c>
+      <c r="IE33">
+        <v>0.08767642431597361</v>
+      </c>
+      <c r="IF33" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG33" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -16700,6 +17604,30 @@
       <c r="HZ34">
         <v>21.6</v>
       </c>
+      <c r="IA34">
+        <v>1</v>
+      </c>
+      <c r="IB34" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="ID34">
+        <v>0.6012182068011893</v>
+      </c>
+      <c r="IE34">
+        <v>0.08767642431597361</v>
+      </c>
+      <c r="IF34" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG34" t="inlineStr">
+        <is>
+          <t>compromised</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -16913,6 +17841,30 @@
       <c r="HZ35">
         <v>21</v>
       </c>
+      <c r="IA35">
+        <v>1</v>
+      </c>
+      <c r="IB35" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="ID35">
+        <v>0.6012182068011893</v>
+      </c>
+      <c r="IE35">
+        <v>0.08767642431597361</v>
+      </c>
+      <c r="IF35" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG35" t="inlineStr">
+        <is>
+          <t>compromised</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -17357,6 +18309,33 @@
       <c r="HZ36">
         <v>31.2</v>
       </c>
+      <c r="IA36">
+        <v>1</v>
+      </c>
+      <c r="IB36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="IC36">
+        <v>1</v>
+      </c>
+      <c r="ID36">
+        <v>0.6012182068011893</v>
+      </c>
+      <c r="IE36">
+        <v>0.08767642431597361</v>
+      </c>
+      <c r="IF36" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG36" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -17805,6 +18784,33 @@
       <c r="HZ37">
         <v>31.2</v>
       </c>
+      <c r="IA37">
+        <v>1</v>
+      </c>
+      <c r="IB37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="IC37">
+        <v>1</v>
+      </c>
+      <c r="ID37">
+        <v>0.6012182068011893</v>
+      </c>
+      <c r="IE37">
+        <v>0.08767642431597361</v>
+      </c>
+      <c r="IF37" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG37" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -18274,6 +19280,33 @@
       <c r="HZ38">
         <v>30</v>
       </c>
+      <c r="IA38">
+        <v>1</v>
+      </c>
+      <c r="IB38" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="IC38">
+        <v>1</v>
+      </c>
+      <c r="ID38">
+        <v>0.6012182068011893</v>
+      </c>
+      <c r="IE38">
+        <v>0.08767642431597361</v>
+      </c>
+      <c r="IF38" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG38" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -18767,6 +19800,33 @@
       <c r="HZ39">
         <v>37.2</v>
       </c>
+      <c r="IA39">
+        <v>1</v>
+      </c>
+      <c r="IB39" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="IC39">
+        <v>1</v>
+      </c>
+      <c r="ID39">
+        <v>0.6012182068011893</v>
+      </c>
+      <c r="IE39">
+        <v>0.08767642431597361</v>
+      </c>
+      <c r="IF39" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG39" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -19214,6 +20274,33 @@
       <c r="HZ40">
         <v>34.2</v>
       </c>
+      <c r="IA40">
+        <v>1</v>
+      </c>
+      <c r="IB40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="IC40">
+        <v>1</v>
+      </c>
+      <c r="ID40">
+        <v>0.6012182068011893</v>
+      </c>
+      <c r="IE40">
+        <v>0.08767642431597361</v>
+      </c>
+      <c r="IF40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG40" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -19610,6 +20697,33 @@
       <c r="HZ41">
         <v>34.2</v>
       </c>
+      <c r="IA41">
+        <v>1</v>
+      </c>
+      <c r="IB41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="IC41">
+        <v>1</v>
+      </c>
+      <c r="ID41">
+        <v>0.6012182068011893</v>
+      </c>
+      <c r="IE41">
+        <v>0.08767642431597361</v>
+      </c>
+      <c r="IF41" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG41" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -19632,7 +20746,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Reef</t>
+          <t>Stone_pile</t>
         </is>
       </c>
       <c r="F42">
@@ -20003,6 +21117,33 @@
       </c>
       <c r="HZ42">
         <v>31.2</v>
+      </c>
+      <c r="IA42">
+        <v>2</v>
+      </c>
+      <c r="IB42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="IC42">
+        <v>0</v>
+      </c>
+      <c r="ID42">
+        <v>4.418038292131671</v>
+      </c>
+      <c r="IE42">
+        <v>0.6450592630039791</v>
+      </c>
+      <c r="IF42" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG42" t="inlineStr">
+        <is>
+          <t>compromised</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -20412,6 +21553,33 @@
       <c r="HZ43">
         <v>26.4</v>
       </c>
+      <c r="IA43">
+        <v>2</v>
+      </c>
+      <c r="IB43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="IC43">
+        <v>1</v>
+      </c>
+      <c r="ID43">
+        <v>4.418038292131671</v>
+      </c>
+      <c r="IE43">
+        <v>0.6450592630039791</v>
+      </c>
+      <c r="IF43" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG43" t="inlineStr">
+        <is>
+          <t>compromised</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -20434,7 +21602,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Reef</t>
+          <t>Stone_pile</t>
         </is>
       </c>
       <c r="F44">
@@ -20840,6 +22008,33 @@
       </c>
       <c r="HZ44">
         <v>18</v>
+      </c>
+      <c r="IA44">
+        <v>2</v>
+      </c>
+      <c r="IB44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="IC44">
+        <v>0</v>
+      </c>
+      <c r="ID44">
+        <v>4.418038292131671</v>
+      </c>
+      <c r="IE44">
+        <v>0.6450592630039791</v>
+      </c>
+      <c r="IF44" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG44" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -21270,6 +22465,33 @@
       <c r="HZ45">
         <v>18</v>
       </c>
+      <c r="IA45">
+        <v>2</v>
+      </c>
+      <c r="IB45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="IC45">
+        <v>0</v>
+      </c>
+      <c r="ID45">
+        <v>4.418038292131671</v>
+      </c>
+      <c r="IE45">
+        <v>0.6450592630039791</v>
+      </c>
+      <c r="IF45" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG45" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -21292,7 +22514,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Reef</t>
+          <t>Stone_pile</t>
         </is>
       </c>
       <c r="F46">
@@ -21654,6 +22876,33 @@
       </c>
       <c r="HZ46">
         <v>14.4</v>
+      </c>
+      <c r="IA46">
+        <v>2</v>
+      </c>
+      <c r="IB46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="IC46">
+        <v>1</v>
+      </c>
+      <c r="ID46">
+        <v>4.418038292131671</v>
+      </c>
+      <c r="IE46">
+        <v>0.6450592630039791</v>
+      </c>
+      <c r="IF46" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG46" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -22049,6 +23298,33 @@
       <c r="HZ47">
         <v>18</v>
       </c>
+      <c r="IA47">
+        <v>2</v>
+      </c>
+      <c r="IB47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="IC47">
+        <v>0</v>
+      </c>
+      <c r="ID47">
+        <v>4.418038292131671</v>
+      </c>
+      <c r="IE47">
+        <v>0.6450592630039791</v>
+      </c>
+      <c r="IF47" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG47" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -22071,7 +23347,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Reef</t>
+          <t>Stone_pile</t>
         </is>
       </c>
       <c r="F48">
@@ -22472,6 +23748,33 @@
       </c>
       <c r="HZ48">
         <v>18</v>
+      </c>
+      <c r="IA48">
+        <v>2</v>
+      </c>
+      <c r="IB48" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="IC48">
+        <v>1</v>
+      </c>
+      <c r="ID48">
+        <v>4.418038292131671</v>
+      </c>
+      <c r="IE48">
+        <v>0.6450592630039791</v>
+      </c>
+      <c r="IF48" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG48" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -22846,6 +24149,33 @@
       <c r="HZ49">
         <v>18</v>
       </c>
+      <c r="IA49">
+        <v>2</v>
+      </c>
+      <c r="IB49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="IC49">
+        <v>0</v>
+      </c>
+      <c r="ID49">
+        <v>4.418038292131671</v>
+      </c>
+      <c r="IE49">
+        <v>0.6450592630039791</v>
+      </c>
+      <c r="IF49" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG49" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -22868,7 +24198,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Reef</t>
+          <t>Stone_pile</t>
         </is>
       </c>
       <c r="F50">
@@ -23294,6 +24624,33 @@
       </c>
       <c r="HZ50">
         <v>20.1</v>
+      </c>
+      <c r="IA50">
+        <v>2</v>
+      </c>
+      <c r="IB50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="IC50">
+        <v>1</v>
+      </c>
+      <c r="ID50">
+        <v>4.418038292131671</v>
+      </c>
+      <c r="IE50">
+        <v>0.6450592630039791</v>
+      </c>
+      <c r="IF50" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG50" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -23719,6 +25076,33 @@
       <c r="HZ51">
         <v>30</v>
       </c>
+      <c r="IA51">
+        <v>2</v>
+      </c>
+      <c r="IB51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="IC51">
+        <v>1</v>
+      </c>
+      <c r="ID51">
+        <v>4.418038292131671</v>
+      </c>
+      <c r="IE51">
+        <v>0.6450592630039791</v>
+      </c>
+      <c r="IF51" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG51" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -24173,6 +25557,33 @@
       <c r="HZ52">
         <v>39.6</v>
       </c>
+      <c r="IA52">
+        <v>2</v>
+      </c>
+      <c r="IB52" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="IC52">
+        <v>0</v>
+      </c>
+      <c r="ID52">
+        <v>1.32638364073583</v>
+      </c>
+      <c r="IE52">
+        <v>0.3790067460938265</v>
+      </c>
+      <c r="IF52" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG52" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -24621,6 +26032,33 @@
       <c r="HZ53">
         <v>37.2</v>
       </c>
+      <c r="IA53">
+        <v>2</v>
+      </c>
+      <c r="IB53" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="IC53">
+        <v>1</v>
+      </c>
+      <c r="ID53">
+        <v>1.32638364073583</v>
+      </c>
+      <c r="IE53">
+        <v>0.3790067460938265</v>
+      </c>
+      <c r="IF53" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG53" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -25048,6 +26486,33 @@
       <c r="HZ54">
         <v>21.6</v>
       </c>
+      <c r="IA54">
+        <v>2</v>
+      </c>
+      <c r="IB54" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="IC54">
+        <v>1</v>
+      </c>
+      <c r="ID54">
+        <v>1.32638364073583</v>
+      </c>
+      <c r="IE54">
+        <v>0.3790067460938265</v>
+      </c>
+      <c r="IF54" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG54" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -25480,6 +26945,33 @@
       <c r="HZ55">
         <v>21</v>
       </c>
+      <c r="IA55">
+        <v>2</v>
+      </c>
+      <c r="IB55" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="IC55">
+        <v>0</v>
+      </c>
+      <c r="ID55">
+        <v>1.32638364073583</v>
+      </c>
+      <c r="IE55">
+        <v>0.3790067460938265</v>
+      </c>
+      <c r="IF55" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG55" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -25912,6 +27404,33 @@
       <c r="HZ56">
         <v>31.2</v>
       </c>
+      <c r="IA56">
+        <v>2</v>
+      </c>
+      <c r="IB56" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="IC56">
+        <v>1</v>
+      </c>
+      <c r="ID56">
+        <v>1.32638364073583</v>
+      </c>
+      <c r="IE56">
+        <v>0.3790067460938265</v>
+      </c>
+      <c r="IF56" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG56" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -26279,6 +27798,33 @@
       <c r="HZ57">
         <v>31.2</v>
       </c>
+      <c r="IA57">
+        <v>2</v>
+      </c>
+      <c r="IB57" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="IC57">
+        <v>0</v>
+      </c>
+      <c r="ID57">
+        <v>1.32638364073583</v>
+      </c>
+      <c r="IE57">
+        <v>0.3790067460938265</v>
+      </c>
+      <c r="IF57" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG57" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -26736,6 +28282,33 @@
       <c r="HZ58">
         <v>30</v>
       </c>
+      <c r="IA58">
+        <v>2</v>
+      </c>
+      <c r="IB58" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="IC58">
+        <v>1</v>
+      </c>
+      <c r="ID58">
+        <v>1.32638364073583</v>
+      </c>
+      <c r="IE58">
+        <v>0.3790067460938265</v>
+      </c>
+      <c r="IF58" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG58" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -27163,6 +28736,33 @@
       <c r="HZ59">
         <v>37.2</v>
       </c>
+      <c r="IA59">
+        <v>2</v>
+      </c>
+      <c r="IB59" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="IC59">
+        <v>0</v>
+      </c>
+      <c r="ID59">
+        <v>1.32638364073583</v>
+      </c>
+      <c r="IE59">
+        <v>0.3790067460938265</v>
+      </c>
+      <c r="IF59" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG59" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -27600,6 +29200,33 @@
       <c r="HZ60">
         <v>34.2</v>
       </c>
+      <c r="IA60">
+        <v>2</v>
+      </c>
+      <c r="IB60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="IC60">
+        <v>1</v>
+      </c>
+      <c r="ID60">
+        <v>1.32638364073583</v>
+      </c>
+      <c r="IE60">
+        <v>0.3790067460938265</v>
+      </c>
+      <c r="IF60" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG60" t="inlineStr">
+        <is>
+          <t>compromised</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -28028,6 +29655,33 @@
       <c r="HZ61">
         <v>34.2</v>
       </c>
+      <c r="IA61">
+        <v>2</v>
+      </c>
+      <c r="IB61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="IC61">
+        <v>1</v>
+      </c>
+      <c r="ID61">
+        <v>1.32638364073583</v>
+      </c>
+      <c r="IE61">
+        <v>0.3790067460938265</v>
+      </c>
+      <c r="IF61" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG61" t="inlineStr">
+        <is>
+          <t>compromised</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -28050,7 +29704,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Reef</t>
+          <t>Stone_pile</t>
         </is>
       </c>
       <c r="F62">
@@ -28232,6 +29886,30 @@
       </c>
       <c r="HZ62">
         <v>31.2</v>
+      </c>
+      <c r="IA62">
+        <v>3</v>
+      </c>
+      <c r="IB62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="ID62">
+        <v>6.207047277994345</v>
+      </c>
+      <c r="IE62">
+        <v>0.001448549898926232</v>
+      </c>
+      <c r="IF62" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG62" t="inlineStr">
+        <is>
+          <t>compromised</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -28443,6 +30121,30 @@
       <c r="HZ63">
         <v>26.4</v>
       </c>
+      <c r="IA63">
+        <v>3</v>
+      </c>
+      <c r="IB63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="ID63">
+        <v>6.207047277994345</v>
+      </c>
+      <c r="IE63">
+        <v>0.001448549898926232</v>
+      </c>
+      <c r="IF63" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG63" t="inlineStr">
+        <is>
+          <t>compromised</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -28465,7 +30167,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Reef</t>
+          <t>Stone_pile</t>
         </is>
       </c>
       <c r="F64">
@@ -28826,6 +30528,33 @@
       </c>
       <c r="HZ64">
         <v>18</v>
+      </c>
+      <c r="IA64">
+        <v>3</v>
+      </c>
+      <c r="IB64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="IC64">
+        <v>0</v>
+      </c>
+      <c r="ID64">
+        <v>6.207047277994345</v>
+      </c>
+      <c r="IE64">
+        <v>0.001448549898926232</v>
+      </c>
+      <c r="IF64" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG64" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -29232,6 +30961,33 @@
       <c r="HZ65">
         <v>18</v>
       </c>
+      <c r="IA65">
+        <v>3</v>
+      </c>
+      <c r="IB65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="IC65">
+        <v>0</v>
+      </c>
+      <c r="ID65">
+        <v>6.207047277994345</v>
+      </c>
+      <c r="IE65">
+        <v>0.001448549898926232</v>
+      </c>
+      <c r="IF65" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG65" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -29254,7 +31010,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Reef</t>
+          <t>Stone_pile</t>
         </is>
       </c>
       <c r="F66">
@@ -29649,6 +31405,33 @@
       </c>
       <c r="HZ66">
         <v>14.4</v>
+      </c>
+      <c r="IA66">
+        <v>3</v>
+      </c>
+      <c r="IB66" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="IC66">
+        <v>1</v>
+      </c>
+      <c r="ID66">
+        <v>6.207047277994345</v>
+      </c>
+      <c r="IE66">
+        <v>0.001448549898926232</v>
+      </c>
+      <c r="IF66" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG66" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -30092,6 +31875,33 @@
       <c r="HZ67">
         <v>18</v>
       </c>
+      <c r="IA67">
+        <v>3</v>
+      </c>
+      <c r="IB67" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="IC67">
+        <v>1</v>
+      </c>
+      <c r="ID67">
+        <v>6.207047277994345</v>
+      </c>
+      <c r="IE67">
+        <v>0.001448549898926232</v>
+      </c>
+      <c r="IF67" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG67" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -30114,7 +31924,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Reef</t>
+          <t>Stone_pile</t>
         </is>
       </c>
       <c r="F68">
@@ -30509,6 +32319,33 @@
       </c>
       <c r="HZ68">
         <v>18</v>
+      </c>
+      <c r="IA68">
+        <v>3</v>
+      </c>
+      <c r="IB68" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="IC68">
+        <v>1</v>
+      </c>
+      <c r="ID68">
+        <v>6.207047277994345</v>
+      </c>
+      <c r="IE68">
+        <v>0.001448549898926232</v>
+      </c>
+      <c r="IF68" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG68" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -30886,6 +32723,33 @@
       <c r="HZ69">
         <v>18</v>
       </c>
+      <c r="IA69">
+        <v>3</v>
+      </c>
+      <c r="IB69" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="IC69">
+        <v>0</v>
+      </c>
+      <c r="ID69">
+        <v>6.207047277994345</v>
+      </c>
+      <c r="IE69">
+        <v>0.001448549898926232</v>
+      </c>
+      <c r="IF69" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG69" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -30908,7 +32772,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Reef</t>
+          <t>Stone_pile</t>
         </is>
       </c>
       <c r="F70">
@@ -31298,6 +33162,33 @@
       </c>
       <c r="HZ70">
         <v>20.1</v>
+      </c>
+      <c r="IA70">
+        <v>3</v>
+      </c>
+      <c r="IB70" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="IC70">
+        <v>1</v>
+      </c>
+      <c r="ID70">
+        <v>6.207047277994345</v>
+      </c>
+      <c r="IE70">
+        <v>0.001448549898926232</v>
+      </c>
+      <c r="IF70" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG70" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -31696,6 +33587,33 @@
       <c r="HZ71">
         <v>30</v>
       </c>
+      <c r="IA71">
+        <v>3</v>
+      </c>
+      <c r="IB71" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="IC71">
+        <v>1</v>
+      </c>
+      <c r="ID71">
+        <v>6.207047277994345</v>
+      </c>
+      <c r="IE71">
+        <v>0.001448549898926232</v>
+      </c>
+      <c r="IF71" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG71" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -32174,6 +34092,33 @@
       <c r="HZ72">
         <v>39.6</v>
       </c>
+      <c r="IA72">
+        <v>3</v>
+      </c>
+      <c r="IB72" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="IC72">
+        <v>1</v>
+      </c>
+      <c r="ID72">
+        <v>4.179236178526182</v>
+      </c>
+      <c r="IE72">
+        <v>0.7541255419473551</v>
+      </c>
+      <c r="IF72" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG72" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -32631,6 +34576,33 @@
       <c r="HZ73">
         <v>37.2</v>
       </c>
+      <c r="IA73">
+        <v>3</v>
+      </c>
+      <c r="IB73" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="IC73">
+        <v>0</v>
+      </c>
+      <c r="ID73">
+        <v>4.179236178526182</v>
+      </c>
+      <c r="IE73">
+        <v>0.7541255419473551</v>
+      </c>
+      <c r="IF73" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG73" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -33049,6 +35021,33 @@
       <c r="HZ74">
         <v>21.6</v>
       </c>
+      <c r="IA74">
+        <v>3</v>
+      </c>
+      <c r="IB74" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="IC74">
+        <v>0</v>
+      </c>
+      <c r="ID74">
+        <v>4.179236178526182</v>
+      </c>
+      <c r="IE74">
+        <v>0.7541255419473551</v>
+      </c>
+      <c r="IF74" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG74" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -33455,6 +35454,33 @@
       <c r="HZ75">
         <v>21</v>
       </c>
+      <c r="IA75">
+        <v>3</v>
+      </c>
+      <c r="IB75" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="IC75">
+        <v>0</v>
+      </c>
+      <c r="ID75">
+        <v>4.179236178526182</v>
+      </c>
+      <c r="IE75">
+        <v>0.7541255419473551</v>
+      </c>
+      <c r="IF75" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG75" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -33878,6 +35904,33 @@
       <c r="HZ76">
         <v>31.2</v>
       </c>
+      <c r="IA76">
+        <v>3</v>
+      </c>
+      <c r="IB76" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="IC76">
+        <v>1</v>
+      </c>
+      <c r="ID76">
+        <v>4.179236178526182</v>
+      </c>
+      <c r="IE76">
+        <v>0.7541255419473551</v>
+      </c>
+      <c r="IF76" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG76" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -34296,6 +36349,33 @@
       <c r="HZ77">
         <v>31.2</v>
       </c>
+      <c r="IA77">
+        <v>3</v>
+      </c>
+      <c r="IB77" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="IC77">
+        <v>1</v>
+      </c>
+      <c r="ID77">
+        <v>4.179236178526182</v>
+      </c>
+      <c r="IE77">
+        <v>0.7541255419473551</v>
+      </c>
+      <c r="IF77" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG77" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -34774,6 +36854,33 @@
       <c r="HZ78">
         <v>30</v>
       </c>
+      <c r="IA78">
+        <v>3</v>
+      </c>
+      <c r="IB78" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="IC78">
+        <v>1</v>
+      </c>
+      <c r="ID78">
+        <v>4.179236178526182</v>
+      </c>
+      <c r="IE78">
+        <v>0.7541255419473551</v>
+      </c>
+      <c r="IF78" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG78" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -35180,6 +37287,33 @@
       <c r="HZ79">
         <v>37.2</v>
       </c>
+      <c r="IA79">
+        <v>3</v>
+      </c>
+      <c r="IB79" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="IC79">
+        <v>1</v>
+      </c>
+      <c r="ID79">
+        <v>4.179236178526182</v>
+      </c>
+      <c r="IE79">
+        <v>0.7541255419473551</v>
+      </c>
+      <c r="IF79" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG79" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -35612,6 +37746,33 @@
       <c r="HZ80">
         <v>34.2</v>
       </c>
+      <c r="IA80">
+        <v>3</v>
+      </c>
+      <c r="IB80" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="IC80">
+        <v>1</v>
+      </c>
+      <c r="ID80">
+        <v>4.179236178526182</v>
+      </c>
+      <c r="IE80">
+        <v>0.7541255419473551</v>
+      </c>
+      <c r="IF80" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG80" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -36044,6 +38205,33 @@
       <c r="HZ81">
         <v>34.2</v>
       </c>
+      <c r="IA81">
+        <v>3</v>
+      </c>
+      <c r="IB81" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="IC81">
+        <v>1</v>
+      </c>
+      <c r="ID81">
+        <v>4.179236178526182</v>
+      </c>
+      <c r="IE81">
+        <v>0.7541255419473551</v>
+      </c>
+      <c r="IF81" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG81" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -36066,7 +38254,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Reef</t>
+          <t>Stone_pile</t>
         </is>
       </c>
       <c r="F82">
@@ -36477,6 +38665,33 @@
       </c>
       <c r="HZ82">
         <v>31.2</v>
+      </c>
+      <c r="IA82">
+        <v>4</v>
+      </c>
+      <c r="IB82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="IC82">
+        <v>1</v>
+      </c>
+      <c r="ID82">
+        <v>5.017294318458739</v>
+      </c>
+      <c r="IE82">
+        <v>0.3498985595628208</v>
+      </c>
+      <c r="IF82" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG82" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -36908,6 +39123,33 @@
       <c r="HZ83">
         <v>26.4</v>
       </c>
+      <c r="IA83">
+        <v>4</v>
+      </c>
+      <c r="IB83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="IC83">
+        <v>1</v>
+      </c>
+      <c r="ID83">
+        <v>5.017294318458739</v>
+      </c>
+      <c r="IE83">
+        <v>0.3498985595628208</v>
+      </c>
+      <c r="IF83" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG83" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -36930,7 +39172,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Reef</t>
+          <t>Stone_pile</t>
         </is>
       </c>
       <c r="F84">
@@ -37291,6 +39533,33 @@
       </c>
       <c r="HZ84">
         <v>18</v>
+      </c>
+      <c r="IA84">
+        <v>4</v>
+      </c>
+      <c r="IB84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="IC84">
+        <v>0</v>
+      </c>
+      <c r="ID84">
+        <v>5.017294318458739</v>
+      </c>
+      <c r="IE84">
+        <v>0.3498985595628208</v>
+      </c>
+      <c r="IF84" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG84" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -37697,6 +39966,33 @@
       <c r="HZ85">
         <v>18</v>
       </c>
+      <c r="IA85">
+        <v>4</v>
+      </c>
+      <c r="IB85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="IC85">
+        <v>0</v>
+      </c>
+      <c r="ID85">
+        <v>5.017294318458739</v>
+      </c>
+      <c r="IE85">
+        <v>0.3498985595628208</v>
+      </c>
+      <c r="IF85" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG85" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -37719,7 +40015,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Reef</t>
+          <t>Stone_pile</t>
         </is>
       </c>
       <c r="F86">
@@ -38141,6 +40437,33 @@
       </c>
       <c r="HZ86">
         <v>14.4</v>
+      </c>
+      <c r="IA86">
+        <v>4</v>
+      </c>
+      <c r="IB86" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="IC86">
+        <v>1</v>
+      </c>
+      <c r="ID86">
+        <v>5.017294318458739</v>
+      </c>
+      <c r="IE86">
+        <v>0.3498985595628208</v>
+      </c>
+      <c r="IF86" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG86" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -38587,6 +40910,33 @@
       <c r="HZ87">
         <v>18</v>
       </c>
+      <c r="IA87">
+        <v>4</v>
+      </c>
+      <c r="IB87" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="IC87">
+        <v>1</v>
+      </c>
+      <c r="ID87">
+        <v>5.017294318458739</v>
+      </c>
+      <c r="IE87">
+        <v>0.3498985595628208</v>
+      </c>
+      <c r="IF87" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG87" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -38609,7 +40959,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Reef</t>
+          <t>Stone_pile</t>
         </is>
       </c>
       <c r="F88">
@@ -39061,6 +41411,33 @@
       </c>
       <c r="HZ88">
         <v>18</v>
+      </c>
+      <c r="IA88">
+        <v>4</v>
+      </c>
+      <c r="IB88" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="IC88">
+        <v>1</v>
+      </c>
+      <c r="ID88">
+        <v>0.2234899839781147</v>
+      </c>
+      <c r="IE88">
+        <v>0.01243505510753767</v>
+      </c>
+      <c r="IF88" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG88" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -39471,6 +41848,33 @@
       <c r="HZ89">
         <v>18</v>
       </c>
+      <c r="IA89">
+        <v>4</v>
+      </c>
+      <c r="IB89" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="IC89">
+        <v>0</v>
+      </c>
+      <c r="ID89">
+        <v>0.2234899839781147</v>
+      </c>
+      <c r="IE89">
+        <v>0.01243505510753767</v>
+      </c>
+      <c r="IF89" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG89" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -39493,7 +41897,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Reef</t>
+          <t>Stone_pile</t>
         </is>
       </c>
       <c r="F90">
@@ -39889,6 +42293,33 @@
       </c>
       <c r="HZ90">
         <v>20.1</v>
+      </c>
+      <c r="IA90">
+        <v>4</v>
+      </c>
+      <c r="IB90" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="IC90">
+        <v>1</v>
+      </c>
+      <c r="ID90">
+        <v>5.017294318458739</v>
+      </c>
+      <c r="IE90">
+        <v>0.3498985595628208</v>
+      </c>
+      <c r="IF90" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG90" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -40320,6 +42751,33 @@
       <c r="HZ91">
         <v>30</v>
       </c>
+      <c r="IA91">
+        <v>4</v>
+      </c>
+      <c r="IB91" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="IC91">
+        <v>1</v>
+      </c>
+      <c r="ID91">
+        <v>5.017294318458739</v>
+      </c>
+      <c r="IE91">
+        <v>0.3498985595628208</v>
+      </c>
+      <c r="IF91" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG91" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -40768,6 +43226,33 @@
       <c r="HZ92">
         <v>39.6</v>
       </c>
+      <c r="IA92">
+        <v>4</v>
+      </c>
+      <c r="IB92" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="IC92">
+        <v>1</v>
+      </c>
+      <c r="ID92">
+        <v>5.442831739229667</v>
+      </c>
+      <c r="IE92">
+        <v>0.1664002489072092</v>
+      </c>
+      <c r="IF92" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG92" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -41246,6 +43731,33 @@
       <c r="HZ93">
         <v>37.2</v>
       </c>
+      <c r="IA93">
+        <v>4</v>
+      </c>
+      <c r="IB93" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="IC93">
+        <v>1</v>
+      </c>
+      <c r="ID93">
+        <v>5.442831739229667</v>
+      </c>
+      <c r="IE93">
+        <v>0.1664002489072092</v>
+      </c>
+      <c r="IF93" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG93" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -41652,6 +44164,33 @@
       <c r="HZ94">
         <v>21.6</v>
       </c>
+      <c r="IA94">
+        <v>4</v>
+      </c>
+      <c r="IB94" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="IC94">
+        <v>0</v>
+      </c>
+      <c r="ID94">
+        <v>5.442831739229667</v>
+      </c>
+      <c r="IE94">
+        <v>0.1664002489072092</v>
+      </c>
+      <c r="IF94" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG94" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -42058,6 +44597,33 @@
       <c r="HZ95">
         <v>21</v>
       </c>
+      <c r="IA95">
+        <v>4</v>
+      </c>
+      <c r="IB95" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="IC95">
+        <v>1</v>
+      </c>
+      <c r="ID95">
+        <v>5.442831739229667</v>
+      </c>
+      <c r="IE95">
+        <v>0.1664002489072092</v>
+      </c>
+      <c r="IF95" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG95" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -42490,6 +45056,33 @@
       <c r="HZ96">
         <v>31.2</v>
       </c>
+      <c r="IA96">
+        <v>4</v>
+      </c>
+      <c r="IB96" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="IC96">
+        <v>1</v>
+      </c>
+      <c r="ID96">
+        <v>5.442831739229667</v>
+      </c>
+      <c r="IE96">
+        <v>0.1664002489072092</v>
+      </c>
+      <c r="IF96" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG96" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -42983,6 +45576,33 @@
       <c r="HZ97">
         <v>31.2</v>
       </c>
+      <c r="IA97">
+        <v>4</v>
+      </c>
+      <c r="IB97" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="IC97">
+        <v>1</v>
+      </c>
+      <c r="ID97">
+        <v>5.442831739229667</v>
+      </c>
+      <c r="IE97">
+        <v>0.1664002489072092</v>
+      </c>
+      <c r="IF97" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG97" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -43419,6 +46039,33 @@
       <c r="HZ98">
         <v>30</v>
       </c>
+      <c r="IA98">
+        <v>4</v>
+      </c>
+      <c r="IB98" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="IC98">
+        <v>1</v>
+      </c>
+      <c r="ID98">
+        <v>5.442831739229667</v>
+      </c>
+      <c r="IE98">
+        <v>0.1664002489072092</v>
+      </c>
+      <c r="IF98" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG98" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -43855,6 +46502,33 @@
       <c r="HZ99">
         <v>37.2</v>
       </c>
+      <c r="IA99">
+        <v>4</v>
+      </c>
+      <c r="IB99" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="IC99">
+        <v>1</v>
+      </c>
+      <c r="ID99">
+        <v>5.442831739229667</v>
+      </c>
+      <c r="IE99">
+        <v>0.1664002489072092</v>
+      </c>
+      <c r="IF99" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG99" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -44278,6 +46952,33 @@
       <c r="HZ100">
         <v>34.2</v>
       </c>
+      <c r="IA100">
+        <v>4</v>
+      </c>
+      <c r="IB100" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="IC100">
+        <v>1</v>
+      </c>
+      <c r="ID100">
+        <v>5.442831739229667</v>
+      </c>
+      <c r="IE100">
+        <v>0.1664002489072092</v>
+      </c>
+      <c r="IF100" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG100" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -44671,6 +47372,33 @@
       <c r="HZ101">
         <v>34.2</v>
       </c>
+      <c r="IA101">
+        <v>4</v>
+      </c>
+      <c r="IB101" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="IC101">
+        <v>1</v>
+      </c>
+      <c r="ID101">
+        <v>5.442831739229667</v>
+      </c>
+      <c r="IE101">
+        <v>0.1664002489072092</v>
+      </c>
+      <c r="IF101" t="inlineStr">
+        <is>
+          <t>Waning</t>
+        </is>
+      </c>
+      <c r="IG101" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -44693,7 +47421,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Reef</t>
+          <t>Stone_pile</t>
         </is>
       </c>
       <c r="F102">
@@ -45080,6 +47808,33 @@
       </c>
       <c r="HZ102">
         <v>31.2</v>
+      </c>
+      <c r="IA102">
+        <v>5</v>
+      </c>
+      <c r="IB102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="IC102">
+        <v>1</v>
+      </c>
+      <c r="ID102">
+        <v>1.161424128298219</v>
+      </c>
+      <c r="IE102">
+        <v>0.3009832601809674</v>
+      </c>
+      <c r="IF102" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG102" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
       </c>
     </row>
     <row r="103">
@@ -45481,6 +48236,33 @@
       <c r="HZ103">
         <v>26.4</v>
       </c>
+      <c r="IA103">
+        <v>5</v>
+      </c>
+      <c r="IB103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="IC103">
+        <v>0</v>
+      </c>
+      <c r="ID103">
+        <v>1.161424128298219</v>
+      </c>
+      <c r="IE103">
+        <v>0.3009832601809674</v>
+      </c>
+      <c r="IF103" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG103" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -45503,7 +48285,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Reef</t>
+          <t>Stone_pile</t>
         </is>
       </c>
       <c r="F104">
@@ -45930,6 +48712,33 @@
       </c>
       <c r="HZ104">
         <v>18</v>
+      </c>
+      <c r="IA104">
+        <v>5</v>
+      </c>
+      <c r="IB104" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="IC104">
+        <v>1</v>
+      </c>
+      <c r="ID104">
+        <v>1.161424128298219</v>
+      </c>
+      <c r="IE104">
+        <v>0.3009832601809674</v>
+      </c>
+      <c r="IF104" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG104" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
       </c>
     </row>
     <row r="105">
@@ -46351,6 +49160,33 @@
       <c r="HZ105">
         <v>18</v>
       </c>
+      <c r="IA105">
+        <v>5</v>
+      </c>
+      <c r="IB105" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="IC105">
+        <v>1</v>
+      </c>
+      <c r="ID105">
+        <v>1.161424128298219</v>
+      </c>
+      <c r="IE105">
+        <v>0.3009832601809674</v>
+      </c>
+      <c r="IF105" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG105" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -46373,7 +49209,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Reef</t>
+          <t>Stone_pile</t>
         </is>
       </c>
       <c r="F106">
@@ -46795,6 +49631,33 @@
       </c>
       <c r="HZ106">
         <v>14.4</v>
+      </c>
+      <c r="IA106">
+        <v>5</v>
+      </c>
+      <c r="IB106" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="IC106">
+        <v>1</v>
+      </c>
+      <c r="ID106">
+        <v>1.161424128298219</v>
+      </c>
+      <c r="IE106">
+        <v>0.3009832601809674</v>
+      </c>
+      <c r="IF106" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG106" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -47186,6 +50049,33 @@
       <c r="HZ107">
         <v>18</v>
       </c>
+      <c r="IA107">
+        <v>5</v>
+      </c>
+      <c r="IB107" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="IC107">
+        <v>0</v>
+      </c>
+      <c r="ID107">
+        <v>1.161424128298219</v>
+      </c>
+      <c r="IE107">
+        <v>0.3009832601809674</v>
+      </c>
+      <c r="IF107" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG107" t="inlineStr">
+        <is>
+          <t>compromised</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -47208,7 +50098,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Reef</t>
+          <t>Stone_pile</t>
         </is>
       </c>
       <c r="F108">
@@ -47630,6 +50520,33 @@
       </c>
       <c r="HZ108">
         <v>18</v>
+      </c>
+      <c r="IA108">
+        <v>5</v>
+      </c>
+      <c r="IB108" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="IC108">
+        <v>1</v>
+      </c>
+      <c r="ID108">
+        <v>1.161424128298219</v>
+      </c>
+      <c r="IE108">
+        <v>0.3009832601809674</v>
+      </c>
+      <c r="IF108" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG108" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
       </c>
     </row>
     <row r="109">
@@ -48010,6 +50927,33 @@
       <c r="HZ109">
         <v>18</v>
       </c>
+      <c r="IA109">
+        <v>5</v>
+      </c>
+      <c r="IB109" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="IC109">
+        <v>0</v>
+      </c>
+      <c r="ID109">
+        <v>1.161424128298219</v>
+      </c>
+      <c r="IE109">
+        <v>0.3009832601809674</v>
+      </c>
+      <c r="IF109" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG109" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -48032,7 +50976,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Reef</t>
+          <t>Stone_pile</t>
         </is>
       </c>
       <c r="F110">
@@ -48449,6 +51393,33 @@
       </c>
       <c r="HZ110">
         <v>20.1</v>
+      </c>
+      <c r="IA110">
+        <v>5</v>
+      </c>
+      <c r="IB110" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="IC110">
+        <v>1</v>
+      </c>
+      <c r="ID110">
+        <v>1.161424128298219</v>
+      </c>
+      <c r="IE110">
+        <v>0.3009832601809674</v>
+      </c>
+      <c r="IF110" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG110" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
       </c>
     </row>
     <row r="111">
@@ -48865,6 +51836,33 @@
       <c r="HZ111">
         <v>30</v>
       </c>
+      <c r="IA111">
+        <v>5</v>
+      </c>
+      <c r="IB111" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="IC111">
+        <v>1</v>
+      </c>
+      <c r="ID111">
+        <v>1.161424128298219</v>
+      </c>
+      <c r="IE111">
+        <v>0.3009832601809674</v>
+      </c>
+      <c r="IF111" t="inlineStr">
+        <is>
+          <t>Waxing</t>
+        </is>
+      </c>
+      <c r="IG111" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -49352,6 +52350,33 @@
       <c r="HZ112">
         <v>39.6</v>
       </c>
+      <c r="IA112">
+        <v>5</v>
+      </c>
+      <c r="IB112" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="IC112">
+        <v>1</v>
+      </c>
+      <c r="ID112">
+        <v>0.7358867075269341</v>
+      </c>
+      <c r="IE112">
+        <v>0.1293820764152031</v>
+      </c>
+      <c r="IF112" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG112" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -49809,6 +52834,33 @@
       <c r="HZ113">
         <v>37.2</v>
       </c>
+      <c r="IA113">
+        <v>5</v>
+      </c>
+      <c r="IB113" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="IC113">
+        <v>1</v>
+      </c>
+      <c r="ID113">
+        <v>0.7358867075269341</v>
+      </c>
+      <c r="IE113">
+        <v>0.1293820764152031</v>
+      </c>
+      <c r="IF113" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG113" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -50197,6 +53249,33 @@
       <c r="HZ114">
         <v>21.6</v>
       </c>
+      <c r="IA114">
+        <v>5</v>
+      </c>
+      <c r="IB114" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="IC114">
+        <v>0</v>
+      </c>
+      <c r="ID114">
+        <v>0.7358867075269341</v>
+      </c>
+      <c r="IE114">
+        <v>0.1293820764152031</v>
+      </c>
+      <c r="IF114" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG114" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -50585,6 +53664,33 @@
       <c r="HZ115">
         <v>21</v>
       </c>
+      <c r="IA115">
+        <v>5</v>
+      </c>
+      <c r="IB115" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="IC115">
+        <v>0</v>
+      </c>
+      <c r="ID115">
+        <v>0.7358867075269341</v>
+      </c>
+      <c r="IE115">
+        <v>0.1293820764152031</v>
+      </c>
+      <c r="IF115" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG115" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -51038,6 +54144,33 @@
       <c r="HZ116">
         <v>31.2</v>
       </c>
+      <c r="IA116">
+        <v>5</v>
+      </c>
+      <c r="IB116" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="IC116">
+        <v>1</v>
+      </c>
+      <c r="ID116">
+        <v>0.7358867075269341</v>
+      </c>
+      <c r="IE116">
+        <v>0.1293820764152031</v>
+      </c>
+      <c r="IF116" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG116" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -51486,6 +54619,33 @@
       <c r="HZ117">
         <v>31.2</v>
       </c>
+      <c r="IA117">
+        <v>5</v>
+      </c>
+      <c r="IB117" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="IC117">
+        <v>0</v>
+      </c>
+      <c r="ID117">
+        <v>0.7358867075269341</v>
+      </c>
+      <c r="IE117">
+        <v>0.1293820764152031</v>
+      </c>
+      <c r="IF117" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG117" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -51946,6 +55106,33 @@
       <c r="HZ118">
         <v>30</v>
       </c>
+      <c r="IA118">
+        <v>5</v>
+      </c>
+      <c r="IB118" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="IC118">
+        <v>1</v>
+      </c>
+      <c r="ID118">
+        <v>0.7358867075269341</v>
+      </c>
+      <c r="IE118">
+        <v>0.1293820764152031</v>
+      </c>
+      <c r="IF118" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG118" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -52385,6 +55572,33 @@
       <c r="HZ119">
         <v>37.2</v>
       </c>
+      <c r="IA119">
+        <v>5</v>
+      </c>
+      <c r="IB119" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="IC119">
+        <v>1</v>
+      </c>
+      <c r="ID119">
+        <v>0.7358867075269341</v>
+      </c>
+      <c r="IE119">
+        <v>0.1293820764152031</v>
+      </c>
+      <c r="IF119" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG119" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -52817,6 +56031,33 @@
       <c r="HZ120">
         <v>34.2</v>
       </c>
+      <c r="IA120">
+        <v>5</v>
+      </c>
+      <c r="IB120" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="IC120">
+        <v>1</v>
+      </c>
+      <c r="ID120">
+        <v>0.7358867075269341</v>
+      </c>
+      <c r="IE120">
+        <v>0.1293820764152031</v>
+      </c>
+      <c r="IF120" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG120" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -53239,6 +56480,33 @@
       </c>
       <c r="HZ121">
         <v>34.2</v>
+      </c>
+      <c r="IA121">
+        <v>5</v>
+      </c>
+      <c r="IB121" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="IC121">
+        <v>1</v>
+      </c>
+      <c r="ID121">
+        <v>0.7358867075269341</v>
+      </c>
+      <c r="IE121">
+        <v>0.1293820764152031</v>
+      </c>
+      <c r="IF121" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="IG121" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/derived/Combined_data.xlsx
+++ b/data/derived/Combined_data.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:IG121"/>
+  <dimension ref="A1:IH121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="11" max="11" width="20.7109375" style="2" customWidth="1"/>
@@ -592,7 +592,7 @@
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>Reef_shape.1</t>
+          <t>Shape.1</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>Hight_above.1</t>
+          <t>Height_above.1</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="BG1" s="1" t="inlineStr">
         <is>
-          <t>Reef_shape.2</t>
+          <t>Shape.2</t>
         </is>
       </c>
       <c r="BH1" s="1" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="BO1" s="1" t="inlineStr">
         <is>
-          <t>Hight_above.2</t>
+          <t>Height_above.2</t>
         </is>
       </c>
       <c r="BP1" s="1" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="BT1" s="1" t="inlineStr">
         <is>
-          <t>Reef_shape.3</t>
+          <t>Shape.3</t>
         </is>
       </c>
       <c r="BU1" s="1" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="CB1" s="1" t="inlineStr">
         <is>
-          <t>Hight_above.3</t>
+          <t>Height_above.3</t>
         </is>
       </c>
       <c r="CC1" s="1" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="HZ1" s="1" t="inlineStr">
         <is>
-          <t>Substrate_index</t>
+          <t>Substrate_index_before</t>
         </is>
       </c>
       <c r="IA1" s="1" t="inlineStr">
@@ -1552,20 +1552,25 @@
       </c>
       <c r="ID1" s="1" t="inlineStr">
         <is>
+          <t>Substrate_index_after</t>
+        </is>
+      </c>
+      <c r="IE1" s="1" t="inlineStr">
+        <is>
           <t>lunar_phase</t>
         </is>
       </c>
-      <c r="IE1" s="1" t="inlineStr">
+      <c r="IF1" s="1" t="inlineStr">
         <is>
           <t>lunar_illumination</t>
         </is>
       </c>
-      <c r="IF1" s="1" t="inlineStr">
+      <c r="IG1" s="1" t="inlineStr">
         <is>
           <t>lunar_name</t>
         </is>
       </c>
-      <c r="IG1" s="1" t="inlineStr">
+      <c r="IH1" s="1" t="inlineStr">
         <is>
           <t>monitoring_quality</t>
         </is>
@@ -1613,7 +1618,7 @@
         </is>
       </c>
       <c r="K2" s="2">
-        <v>45692.125</v>
+        <v>45691.58333333333</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -1696,7 +1701,7 @@
         <v>159.5</v>
       </c>
       <c r="AM2">
-        <v>156.2193927522037</v>
+        <v>156.219392752204</v>
       </c>
       <c r="AN2">
         <v>8.119999999999999</v>
@@ -2187,7 +2192,7 @@
         </is>
       </c>
       <c r="HM2" s="3">
-        <v>45692</v>
+        <v>45691</v>
       </c>
       <c r="HN2" t="inlineStr">
         <is>
@@ -2211,7 +2216,7 @@
         </is>
       </c>
       <c r="HS2">
-        <v>1738638000</v>
+        <v>1738591200</v>
       </c>
       <c r="HT2" t="inlineStr">
         <is>
@@ -2225,10 +2230,10 @@
         <v>164.450019734722</v>
       </c>
       <c r="HW2">
-        <v>16.59778041809964</v>
+        <v>0.06024901973697124</v>
       </c>
       <c r="HX2">
-        <v>8.222500986736099</v>
+        <v>0.121617498327227</v>
       </c>
       <c r="HY2" t="inlineStr">
         <is>
@@ -2236,7 +2241,7 @@
         </is>
       </c>
       <c r="HZ2">
-        <v>31.2</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="IA2">
         <v>0</v>
@@ -2250,17 +2255,20 @@
         <v>1</v>
       </c>
       <c r="ID2">
-        <v>1.365433745565868</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="IE2">
-        <v>0.3980389321744662</v>
-      </c>
-      <c r="IF2" t="inlineStr">
+        <v>1.152665035180047</v>
+      </c>
+      <c r="IF2">
+        <v>0.2969732774352599</v>
+      </c>
+      <c r="IG2" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG2" t="inlineStr">
+      <c r="IH2" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -2308,7 +2316,7 @@
         </is>
       </c>
       <c r="K3" s="2">
-        <v>45692.14583333333</v>
+        <v>45691.60416666667</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -2691,7 +2699,7 @@
         </is>
       </c>
       <c r="HM3" s="3">
-        <v>45692</v>
+        <v>45691</v>
       </c>
       <c r="HN3" t="inlineStr">
         <is>
@@ -2715,7 +2723,7 @@
         </is>
       </c>
       <c r="HS3">
-        <v>1738639800</v>
+        <v>1738593000</v>
       </c>
       <c r="HT3" t="inlineStr">
         <is>
@@ -2729,10 +2737,10 @@
         <v>180.302636624781</v>
       </c>
       <c r="HW3">
-        <v>21.0891039081872</v>
+        <v>0.04741785162392701</v>
       </c>
       <c r="HX3">
-        <v>9.015131831239049</v>
+        <v>0.1109246119435348</v>
       </c>
       <c r="HY3" t="inlineStr">
         <is>
@@ -2740,7 +2748,7 @@
         </is>
       </c>
       <c r="HZ3">
-        <v>26.4</v>
+        <v>4.4</v>
       </c>
       <c r="IA3">
         <v>0</v>
@@ -2754,17 +2762,20 @@
         <v>1</v>
       </c>
       <c r="ID3">
-        <v>1.365433745565868</v>
+        <v>4.4</v>
       </c>
       <c r="IE3">
-        <v>0.3980389321744662</v>
-      </c>
-      <c r="IF3" t="inlineStr">
+        <v>1.152665035180047</v>
+      </c>
+      <c r="IF3">
+        <v>0.2969732774352599</v>
+      </c>
+      <c r="IG3" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG3" t="inlineStr">
+      <c r="IH3" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -2812,7 +2823,7 @@
         </is>
       </c>
       <c r="K4" s="2">
-        <v>45692.53472222222</v>
+        <v>45691.99305555555</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -2910,7 +2921,7 @@
         <v>170.8</v>
       </c>
       <c r="AM4">
-        <v>170.0856403106951</v>
+        <v>170.085640310695</v>
       </c>
       <c r="AN4">
         <v>8.82</v>
@@ -3326,7 +3337,7 @@
         </is>
       </c>
       <c r="HM4" s="3">
-        <v>45692</v>
+        <v>45691</v>
       </c>
       <c r="HN4" t="inlineStr">
         <is>
@@ -3350,7 +3361,7 @@
         </is>
       </c>
       <c r="HS4">
-        <v>1738673400</v>
+        <v>1738626600</v>
       </c>
       <c r="HT4" t="inlineStr">
         <is>
@@ -3364,10 +3375,10 @@
         <v>1429.22107248619</v>
       </c>
       <c r="HW4">
-        <v>15.02060854953934</v>
+        <v>0.06657519878118842</v>
       </c>
       <c r="HX4">
-        <v>71.4610536243095</v>
+        <v>0.01399363638349465</v>
       </c>
       <c r="HY4" t="inlineStr">
         <is>
@@ -3375,7 +3386,7 @@
         </is>
       </c>
       <c r="HZ4">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="IA4">
         <v>0</v>
@@ -3389,17 +3400,20 @@
         <v>0</v>
       </c>
       <c r="ID4">
-        <v>1.365433745565868</v>
+        <v>3</v>
       </c>
       <c r="IE4">
-        <v>0.3980389321744662</v>
-      </c>
-      <c r="IF4" t="inlineStr">
+        <v>1.152665035180047</v>
+      </c>
+      <c r="IF4">
+        <v>0.2969732774352599</v>
+      </c>
+      <c r="IG4" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG4" t="inlineStr">
+      <c r="IH4" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -3447,7 +3461,7 @@
         </is>
       </c>
       <c r="K5" s="2">
-        <v>45692.52083333333</v>
+        <v>45691.97916666667</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -3545,7 +3559,7 @@
         <v>170.9</v>
       </c>
       <c r="AM5">
-        <v>168.7734544736323</v>
+        <v>168.773454473632</v>
       </c>
       <c r="AN5">
         <v>8.51</v>
@@ -3766,7 +3780,7 @@
         </is>
       </c>
       <c r="HM5" s="3">
-        <v>45692</v>
+        <v>45691</v>
       </c>
       <c r="HN5" t="inlineStr">
         <is>
@@ -3790,7 +3804,7 @@
         </is>
       </c>
       <c r="HS5">
-        <v>1738672200</v>
+        <v>1738625400</v>
       </c>
       <c r="HT5" t="inlineStr">
         <is>
@@ -3804,10 +3818,10 @@
         <v>1435.7027457702</v>
       </c>
       <c r="HW5">
-        <v>14.62128427785038</v>
+        <v>0.06839344485729539</v>
       </c>
       <c r="HX5">
-        <v>71.78513728851</v>
+        <v>0.01393046022856964</v>
       </c>
       <c r="HY5" t="inlineStr">
         <is>
@@ -3815,7 +3829,7 @@
         </is>
       </c>
       <c r="HZ5">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="IA5">
         <v>0</v>
@@ -3829,17 +3843,20 @@
         <v>0</v>
       </c>
       <c r="ID5">
-        <v>1.365433745565868</v>
+        <v>3</v>
       </c>
       <c r="IE5">
-        <v>0.3980389321744662</v>
-      </c>
-      <c r="IF5" t="inlineStr">
+        <v>1.152665035180047</v>
+      </c>
+      <c r="IF5">
+        <v>0.2969732774352599</v>
+      </c>
+      <c r="IG5" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG5" t="inlineStr">
+      <c r="IH5" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -3887,7 +3904,7 @@
         </is>
       </c>
       <c r="K6" s="2">
-        <v>45692.47916666667</v>
+        <v>45691.9375</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -3975,7 +3992,7 @@
         <v>172</v>
       </c>
       <c r="AM6">
-        <v>174.9389747762409</v>
+        <v>174.938974776241</v>
       </c>
       <c r="AN6">
         <v>8.119999999999999</v>
@@ -4436,7 +4453,7 @@
         </is>
       </c>
       <c r="HM6" s="3">
-        <v>45692</v>
+        <v>45691</v>
       </c>
       <c r="HN6" t="inlineStr">
         <is>
@@ -4460,7 +4477,7 @@
         </is>
       </c>
       <c r="HS6">
-        <v>1738668600</v>
+        <v>1738621800</v>
       </c>
       <c r="HT6" t="inlineStr">
         <is>
@@ -4474,10 +4491,10 @@
         <v>1689.68543182272</v>
       </c>
       <c r="HW6">
-        <v>53.510285413158</v>
+        <v>0.01868799600448596</v>
       </c>
       <c r="HX6">
-        <v>84.48427159113599</v>
+        <v>0.0118365227179744</v>
       </c>
       <c r="HY6" t="inlineStr">
         <is>
@@ -4485,7 +4502,7 @@
         </is>
       </c>
       <c r="HZ6">
-        <v>14.4</v>
+        <v>2.4</v>
       </c>
       <c r="IA6">
         <v>0</v>
@@ -4499,17 +4516,20 @@
         <v>1</v>
       </c>
       <c r="ID6">
-        <v>1.365433745565868</v>
+        <v>2.4</v>
       </c>
       <c r="IE6">
-        <v>0.3980389321744662</v>
-      </c>
-      <c r="IF6" t="inlineStr">
+        <v>1.152665035180047</v>
+      </c>
+      <c r="IF6">
+        <v>0.2969732774352599</v>
+      </c>
+      <c r="IG6" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG6" t="inlineStr">
+      <c r="IH6" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -4557,7 +4577,7 @@
         </is>
       </c>
       <c r="K7" s="2">
-        <v>45692.45833333333</v>
+        <v>45691.91666666667</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -4645,7 +4665,7 @@
         <v>172.1</v>
       </c>
       <c r="AM7">
-        <v>175.4153501172154</v>
+        <v>175.415350117215</v>
       </c>
       <c r="AN7">
         <v>8.109999999999999</v>
@@ -4890,7 +4910,7 @@
         </is>
       </c>
       <c r="HM7" s="3">
-        <v>45692</v>
+        <v>45691</v>
       </c>
       <c r="HN7" t="inlineStr">
         <is>
@@ -4914,7 +4934,7 @@
         </is>
       </c>
       <c r="HS7">
-        <v>1738666800</v>
+        <v>1738620000</v>
       </c>
       <c r="HT7" t="inlineStr">
         <is>
@@ -4928,18 +4948,18 @@
         <v>1741.06263130931</v>
       </c>
       <c r="HW7">
-        <v>44.1049746442002</v>
+        <v>0.022673179342401</v>
       </c>
       <c r="HX7">
-        <v>87.05313156546551</v>
+        <v>0.0114872375297376</v>
       </c>
       <c r="HY7" t="inlineStr">
         <is>
-          <t>Emergent Macrophyte</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="HZ7">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="IA7">
         <v>0</v>
@@ -4953,17 +4973,20 @@
         <v>0</v>
       </c>
       <c r="ID7">
-        <v>1.365433745565868</v>
+        <v>3</v>
       </c>
       <c r="IE7">
-        <v>0.3980389321744662</v>
-      </c>
-      <c r="IF7" t="inlineStr">
+        <v>1.152665035180047</v>
+      </c>
+      <c r="IF7">
+        <v>0.2969732774352599</v>
+      </c>
+      <c r="IG7" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG7" t="inlineStr">
+      <c r="IH7" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -5011,7 +5034,7 @@
         </is>
       </c>
       <c r="K8" s="2">
-        <v>45692.10416666667</v>
+        <v>45691.5625</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -5099,7 +5122,7 @@
         <v>330.6</v>
       </c>
       <c r="AM8">
-        <v>319.8529411764706</v>
+        <v>319.852941176471</v>
       </c>
       <c r="AN8">
         <v>3.69</v>
@@ -5524,7 +5547,7 @@
         </is>
       </c>
       <c r="HM8" s="3">
-        <v>45692</v>
+        <v>45691</v>
       </c>
       <c r="HN8" t="inlineStr">
         <is>
@@ -5548,7 +5571,7 @@
         </is>
       </c>
       <c r="HS8">
-        <v>1738636200</v>
+        <v>1738589400</v>
       </c>
       <c r="HT8" t="inlineStr">
         <is>
@@ -5562,10 +5585,10 @@
         <v>334.104864132139</v>
       </c>
       <c r="HW8">
-        <v>26.1356496959392</v>
+        <v>0.03826191472697057</v>
       </c>
       <c r="HX8">
-        <v>16.70524320660695</v>
+        <v>0.05986144515420753</v>
       </c>
       <c r="HY8" t="inlineStr">
         <is>
@@ -5573,7 +5596,7 @@
         </is>
       </c>
       <c r="HZ8">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="IA8">
         <v>0</v>
@@ -5587,17 +5610,20 @@
         <v>0</v>
       </c>
       <c r="ID8">
-        <v>1.365433745565868</v>
+        <v>3</v>
       </c>
       <c r="IE8">
-        <v>0.3980389321744662</v>
-      </c>
-      <c r="IF8" t="inlineStr">
+        <v>1.152665035180047</v>
+      </c>
+      <c r="IF8">
+        <v>0.2969732774352599</v>
+      </c>
+      <c r="IG8" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG8" t="inlineStr">
+      <c r="IH8" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -5645,7 +5671,7 @@
         </is>
       </c>
       <c r="K9" s="2">
-        <v>45692.08333333333</v>
+        <v>45691.54166666667</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -5733,7 +5759,7 @@
         <v>346</v>
       </c>
       <c r="AM9">
-        <v>339.5819020512317</v>
+        <v>339.581902051232</v>
       </c>
       <c r="AN9">
         <v>3.72</v>
@@ -5996,7 +6022,7 @@
         </is>
       </c>
       <c r="HM9" s="3">
-        <v>45692</v>
+        <v>45691</v>
       </c>
       <c r="HN9" t="inlineStr">
         <is>
@@ -6020,7 +6046,7 @@
         </is>
       </c>
       <c r="HS9">
-        <v>1738634400</v>
+        <v>1738587600</v>
       </c>
       <c r="HT9" t="inlineStr">
         <is>
@@ -6034,10 +6060,10 @@
         <v>381.61439291614</v>
       </c>
       <c r="HW9">
-        <v>13.90163680253436</v>
+        <v>0.07193397541631165</v>
       </c>
       <c r="HX9">
-        <v>19.080719645807</v>
+        <v>0.05240892474512882</v>
       </c>
       <c r="HY9" t="inlineStr">
         <is>
@@ -6045,7 +6071,7 @@
         </is>
       </c>
       <c r="HZ9">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="IA9">
         <v>0</v>
@@ -6059,17 +6085,20 @@
         <v>0</v>
       </c>
       <c r="ID9">
-        <v>1.365433745565868</v>
+        <v>3</v>
       </c>
       <c r="IE9">
-        <v>0.3980389321744662</v>
-      </c>
-      <c r="IF9" t="inlineStr">
+        <v>1.152665035180047</v>
+      </c>
+      <c r="IF9">
+        <v>0.2969732774352599</v>
+      </c>
+      <c r="IG9" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG9" t="inlineStr">
+      <c r="IH9" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -6117,7 +6146,7 @@
         </is>
       </c>
       <c r="K10" s="2">
-        <v>45692.40625</v>
+        <v>45691.86458333333</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -6200,7 +6229,7 @@
         <v>145.3</v>
       </c>
       <c r="AM10">
-        <v>156.1190501772859</v>
+        <v>156.119050177286</v>
       </c>
       <c r="AN10">
         <v>8.74</v>
@@ -6655,7 +6684,7 @@
         </is>
       </c>
       <c r="HM10" s="3">
-        <v>45692</v>
+        <v>45691</v>
       </c>
       <c r="HN10" t="inlineStr">
         <is>
@@ -6679,7 +6708,7 @@
         </is>
       </c>
       <c r="HS10">
-        <v>1738662300</v>
+        <v>1738615500</v>
       </c>
       <c r="HT10" t="inlineStr">
         <is>
@@ -6693,18 +6722,18 @@
         <v>259.826404337621</v>
       </c>
       <c r="HW10">
-        <v>33.667898204025</v>
+        <v>0.02970188379268801</v>
       </c>
       <c r="HX10">
-        <v>12.99132021688105</v>
+        <v>0.07697447090100898</v>
       </c>
       <c r="HY10" t="inlineStr">
         <is>
-          <t>Rocky</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="HZ10">
-        <v>20.1</v>
+        <v>3.35</v>
       </c>
       <c r="IA10">
         <v>0</v>
@@ -6718,17 +6747,20 @@
         <v>0</v>
       </c>
       <c r="ID10">
-        <v>1.365433745565868</v>
+        <v>3.35</v>
       </c>
       <c r="IE10">
-        <v>0.3980389321744662</v>
-      </c>
-      <c r="IF10" t="inlineStr">
+        <v>1.152665035180047</v>
+      </c>
+      <c r="IF10">
+        <v>0.2969732774352599</v>
+      </c>
+      <c r="IG10" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG10" t="inlineStr">
+      <c r="IH10" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -6776,7 +6808,7 @@
         </is>
       </c>
       <c r="K11" s="2">
-        <v>45692.43055555555</v>
+        <v>45691.88888888889</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -6864,7 +6896,7 @@
         <v>150.4</v>
       </c>
       <c r="AM11">
-        <v>158.7335092348285</v>
+        <v>158.733509234828</v>
       </c>
       <c r="AN11">
         <v>8.65</v>
@@ -7124,7 +7156,7 @@
         </is>
       </c>
       <c r="HM11" s="3">
-        <v>45692</v>
+        <v>45691</v>
       </c>
       <c r="HN11" t="inlineStr">
         <is>
@@ -7148,7 +7180,7 @@
         </is>
       </c>
       <c r="HS11">
-        <v>1738664400</v>
+        <v>1738617600</v>
       </c>
       <c r="HT11" t="inlineStr">
         <is>
@@ -7162,10 +7194,10 @@
         <v>221.365381729161</v>
       </c>
       <c r="HW11">
-        <v>27.7244235402752</v>
+        <v>0.03606928016185089</v>
       </c>
       <c r="HX11">
-        <v>11.06826908645805</v>
+        <v>0.09034836361391801</v>
       </c>
       <c r="HY11" t="inlineStr">
         <is>
@@ -7173,7 +7205,7 @@
         </is>
       </c>
       <c r="HZ11">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="IA11">
         <v>0</v>
@@ -7187,17 +7219,20 @@
         <v>1</v>
       </c>
       <c r="ID11">
-        <v>1.365433745565868</v>
+        <v>5</v>
       </c>
       <c r="IE11">
-        <v>0.3980389321744662</v>
-      </c>
-      <c r="IF11" t="inlineStr">
+        <v>1.152665035180047</v>
+      </c>
+      <c r="IF11">
+        <v>0.2969732774352599</v>
+      </c>
+      <c r="IG11" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG11" t="inlineStr">
+      <c r="IH11" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -7245,7 +7280,7 @@
         </is>
       </c>
       <c r="K12" s="2">
-        <v>45694.61527777778</v>
+        <v>45694.07361111111</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -7338,7 +7373,7 @@
         <v>156.9</v>
       </c>
       <c r="AM12">
-        <v>158.9021673080819</v>
+        <v>158.902167308082</v>
       </c>
       <c r="AN12">
         <v>9.18</v>
@@ -7607,7 +7642,7 @@
         </is>
       </c>
       <c r="HS12">
-        <v>1738853160</v>
+        <v>1738806360</v>
       </c>
       <c r="HT12" t="inlineStr">
         <is>
@@ -7621,10 +7656,10 @@
         <v>121.850769016352</v>
       </c>
       <c r="HW12">
-        <v>7.788448912465</v>
+        <v>0.1283952698719706</v>
       </c>
       <c r="HX12">
-        <v>6.0925384508176</v>
+        <v>0.1641351971879313</v>
       </c>
       <c r="HY12" t="inlineStr">
         <is>
@@ -7632,7 +7667,7 @@
         </is>
       </c>
       <c r="HZ12">
-        <v>39.6</v>
+        <v>6.600000000000001</v>
       </c>
       <c r="IA12">
         <v>0</v>
@@ -7646,17 +7681,20 @@
         <v>0</v>
       </c>
       <c r="ID12">
+        <v>6.600000000000001</v>
+      </c>
+      <c r="IE12">
         <v>1.790971166336796</v>
       </c>
-      <c r="IE12">
+      <c r="IF12">
         <v>0.6092001226037329</v>
       </c>
-      <c r="IF12" t="inlineStr">
+      <c r="IG12" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG12" t="inlineStr">
+      <c r="IH12" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -7704,7 +7742,7 @@
         </is>
       </c>
       <c r="K13" s="2">
-        <v>45694.63194444445</v>
+        <v>45694.09027777778</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -7797,7 +7835,7 @@
         <v>161.1</v>
       </c>
       <c r="AM13">
-        <v>159.7580325267751</v>
+        <v>159.758032526775</v>
       </c>
       <c r="AN13">
         <v>9.140000000000001</v>
@@ -8081,7 +8119,7 @@
         </is>
       </c>
       <c r="HS13">
-        <v>1738854600</v>
+        <v>1738807800</v>
       </c>
       <c r="HT13" t="inlineStr">
         <is>
@@ -8095,10 +8133,10 @@
         <v>162.050124796368</v>
       </c>
       <c r="HW13">
-        <v>14.18372682915204</v>
+        <v>0.07050333188486711</v>
       </c>
       <c r="HX13">
-        <v>8.1025062398184</v>
+        <v>0.1234186028868042</v>
       </c>
       <c r="HY13" t="inlineStr">
         <is>
@@ -8106,7 +8144,7 @@
         </is>
       </c>
       <c r="HZ13">
-        <v>37.2</v>
+        <v>6.2</v>
       </c>
       <c r="IA13">
         <v>0</v>
@@ -8120,17 +8158,20 @@
         <v>0</v>
       </c>
       <c r="ID13">
+        <v>6.2</v>
+      </c>
+      <c r="IE13">
         <v>1.790971166336796</v>
       </c>
-      <c r="IE13">
+      <c r="IF13">
         <v>0.6092001226037329</v>
       </c>
-      <c r="IF13" t="inlineStr">
+      <c r="IG13" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG13" t="inlineStr">
+      <c r="IH13" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -8178,7 +8219,7 @@
         </is>
       </c>
       <c r="K14" s="2">
-        <v>45694.46875</v>
+        <v>45693.92708333333</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -8271,7 +8312,7 @@
         <v>177.9</v>
       </c>
       <c r="AM14">
-        <v>180.5541459453973</v>
+        <v>180.554145945397</v>
       </c>
       <c r="AN14">
         <v>7.57</v>
@@ -8465,7 +8506,7 @@
         </is>
       </c>
       <c r="HM14" s="3">
-        <v>45694</v>
+        <v>45693</v>
       </c>
       <c r="HN14" t="inlineStr">
         <is>
@@ -8489,7 +8530,7 @@
         </is>
       </c>
       <c r="HS14">
-        <v>1738840500</v>
+        <v>1738793700</v>
       </c>
       <c r="HT14" t="inlineStr">
         <is>
@@ -8503,18 +8544,18 @@
         <v>218.544411001867</v>
       </c>
       <c r="HW14">
-        <v>12.66700316387234</v>
+        <v>0.07894527119501382</v>
       </c>
       <c r="HX14">
-        <v>10.92722055009335</v>
+        <v>0.09151458007237322</v>
       </c>
       <c r="HY14" t="inlineStr">
         <is>
-          <t>Rocky</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="HZ14">
-        <v>21.6</v>
+        <v>3.6</v>
       </c>
       <c r="IA14">
         <v>0</v>
@@ -8528,17 +8569,20 @@
         <v>0</v>
       </c>
       <c r="ID14">
-        <v>1.790971166336796</v>
+        <v>3.6</v>
       </c>
       <c r="IE14">
-        <v>0.6092001226037329</v>
-      </c>
-      <c r="IF14" t="inlineStr">
+        <v>1.578202455951332</v>
+      </c>
+      <c r="IF14">
+        <v>0.5037030307256661</v>
+      </c>
+      <c r="IG14" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG14" t="inlineStr">
+      <c r="IH14" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -8586,7 +8630,7 @@
         </is>
       </c>
       <c r="K15" s="2">
-        <v>45694.45833333333</v>
+        <v>45693.91666666667</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -8679,7 +8723,7 @@
         <v>177.9</v>
       </c>
       <c r="AM15">
-        <v>180.5541459453973</v>
+        <v>180.554145945397</v>
       </c>
       <c r="AN15">
         <v>7.52</v>
@@ -8888,7 +8932,7 @@
         </is>
       </c>
       <c r="HM15" s="3">
-        <v>45694</v>
+        <v>45693</v>
       </c>
       <c r="HN15" t="inlineStr">
         <is>
@@ -8912,7 +8956,7 @@
         </is>
       </c>
       <c r="HS15">
-        <v>1738839600</v>
+        <v>1738792800</v>
       </c>
       <c r="HT15" t="inlineStr">
         <is>
@@ -8926,18 +8970,18 @@
         <v>183.129609879407</v>
       </c>
       <c r="HW15">
-        <v>11.9760957338734</v>
+        <v>0.08349966652083303</v>
       </c>
       <c r="HX15">
-        <v>9.156480493970351</v>
+        <v>0.1092122678204264</v>
       </c>
       <c r="HY15" t="inlineStr">
         <is>
-          <t>Rocky</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="HZ15">
-        <v>21</v>
+        <v>3.5</v>
       </c>
       <c r="IA15">
         <v>0</v>
@@ -8951,17 +8995,20 @@
         <v>1</v>
       </c>
       <c r="ID15">
-        <v>1.790971166336796</v>
+        <v>3.5</v>
       </c>
       <c r="IE15">
-        <v>0.6092001226037329</v>
-      </c>
-      <c r="IF15" t="inlineStr">
+        <v>1.578202455951332</v>
+      </c>
+      <c r="IF15">
+        <v>0.5037030307256661</v>
+      </c>
+      <c r="IG15" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG15" t="inlineStr">
+      <c r="IH15" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -9009,7 +9056,7 @@
         </is>
       </c>
       <c r="K16" s="2">
-        <v>45694.41666666667</v>
+        <v>45693.875</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -9107,7 +9154,7 @@
         <v>160.9</v>
       </c>
       <c r="AM16">
-        <v>167.2209519850343</v>
+        <v>167.220951985034</v>
       </c>
       <c r="AN16">
         <v>8.23</v>
@@ -9388,7 +9435,7 @@
         </is>
       </c>
       <c r="HM16" s="3">
-        <v>45694</v>
+        <v>45693</v>
       </c>
       <c r="HN16" t="inlineStr">
         <is>
@@ -9412,7 +9459,7 @@
         </is>
       </c>
       <c r="HS16">
-        <v>1738836000</v>
+        <v>1738789200</v>
       </c>
       <c r="HT16" t="inlineStr">
         <is>
@@ -9426,10 +9473,10 @@
         <v>639.033952746429</v>
       </c>
       <c r="HW16">
-        <v>11.58822586362554</v>
+        <v>0.08629448647000533</v>
       </c>
       <c r="HX16">
-        <v>31.95169763732145</v>
+        <v>0.03129724158480836</v>
       </c>
       <c r="HY16" t="inlineStr">
         <is>
@@ -9437,7 +9484,7 @@
         </is>
       </c>
       <c r="HZ16">
-        <v>31.2</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="IA16">
         <v>0</v>
@@ -9451,17 +9498,20 @@
         <v>1</v>
       </c>
       <c r="ID16">
-        <v>1.790971166336796</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="IE16">
-        <v>0.6092001226037329</v>
-      </c>
-      <c r="IF16" t="inlineStr">
+        <v>1.578202455951332</v>
+      </c>
+      <c r="IF16">
+        <v>0.5037030307256661</v>
+      </c>
+      <c r="IG16" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG16" t="inlineStr">
+      <c r="IH16" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -9509,7 +9559,7 @@
         </is>
       </c>
       <c r="K17" s="2">
-        <v>45694.42708333333</v>
+        <v>45693.88541666667</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -9602,7 +9652,7 @@
         <v>160.5</v>
       </c>
       <c r="AM17">
-        <v>166.0802980132451</v>
+        <v>166.080298013245</v>
       </c>
       <c r="AN17">
         <v>8.1</v>
@@ -9862,7 +9912,7 @@
         </is>
       </c>
       <c r="HM17" s="3">
-        <v>45694</v>
+        <v>45693</v>
       </c>
       <c r="HN17" t="inlineStr">
         <is>
@@ -9886,7 +9936,7 @@
         </is>
       </c>
       <c r="HS17">
-        <v>1738836900</v>
+        <v>1738790100</v>
       </c>
       <c r="HT17" t="inlineStr">
         <is>
@@ -9900,10 +9950,10 @@
         <v>565.618637286375</v>
       </c>
       <c r="HW17">
-        <v>5.517255633815</v>
+        <v>0.1812495317184593</v>
       </c>
       <c r="HX17">
-        <v>28.28093186431875</v>
+        <v>0.03535951378114494</v>
       </c>
       <c r="HY17" t="inlineStr">
         <is>
@@ -9911,7 +9961,7 @@
         </is>
       </c>
       <c r="HZ17">
-        <v>31.2</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="IA17">
         <v>0</v>
@@ -9925,17 +9975,20 @@
         <v>1</v>
       </c>
       <c r="ID17">
-        <v>1.790971166336796</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="IE17">
-        <v>0.6092001226037329</v>
-      </c>
-      <c r="IF17" t="inlineStr">
+        <v>1.578202455951332</v>
+      </c>
+      <c r="IF17">
+        <v>0.5037030307256661</v>
+      </c>
+      <c r="IG17" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG17" t="inlineStr">
+      <c r="IH17" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -9983,7 +10036,7 @@
         </is>
       </c>
       <c r="K18" s="2">
-        <v>45694.54791666666</v>
+        <v>45694.00625</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -10076,7 +10129,7 @@
         <v>159.8</v>
       </c>
       <c r="AM18">
-        <v>158.7995627546457</v>
+        <v>158.799562754646</v>
       </c>
       <c r="AN18">
         <v>8.52</v>
@@ -10354,7 +10407,7 @@
         </is>
       </c>
       <c r="HS18">
-        <v>1738847340</v>
+        <v>1738800540</v>
       </c>
       <c r="HT18" t="inlineStr">
         <is>
@@ -10368,10 +10421,10 @@
         <v>411.557104130868</v>
       </c>
       <c r="HW18">
-        <v>2.78311960706048</v>
+        <v>0.3593090277051356</v>
       </c>
       <c r="HX18">
-        <v>20.5778552065434</v>
+        <v>0.04859592945731377</v>
       </c>
       <c r="HY18" t="inlineStr">
         <is>
@@ -10379,7 +10432,7 @@
         </is>
       </c>
       <c r="HZ18">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="IA18">
         <v>0</v>
@@ -10393,17 +10446,20 @@
         <v>1</v>
       </c>
       <c r="ID18">
+        <v>5</v>
+      </c>
+      <c r="IE18">
         <v>1.790971166336796</v>
       </c>
-      <c r="IE18">
+      <c r="IF18">
         <v>0.6092001226037329</v>
       </c>
-      <c r="IF18" t="inlineStr">
+      <c r="IG18" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG18" t="inlineStr">
+      <c r="IH18" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -10451,7 +10507,7 @@
         </is>
       </c>
       <c r="K19" s="2">
-        <v>45694.5625</v>
+        <v>45694.02083333333</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -10544,7 +10600,7 @@
         <v>161.2</v>
       </c>
       <c r="AM19">
-        <v>159.8571995239984</v>
+        <v>159.857199523998</v>
       </c>
       <c r="AN19">
         <v>8.67</v>
@@ -10834,7 +10890,7 @@
         </is>
       </c>
       <c r="HS19">
-        <v>1738848600</v>
+        <v>1738801800</v>
       </c>
       <c r="HT19" t="inlineStr">
         <is>
@@ -10848,10 +10904,10 @@
         <v>393.995431341253</v>
       </c>
       <c r="HW19">
-        <v>2.05165630733588</v>
+        <v>0.4874110719346174</v>
       </c>
       <c r="HX19">
-        <v>19.69977156706265</v>
+        <v>0.05076200993477336</v>
       </c>
       <c r="HY19" t="inlineStr">
         <is>
@@ -10859,7 +10915,7 @@
         </is>
       </c>
       <c r="HZ19">
-        <v>37.2</v>
+        <v>6.2</v>
       </c>
       <c r="IA19">
         <v>0</v>
@@ -10873,17 +10929,20 @@
         <v>1</v>
       </c>
       <c r="ID19">
+        <v>6.2</v>
+      </c>
+      <c r="IE19">
         <v>1.790971166336796</v>
       </c>
-      <c r="IE19">
+      <c r="IF19">
         <v>0.6092001226037329</v>
       </c>
-      <c r="IF19" t="inlineStr">
+      <c r="IG19" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG19" t="inlineStr">
+      <c r="IH19" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -10931,7 +10990,7 @@
         </is>
       </c>
       <c r="K20" s="2">
-        <v>45694.63888888889</v>
+        <v>45694.09722222222</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -11029,7 +11088,7 @@
         <v>160.5</v>
       </c>
       <c r="AM20">
-        <v>163.2424735557364</v>
+        <v>163.242473555736</v>
       </c>
       <c r="AN20">
         <v>9.34</v>
@@ -11319,7 +11378,7 @@
         </is>
       </c>
       <c r="HS20">
-        <v>1738855200</v>
+        <v>1738808400</v>
       </c>
       <c r="HT20" t="inlineStr">
         <is>
@@ -11333,10 +11392,10 @@
         <v>187.90193049333</v>
       </c>
       <c r="HW20">
-        <v>28.5391286313226</v>
+        <v>0.03503961220814809</v>
       </c>
       <c r="HX20">
-        <v>9.395096524666501</v>
+        <v>0.1064385019754225</v>
       </c>
       <c r="HY20" t="inlineStr">
         <is>
@@ -11344,7 +11403,7 @@
         </is>
       </c>
       <c r="HZ20">
-        <v>34.2</v>
+        <v>5.699999999999999</v>
       </c>
       <c r="IA20">
         <v>0</v>
@@ -11358,17 +11417,20 @@
         <v>1</v>
       </c>
       <c r="ID20">
+        <v>5.699999999999999</v>
+      </c>
+      <c r="IE20">
         <v>1.790971166336796</v>
       </c>
-      <c r="IE20">
+      <c r="IF20">
         <v>0.6092001226037329</v>
       </c>
-      <c r="IF20" t="inlineStr">
+      <c r="IG20" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG20" t="inlineStr">
+      <c r="IH20" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -11416,7 +11478,7 @@
         </is>
       </c>
       <c r="K21" s="2">
-        <v>45694.65277777778</v>
+        <v>45694.11111111111</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -11514,7 +11576,7 @@
         <v>159.2</v>
       </c>
       <c r="AM21">
-        <v>159.5350235494539</v>
+        <v>159.535023549454</v>
       </c>
       <c r="AN21">
         <v>9.07</v>
@@ -11819,7 +11881,7 @@
         </is>
       </c>
       <c r="HS21">
-        <v>1738856400</v>
+        <v>1738809600</v>
       </c>
       <c r="HT21" t="inlineStr">
         <is>
@@ -11833,10 +11895,10 @@
         <v>153.52894194799</v>
       </c>
       <c r="HW21">
-        <v>22.5304101069624</v>
+        <v>0.04438445617512207</v>
       </c>
       <c r="HX21">
-        <v>7.6764470973995</v>
+        <v>0.1302685978698093</v>
       </c>
       <c r="HY21" t="inlineStr">
         <is>
@@ -11844,7 +11906,7 @@
         </is>
       </c>
       <c r="HZ21">
-        <v>34.2</v>
+        <v>5.699999999999999</v>
       </c>
       <c r="IA21">
         <v>0</v>
@@ -11858,17 +11920,20 @@
         <v>1</v>
       </c>
       <c r="ID21">
+        <v>5.699999999999999</v>
+      </c>
+      <c r="IE21">
         <v>1.790971166336796</v>
       </c>
-      <c r="IE21">
+      <c r="IF21">
         <v>0.6092001226037329</v>
       </c>
-      <c r="IF21" t="inlineStr">
+      <c r="IG21" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG21" t="inlineStr">
+      <c r="IH21" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -11916,7 +11981,7 @@
         </is>
       </c>
       <c r="K22" s="2">
-        <v>45775.54166666667</v>
+        <v>45775.04166666667</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -11999,7 +12064,7 @@
         <v>129</v>
       </c>
       <c r="AM22">
-        <v>151.6041838053825</v>
+        <v>151.604183805383</v>
       </c>
       <c r="AN22">
         <v>7.42</v>
@@ -12289,7 +12354,7 @@
         </is>
       </c>
       <c r="HS22">
-        <v>1745845200</v>
+        <v>1745802000</v>
       </c>
       <c r="HT22" t="inlineStr">
         <is>
@@ -12303,10 +12368,10 @@
         <v>164.450019734722</v>
       </c>
       <c r="HW22">
-        <v>16.59778041809964</v>
+        <v>0.06024901973697124</v>
       </c>
       <c r="HX22">
-        <v>8.222500986736099</v>
+        <v>0.121617498327227</v>
       </c>
       <c r="HY22" t="inlineStr">
         <is>
@@ -12314,7 +12379,7 @@
         </is>
       </c>
       <c r="HZ22">
-        <v>31.2</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="IA22">
         <v>1</v>
@@ -12328,17 +12393,20 @@
         <v>1</v>
       </c>
       <c r="ID22">
+        <v>5.557973333333334</v>
+      </c>
+      <c r="IE22">
         <v>0.1756807860302614</v>
       </c>
-      <c r="IE22">
+      <c r="IF22">
         <v>0.007696109834573639</v>
       </c>
-      <c r="IF22" t="inlineStr">
+      <c r="IG22" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG22" t="inlineStr">
+      <c r="IH22" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -12386,7 +12454,7 @@
         </is>
       </c>
       <c r="K23" s="2">
-        <v>45775.52083333333</v>
+        <v>45775.02083333333</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -12474,7 +12542,7 @@
         <v>128.5</v>
       </c>
       <c r="AM23">
-        <v>152.1430262846318</v>
+        <v>152.143026284632</v>
       </c>
       <c r="AN23">
         <v>7.36</v>
@@ -12752,7 +12820,7 @@
         </is>
       </c>
       <c r="HS23">
-        <v>1745843400</v>
+        <v>1745800200</v>
       </c>
       <c r="HT23" t="inlineStr">
         <is>
@@ -12766,10 +12834,10 @@
         <v>180.302636624781</v>
       </c>
       <c r="HW23">
-        <v>21.0891039081872</v>
+        <v>0.04741785162392701</v>
       </c>
       <c r="HX23">
-        <v>9.015131831239049</v>
+        <v>0.1109246119435348</v>
       </c>
       <c r="HY23" t="inlineStr">
         <is>
@@ -12777,7 +12845,7 @@
         </is>
       </c>
       <c r="HZ23">
-        <v>26.4</v>
+        <v>4.4</v>
       </c>
       <c r="IA23">
         <v>1</v>
@@ -12791,17 +12859,20 @@
         <v>1</v>
       </c>
       <c r="ID23">
+        <v>4.4</v>
+      </c>
+      <c r="IE23">
         <v>0.1756807860302614</v>
       </c>
-      <c r="IE23">
+      <c r="IF23">
         <v>0.007696109834573639</v>
       </c>
-      <c r="IF23" t="inlineStr">
+      <c r="IG23" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG23" t="inlineStr">
+      <c r="IH23" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -12849,7 +12920,7 @@
         </is>
       </c>
       <c r="K24" s="2">
-        <v>45775.45138888889</v>
+        <v>45774.95138888889</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -12942,7 +13013,7 @@
         <v>142</v>
       </c>
       <c r="AM24">
-        <v>166.8821248090257</v>
+        <v>166.882124809026</v>
       </c>
       <c r="AN24">
         <v>7.49</v>
@@ -13151,7 +13222,7 @@
         </is>
       </c>
       <c r="HM24" s="3">
-        <v>45775</v>
+        <v>45774</v>
       </c>
       <c r="HN24" t="inlineStr">
         <is>
@@ -13175,7 +13246,7 @@
         </is>
       </c>
       <c r="HS24">
-        <v>1745837400</v>
+        <v>1745794200</v>
       </c>
       <c r="HT24" t="inlineStr">
         <is>
@@ -13189,10 +13260,10 @@
         <v>1429.22107248619</v>
       </c>
       <c r="HW24">
-        <v>15.02060854953934</v>
+        <v>0.06657519878118842</v>
       </c>
       <c r="HX24">
-        <v>71.4610536243095</v>
+        <v>0.01399363638349465</v>
       </c>
       <c r="HY24" t="inlineStr">
         <is>
@@ -13200,7 +13271,7 @@
         </is>
       </c>
       <c r="HZ24">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="IA24">
         <v>1</v>
@@ -13214,17 +13285,20 @@
         <v>0</v>
       </c>
       <c r="ID24">
-        <v>0.1756807860302614</v>
+        <v>3.22144</v>
       </c>
       <c r="IE24">
-        <v>0.007696109834573639</v>
-      </c>
-      <c r="IF24" t="inlineStr">
+        <v>6.246097382824026</v>
+      </c>
+      <c r="IF24">
+        <v>0.00034383911757635</v>
+      </c>
+      <c r="IG24" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG24" t="inlineStr">
+      <c r="IH24" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -13272,7 +13346,7 @@
         </is>
       </c>
       <c r="K25" s="2">
-        <v>45775.4375</v>
+        <v>45774.9375</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -13610,7 +13684,7 @@
         </is>
       </c>
       <c r="HM25" s="3">
-        <v>45775</v>
+        <v>45774</v>
       </c>
       <c r="HN25" t="inlineStr">
         <is>
@@ -13634,7 +13708,7 @@
         </is>
       </c>
       <c r="HS25">
-        <v>1745836200</v>
+        <v>1745793000</v>
       </c>
       <c r="HT25" t="inlineStr">
         <is>
@@ -13648,10 +13722,10 @@
         <v>1435.7027457702</v>
       </c>
       <c r="HW25">
-        <v>14.62128427785038</v>
+        <v>0.06839344485729539</v>
       </c>
       <c r="HX25">
-        <v>71.78513728851</v>
+        <v>0.01393046022856964</v>
       </c>
       <c r="HY25" t="inlineStr">
         <is>
@@ -13659,7 +13733,7 @@
         </is>
       </c>
       <c r="HZ25">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="IA25">
         <v>1</v>
@@ -13673,17 +13747,20 @@
         <v>1</v>
       </c>
       <c r="ID25">
-        <v>0.1756807860302614</v>
+        <v>3</v>
       </c>
       <c r="IE25">
-        <v>0.007696109834573639</v>
-      </c>
-      <c r="IF25" t="inlineStr">
+        <v>6.246097382824026</v>
+      </c>
+      <c r="IF25">
+        <v>0.00034383911757635</v>
+      </c>
+      <c r="IG25" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG25" t="inlineStr">
+      <c r="IH25" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -13731,7 +13808,7 @@
         </is>
       </c>
       <c r="K26" s="2">
-        <v>45775.375</v>
+        <v>45774.875</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -13819,7 +13896,7 @@
         <v>139</v>
       </c>
       <c r="AM26">
-        <v>167.4900590432582</v>
+        <v>167.490059043258</v>
       </c>
       <c r="AN26">
         <v>6.82</v>
@@ -14064,7 +14141,7 @@
         </is>
       </c>
       <c r="HM26" s="3">
-        <v>45775</v>
+        <v>45774</v>
       </c>
       <c r="HN26" t="inlineStr">
         <is>
@@ -14088,7 +14165,7 @@
         </is>
       </c>
       <c r="HS26">
-        <v>1745830800</v>
+        <v>1745787600</v>
       </c>
       <c r="HT26" t="inlineStr">
         <is>
@@ -14102,10 +14179,10 @@
         <v>1689.68543182272</v>
       </c>
       <c r="HW26">
-        <v>53.510285413158</v>
+        <v>0.01868799600448596</v>
       </c>
       <c r="HX26">
-        <v>84.48427159113599</v>
+        <v>0.0118365227179744</v>
       </c>
       <c r="HY26" t="inlineStr">
         <is>
@@ -14113,7 +14190,7 @@
         </is>
       </c>
       <c r="HZ26">
-        <v>14.4</v>
+        <v>2.4</v>
       </c>
       <c r="IA26">
         <v>1</v>
@@ -14127,17 +14204,20 @@
         <v>1</v>
       </c>
       <c r="ID26">
-        <v>0.1756807860302614</v>
+        <v>2.66496</v>
       </c>
       <c r="IE26">
-        <v>0.007696109834573639</v>
-      </c>
-      <c r="IF26" t="inlineStr">
+        <v>6.246097382824026</v>
+      </c>
+      <c r="IF26">
+        <v>0.00034383911757635</v>
+      </c>
+      <c r="IG26" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG26" t="inlineStr">
+      <c r="IH26" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -14185,7 +14265,7 @@
         </is>
       </c>
       <c r="K27" s="2">
-        <v>45775.35416666667</v>
+        <v>45774.85416666667</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -14278,7 +14358,7 @@
         <v>36.6</v>
       </c>
       <c r="AM27">
-        <v>45.24663122759303</v>
+        <v>45.246631227593</v>
       </c>
       <c r="AN27">
         <v>6.5</v>
@@ -14544,7 +14624,7 @@
         </is>
       </c>
       <c r="HM27" s="3">
-        <v>45775</v>
+        <v>45774</v>
       </c>
       <c r="HN27" t="inlineStr">
         <is>
@@ -14568,7 +14648,7 @@
         </is>
       </c>
       <c r="HS27">
-        <v>1745829000</v>
+        <v>1745785800</v>
       </c>
       <c r="HT27" t="inlineStr">
         <is>
@@ -14582,18 +14662,18 @@
         <v>1741.06263130931</v>
       </c>
       <c r="HW27">
-        <v>44.1049746442002</v>
+        <v>0.022673179342401</v>
       </c>
       <c r="HX27">
-        <v>87.05313156546551</v>
+        <v>0.0114872375297376</v>
       </c>
       <c r="HY27" t="inlineStr">
         <is>
-          <t>Emergent Macrophyte</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="HZ27">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="IA27">
         <v>1</v>
@@ -14607,17 +14687,20 @@
         <v>1</v>
       </c>
       <c r="ID27">
-        <v>0.1756807860302614</v>
+        <v>3</v>
       </c>
       <c r="IE27">
-        <v>0.007696109834573639</v>
-      </c>
-      <c r="IF27" t="inlineStr">
+        <v>6.246097382824026</v>
+      </c>
+      <c r="IF27">
+        <v>0.00034383911757635</v>
+      </c>
+      <c r="IG27" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG27" t="inlineStr">
+      <c r="IH27" t="inlineStr">
         <is>
           <t>compromised</t>
         </is>
@@ -14665,7 +14748,7 @@
         </is>
       </c>
       <c r="K28" s="2">
-        <v>45775.48888888889</v>
+        <v>45774.98888888889</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -14753,7 +14836,7 @@
         <v>139.2</v>
       </c>
       <c r="AM28">
-        <v>163.5914913620872</v>
+        <v>163.591491362087</v>
       </c>
       <c r="AN28">
         <v>7.38</v>
@@ -15028,7 +15111,7 @@
         </is>
       </c>
       <c r="HM28" s="3">
-        <v>45775</v>
+        <v>45774</v>
       </c>
       <c r="HN28" t="inlineStr">
         <is>
@@ -15052,7 +15135,7 @@
         </is>
       </c>
       <c r="HS28">
-        <v>1745840640</v>
+        <v>1745797440</v>
       </c>
       <c r="HT28" t="inlineStr">
         <is>
@@ -15066,10 +15149,10 @@
         <v>334.104864132139</v>
       </c>
       <c r="HW28">
-        <v>26.1356496959392</v>
+        <v>0.03826191472697057</v>
       </c>
       <c r="HX28">
-        <v>16.70524320660695</v>
+        <v>0.05986144515420753</v>
       </c>
       <c r="HY28" t="inlineStr">
         <is>
@@ -15077,7 +15160,7 @@
         </is>
       </c>
       <c r="HZ28">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="IA28">
         <v>1</v>
@@ -15091,17 +15174,20 @@
         <v>1</v>
       </c>
       <c r="ID28">
-        <v>0.1756807860302614</v>
+        <v>3.203733333333333</v>
       </c>
       <c r="IE28">
-        <v>0.007696109834573639</v>
-      </c>
-      <c r="IF28" t="inlineStr">
+        <v>6.246097382824026</v>
+      </c>
+      <c r="IF28">
+        <v>0.00034383911757635</v>
+      </c>
+      <c r="IG28" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG28" t="inlineStr">
+      <c r="IH28" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -15149,7 +15235,7 @@
         </is>
       </c>
       <c r="K29" s="2">
-        <v>45775.47916666667</v>
+        <v>45774.97916666667</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -15242,7 +15328,7 @@
         <v>138.9</v>
       </c>
       <c r="AM29">
-        <v>163.2389234927724</v>
+        <v>163.238923492772</v>
       </c>
       <c r="AN29">
         <v>7.45</v>
@@ -15457,7 +15543,7 @@
         </is>
       </c>
       <c r="HM29" s="3">
-        <v>45775</v>
+        <v>45774</v>
       </c>
       <c r="HN29" t="inlineStr">
         <is>
@@ -15481,7 +15567,7 @@
         </is>
       </c>
       <c r="HS29">
-        <v>1745839800</v>
+        <v>1745796600</v>
       </c>
       <c r="HT29" t="inlineStr">
         <is>
@@ -15495,10 +15581,10 @@
         <v>381.61439291614</v>
       </c>
       <c r="HW29">
-        <v>13.90163680253436</v>
+        <v>0.07193397541631165</v>
       </c>
       <c r="HX29">
-        <v>19.080719645807</v>
+        <v>0.05240892474512882</v>
       </c>
       <c r="HY29" t="inlineStr">
         <is>
@@ -15506,7 +15592,7 @@
         </is>
       </c>
       <c r="HZ29">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="IA29">
         <v>1</v>
@@ -15520,17 +15606,20 @@
         <v>0</v>
       </c>
       <c r="ID29">
-        <v>0.1756807860302614</v>
+        <v>3</v>
       </c>
       <c r="IE29">
-        <v>0.007696109834573639</v>
-      </c>
-      <c r="IF29" t="inlineStr">
+        <v>6.246097382824026</v>
+      </c>
+      <c r="IF29">
+        <v>0.00034383911757635</v>
+      </c>
+      <c r="IG29" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG29" t="inlineStr">
+      <c r="IH29" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -15578,7 +15667,7 @@
         </is>
       </c>
       <c r="K30" s="2">
-        <v>45775.39583333333</v>
+        <v>45774.89583333333</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -15906,7 +15995,7 @@
         </is>
       </c>
       <c r="HM30" s="3">
-        <v>45775</v>
+        <v>45774</v>
       </c>
       <c r="HN30" t="inlineStr">
         <is>
@@ -15930,7 +16019,7 @@
         </is>
       </c>
       <c r="HS30">
-        <v>1745832600</v>
+        <v>1745789400</v>
       </c>
       <c r="HT30" t="inlineStr">
         <is>
@@ -15944,18 +16033,18 @@
         <v>259.826404337621</v>
       </c>
       <c r="HW30">
-        <v>33.667898204025</v>
+        <v>0.02970188379268801</v>
       </c>
       <c r="HX30">
-        <v>12.99132021688105</v>
+        <v>0.07697447090100898</v>
       </c>
       <c r="HY30" t="inlineStr">
         <is>
-          <t>Rocky</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="HZ30">
-        <v>20.1</v>
+        <v>3.35</v>
       </c>
       <c r="IA30">
         <v>1</v>
@@ -15969,17 +16058,20 @@
         <v>1</v>
       </c>
       <c r="ID30">
-        <v>0.1756807860302614</v>
+        <v>3.613893333333333</v>
       </c>
       <c r="IE30">
-        <v>0.007696109834573639</v>
-      </c>
-      <c r="IF30" t="inlineStr">
+        <v>6.246097382824026</v>
+      </c>
+      <c r="IF30">
+        <v>0.00034383911757635</v>
+      </c>
+      <c r="IG30" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG30" t="inlineStr">
+      <c r="IH30" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -16027,7 +16119,7 @@
         </is>
       </c>
       <c r="K31" s="2">
-        <v>45775.40625</v>
+        <v>45774.90625</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -16115,7 +16207,7 @@
         <v>133.4</v>
       </c>
       <c r="AM31">
-        <v>156.7751792220002</v>
+        <v>156.775179222</v>
       </c>
       <c r="AN31">
         <v>7.46</v>
@@ -16390,7 +16482,7 @@
         </is>
       </c>
       <c r="HM31" s="3">
-        <v>45775</v>
+        <v>45774</v>
       </c>
       <c r="HN31" t="inlineStr">
         <is>
@@ -16414,7 +16506,7 @@
         </is>
       </c>
       <c r="HS31">
-        <v>1745833500</v>
+        <v>1745790300</v>
       </c>
       <c r="HT31" t="inlineStr">
         <is>
@@ -16428,10 +16520,10 @@
         <v>221.365381729161</v>
       </c>
       <c r="HW31">
-        <v>27.7244235402752</v>
+        <v>0.03606928016185089</v>
       </c>
       <c r="HX31">
-        <v>11.06826908645805</v>
+        <v>0.09034836361391801</v>
       </c>
       <c r="HY31" t="inlineStr">
         <is>
@@ -16439,7 +16531,7 @@
         </is>
       </c>
       <c r="HZ31">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="IA31">
         <v>1</v>
@@ -16453,17 +16545,20 @@
         <v>1</v>
       </c>
       <c r="ID31">
-        <v>0.1756807860302614</v>
+        <v>5</v>
       </c>
       <c r="IE31">
-        <v>0.007696109834573639</v>
-      </c>
-      <c r="IF31" t="inlineStr">
+        <v>6.246097382824026</v>
+      </c>
+      <c r="IF31">
+        <v>0.00034383911757635</v>
+      </c>
+      <c r="IG31" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG31" t="inlineStr">
+      <c r="IH31" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -16511,7 +16606,7 @@
         </is>
       </c>
       <c r="K32" s="2">
-        <v>45777.67847222222</v>
+        <v>45777.17847222222</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -16674,10 +16769,10 @@
         <v>12.25</v>
       </c>
       <c r="CZ32">
-        <v>683.3333333333333</v>
+        <v>683.3333333333326</v>
       </c>
       <c r="DA32">
-        <v>683.3333333333333</v>
+        <v>683.3333333333326</v>
       </c>
       <c r="DB32">
         <v>0</v>
@@ -16686,7 +16781,7 @@
         <v>0</v>
       </c>
       <c r="DD32">
-        <v>683.3333333333333</v>
+        <v>683.3333333333326</v>
       </c>
       <c r="DE32">
         <v>0</v>
@@ -16701,13 +16796,13 @@
         <v>49</v>
       </c>
       <c r="DI32">
-        <v>2733.333333333333</v>
+        <v>2733.33333333333</v>
       </c>
       <c r="DJ32">
-        <v>2733.333333333333</v>
+        <v>2733.33333333333</v>
       </c>
       <c r="DM32">
-        <v>2733.333333333333</v>
+        <v>2733.33333333333</v>
       </c>
       <c r="DQ32">
         <v>23.75</v>
@@ -16716,13 +16811,13 @@
         <v>12.25</v>
       </c>
       <c r="EA32">
-        <v>1366.666666666667</v>
+        <v>1366.666666666665</v>
       </c>
       <c r="EB32">
-        <v>1366.666666666667</v>
+        <v>1366.666666666665</v>
       </c>
       <c r="EE32">
-        <v>1366.666666666667</v>
+        <v>1366.666666666665</v>
       </c>
       <c r="EI32">
         <v>4</v>
@@ -16740,13 +16835,13 @@
         <v>49</v>
       </c>
       <c r="ES32">
-        <v>2733.333333333333</v>
+        <v>2733.33333333333</v>
       </c>
       <c r="ET32">
-        <v>2733.333333333333</v>
+        <v>2733.33333333333</v>
       </c>
       <c r="EW32">
-        <v>2733.333333333333</v>
+        <v>2733.33333333333</v>
       </c>
       <c r="FA32">
         <v>4</v>
@@ -16782,13 +16877,13 @@
         <v>29</v>
       </c>
       <c r="GL32">
-        <v>2033.333333333333</v>
+        <v>2033.33333333333</v>
       </c>
       <c r="GM32">
-        <v>2033.333333333333</v>
+        <v>2033.33333333333</v>
       </c>
       <c r="GP32">
-        <v>2033.333333333333</v>
+        <v>2033.33333333333</v>
       </c>
       <c r="GT32">
         <v>3</v>
@@ -16859,7 +16954,7 @@
         </is>
       </c>
       <c r="HS32">
-        <v>1746029820</v>
+        <v>1745986620</v>
       </c>
       <c r="HT32" t="inlineStr">
         <is>
@@ -16873,10 +16968,10 @@
         <v>121.850769016352</v>
       </c>
       <c r="HW32">
-        <v>7.788448912465</v>
+        <v>0.1283952698719706</v>
       </c>
       <c r="HX32">
-        <v>6.0925384508176</v>
+        <v>0.1641351971879313</v>
       </c>
       <c r="HY32" t="inlineStr">
         <is>
@@ -16884,7 +16979,7 @@
         </is>
       </c>
       <c r="HZ32">
-        <v>39.6</v>
+        <v>6.600000000000001</v>
       </c>
       <c r="IA32">
         <v>1</v>
@@ -16898,17 +16993,20 @@
         <v>1</v>
       </c>
       <c r="ID32">
+        <v>6.600000000000001</v>
+      </c>
+      <c r="IE32">
         <v>0.6012182068011893</v>
       </c>
-      <c r="IE32">
+      <c r="IF32">
         <v>0.08767642431597361</v>
       </c>
-      <c r="IF32" t="inlineStr">
+      <c r="IG32" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG32" t="inlineStr">
+      <c r="IH32" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -16956,7 +17054,7 @@
         </is>
       </c>
       <c r="K33" s="2">
-        <v>45777.67847222222</v>
+        <v>45777.17847222222</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -17337,7 +17435,7 @@
         </is>
       </c>
       <c r="HS33">
-        <v>1746029820</v>
+        <v>1745986620</v>
       </c>
       <c r="HT33" t="inlineStr">
         <is>
@@ -17351,10 +17449,10 @@
         <v>162.050124796368</v>
       </c>
       <c r="HW33">
-        <v>14.18372682915204</v>
+        <v>0.07050333188486711</v>
       </c>
       <c r="HX33">
-        <v>8.1025062398184</v>
+        <v>0.1234186028868042</v>
       </c>
       <c r="HY33" t="inlineStr">
         <is>
@@ -17362,7 +17460,7 @@
         </is>
       </c>
       <c r="HZ33">
-        <v>37.2</v>
+        <v>6.2</v>
       </c>
       <c r="IA33">
         <v>1</v>
@@ -17376,17 +17474,20 @@
         <v>1</v>
       </c>
       <c r="ID33">
+        <v>6.2</v>
+      </c>
+      <c r="IE33">
         <v>0.6012182068011893</v>
       </c>
-      <c r="IE33">
+      <c r="IF33">
         <v>0.08767642431597361</v>
       </c>
-      <c r="IF33" t="inlineStr">
+      <c r="IG33" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG33" t="inlineStr">
+      <c r="IH33" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -17434,7 +17535,7 @@
         </is>
       </c>
       <c r="K34" s="2">
-        <v>45777.71597222222</v>
+        <v>45777.21597222222</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -17577,7 +17678,7 @@
         </is>
       </c>
       <c r="HS34">
-        <v>1746033060</v>
+        <v>1745989860</v>
       </c>
       <c r="HT34" t="inlineStr">
         <is>
@@ -17591,18 +17692,18 @@
         <v>218.544411001867</v>
       </c>
       <c r="HW34">
-        <v>12.66700316387234</v>
+        <v>0.07894527119501382</v>
       </c>
       <c r="HX34">
-        <v>10.92722055009335</v>
+        <v>0.09151458007237322</v>
       </c>
       <c r="HY34" t="inlineStr">
         <is>
-          <t>Rocky</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="HZ34">
-        <v>21.6</v>
+        <v>3.6</v>
       </c>
       <c r="IA34">
         <v>1</v>
@@ -17613,17 +17714,20 @@
         </is>
       </c>
       <c r="ID34">
+        <v>3.6</v>
+      </c>
+      <c r="IE34">
         <v>0.6012182068011893</v>
       </c>
-      <c r="IE34">
+      <c r="IF34">
         <v>0.08767642431597361</v>
       </c>
-      <c r="IF34" t="inlineStr">
+      <c r="IG34" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG34" t="inlineStr">
+      <c r="IH34" t="inlineStr">
         <is>
           <t>compromised</t>
         </is>
@@ -17671,7 +17775,7 @@
         </is>
       </c>
       <c r="K35" s="2">
-        <v>45777.71597222222</v>
+        <v>45777.21597222222</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -17814,7 +17918,7 @@
         </is>
       </c>
       <c r="HS35">
-        <v>1746033060</v>
+        <v>1745989860</v>
       </c>
       <c r="HT35" t="inlineStr">
         <is>
@@ -17828,18 +17932,18 @@
         <v>183.129609879407</v>
       </c>
       <c r="HW35">
-        <v>11.9760957338734</v>
+        <v>0.08349966652083303</v>
       </c>
       <c r="HX35">
-        <v>9.156480493970351</v>
+        <v>0.1092122678204264</v>
       </c>
       <c r="HY35" t="inlineStr">
         <is>
-          <t>Rocky</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="HZ35">
-        <v>21</v>
+        <v>3.5</v>
       </c>
       <c r="IA35">
         <v>1</v>
@@ -17850,17 +17954,20 @@
         </is>
       </c>
       <c r="ID35">
+        <v>3.5</v>
+      </c>
+      <c r="IE35">
         <v>0.6012182068011893</v>
       </c>
-      <c r="IE35">
+      <c r="IF35">
         <v>0.08767642431597361</v>
       </c>
-      <c r="IF35" t="inlineStr">
+      <c r="IG35" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG35" t="inlineStr">
+      <c r="IH35" t="inlineStr">
         <is>
           <t>compromised</t>
         </is>
@@ -17908,7 +18015,7 @@
         </is>
       </c>
       <c r="K36" s="2">
-        <v>45777.52847222222</v>
+        <v>45777.02847222222</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -18282,7 +18389,7 @@
         </is>
       </c>
       <c r="HS36">
-        <v>1746016860</v>
+        <v>1745973660</v>
       </c>
       <c r="HT36" t="inlineStr">
         <is>
@@ -18296,10 +18403,10 @@
         <v>639.033952746429</v>
       </c>
       <c r="HW36">
-        <v>11.58822586362554</v>
+        <v>0.08629448647000533</v>
       </c>
       <c r="HX36">
-        <v>31.95169763732145</v>
+        <v>0.03129724158480836</v>
       </c>
       <c r="HY36" t="inlineStr">
         <is>
@@ -18307,7 +18414,7 @@
         </is>
       </c>
       <c r="HZ36">
-        <v>31.2</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="IA36">
         <v>1</v>
@@ -18321,17 +18428,20 @@
         <v>1</v>
       </c>
       <c r="ID36">
+        <v>5.199999999999999</v>
+      </c>
+      <c r="IE36">
         <v>0.6012182068011893</v>
       </c>
-      <c r="IE36">
+      <c r="IF36">
         <v>0.08767642431597361</v>
       </c>
-      <c r="IF36" t="inlineStr">
+      <c r="IG36" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG36" t="inlineStr">
+      <c r="IH36" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -18379,7 +18489,7 @@
         </is>
       </c>
       <c r="K37" s="2">
-        <v>45777.54722222222</v>
+        <v>45777.04722222222</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -18757,7 +18867,7 @@
         </is>
       </c>
       <c r="HS37">
-        <v>1746018480</v>
+        <v>1745975280</v>
       </c>
       <c r="HT37" t="inlineStr">
         <is>
@@ -18771,10 +18881,10 @@
         <v>565.618637286375</v>
       </c>
       <c r="HW37">
-        <v>5.517255633815</v>
+        <v>0.1812495317184593</v>
       </c>
       <c r="HX37">
-        <v>28.28093186431875</v>
+        <v>0.03535951378114494</v>
       </c>
       <c r="HY37" t="inlineStr">
         <is>
@@ -18782,7 +18892,7 @@
         </is>
       </c>
       <c r="HZ37">
-        <v>31.2</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="IA37">
         <v>1</v>
@@ -18796,17 +18906,20 @@
         <v>1</v>
       </c>
       <c r="ID37">
+        <v>5.199999999999999</v>
+      </c>
+      <c r="IE37">
         <v>0.6012182068011893</v>
       </c>
-      <c r="IE37">
+      <c r="IF37">
         <v>0.08767642431597361</v>
       </c>
-      <c r="IF37" t="inlineStr">
+      <c r="IG37" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG37" t="inlineStr">
+      <c r="IH37" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -18854,7 +18967,7 @@
         </is>
       </c>
       <c r="K38" s="2">
-        <v>45777.59027777778</v>
+        <v>45777.09027777778</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -19253,7 +19366,7 @@
         </is>
       </c>
       <c r="HS38">
-        <v>1746022200</v>
+        <v>1745979000</v>
       </c>
       <c r="HT38" t="inlineStr">
         <is>
@@ -19267,10 +19380,10 @@
         <v>411.557104130868</v>
       </c>
       <c r="HW38">
-        <v>2.78311960706048</v>
+        <v>0.3593090277051356</v>
       </c>
       <c r="HX38">
-        <v>20.5778552065434</v>
+        <v>0.04859592945731377</v>
       </c>
       <c r="HY38" t="inlineStr">
         <is>
@@ -19278,7 +19391,7 @@
         </is>
       </c>
       <c r="HZ38">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="IA38">
         <v>1</v>
@@ -19292,17 +19405,20 @@
         <v>1</v>
       </c>
       <c r="ID38">
+        <v>5</v>
+      </c>
+      <c r="IE38">
         <v>0.6012182068011893</v>
       </c>
-      <c r="IE38">
+      <c r="IF38">
         <v>0.08767642431597361</v>
       </c>
-      <c r="IF38" t="inlineStr">
+      <c r="IG38" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG38" t="inlineStr">
+      <c r="IH38" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -19350,7 +19466,7 @@
         </is>
       </c>
       <c r="K39" s="2">
-        <v>45777.59027777778</v>
+        <v>45777.09027777778</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -19773,7 +19889,7 @@
         </is>
       </c>
       <c r="HS39">
-        <v>1746022200</v>
+        <v>1745979000</v>
       </c>
       <c r="HT39" t="inlineStr">
         <is>
@@ -19787,10 +19903,10 @@
         <v>393.995431341253</v>
       </c>
       <c r="HW39">
-        <v>2.05165630733588</v>
+        <v>0.4874110719346174</v>
       </c>
       <c r="HX39">
-        <v>19.69977156706265</v>
+        <v>0.05076200993477336</v>
       </c>
       <c r="HY39" t="inlineStr">
         <is>
@@ -19798,7 +19914,7 @@
         </is>
       </c>
       <c r="HZ39">
-        <v>37.2</v>
+        <v>6.2</v>
       </c>
       <c r="IA39">
         <v>1</v>
@@ -19812,17 +19928,20 @@
         <v>1</v>
       </c>
       <c r="ID39">
+        <v>6.2</v>
+      </c>
+      <c r="IE39">
         <v>0.6012182068011893</v>
       </c>
-      <c r="IE39">
+      <c r="IF39">
         <v>0.08767642431597361</v>
       </c>
-      <c r="IF39" t="inlineStr">
+      <c r="IG39" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG39" t="inlineStr">
+      <c r="IH39" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -19870,7 +19989,7 @@
         </is>
       </c>
       <c r="K40" s="2">
-        <v>45777.63194444445</v>
+        <v>45777.13194444445</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -19950,6 +20069,24 @@
       <c r="AH40">
         <v>4</v>
       </c>
+      <c r="AI40">
+        <v>17.3</v>
+      </c>
+      <c r="AJ40">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AK40">
+        <v>102.2</v>
+      </c>
+      <c r="AL40">
+        <v>130</v>
+      </c>
+      <c r="AM40">
+        <v>152.3</v>
+      </c>
+      <c r="AN40">
+        <v>7.76</v>
+      </c>
       <c r="AP40">
         <v>0</v>
       </c>
@@ -20247,7 +20384,7 @@
         </is>
       </c>
       <c r="HS40">
-        <v>1746025800</v>
+        <v>1745982600</v>
       </c>
       <c r="HT40" t="inlineStr">
         <is>
@@ -20261,10 +20398,10 @@
         <v>187.90193049333</v>
       </c>
       <c r="HW40">
-        <v>28.5391286313226</v>
+        <v>0.03503961220814809</v>
       </c>
       <c r="HX40">
-        <v>9.395096524666501</v>
+        <v>0.1064385019754225</v>
       </c>
       <c r="HY40" t="inlineStr">
         <is>
@@ -20272,7 +20409,7 @@
         </is>
       </c>
       <c r="HZ40">
-        <v>34.2</v>
+        <v>5.699999999999999</v>
       </c>
       <c r="IA40">
         <v>1</v>
@@ -20286,17 +20423,20 @@
         <v>1</v>
       </c>
       <c r="ID40">
+        <v>5.699999999999999</v>
+      </c>
+      <c r="IE40">
         <v>0.6012182068011893</v>
       </c>
-      <c r="IE40">
+      <c r="IF40">
         <v>0.08767642431597361</v>
       </c>
-      <c r="IF40" t="inlineStr">
+      <c r="IG40" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG40" t="inlineStr">
+      <c r="IH40" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -20344,7 +20484,7 @@
         </is>
       </c>
       <c r="K41" s="2">
-        <v>45777.63194444445</v>
+        <v>45777.13194444445</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -20424,6 +20564,24 @@
       <c r="AH41">
         <v>0</v>
       </c>
+      <c r="AI41">
+        <v>17.3</v>
+      </c>
+      <c r="AJ41">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AK41">
+        <v>102.2</v>
+      </c>
+      <c r="AL41">
+        <v>130</v>
+      </c>
+      <c r="AM41">
+        <v>152.3</v>
+      </c>
+      <c r="AN41">
+        <v>7.76</v>
+      </c>
       <c r="AP41">
         <v>0</v>
       </c>
@@ -20670,7 +20828,7 @@
         </is>
       </c>
       <c r="HS41">
-        <v>1746025800</v>
+        <v>1745982600</v>
       </c>
       <c r="HT41" t="inlineStr">
         <is>
@@ -20684,10 +20842,10 @@
         <v>153.52894194799</v>
       </c>
       <c r="HW41">
-        <v>22.5304101069624</v>
+        <v>0.04438445617512207</v>
       </c>
       <c r="HX41">
-        <v>7.6764470973995</v>
+        <v>0.1302685978698093</v>
       </c>
       <c r="HY41" t="inlineStr">
         <is>
@@ -20695,7 +20853,7 @@
         </is>
       </c>
       <c r="HZ41">
-        <v>34.2</v>
+        <v>5.699999999999999</v>
       </c>
       <c r="IA41">
         <v>1</v>
@@ -20709,17 +20867,20 @@
         <v>1</v>
       </c>
       <c r="ID41">
+        <v>5.699999999999999</v>
+      </c>
+      <c r="IE41">
         <v>0.6012182068011893</v>
       </c>
-      <c r="IE41">
+      <c r="IF41">
         <v>0.08767642431597361</v>
       </c>
-      <c r="IF41" t="inlineStr">
+      <c r="IG41" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG41" t="inlineStr">
+      <c r="IH41" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -20767,7 +20928,7 @@
         </is>
       </c>
       <c r="K42" s="2">
-        <v>45854.55</v>
+        <v>45854.05</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -21091,7 +21252,7 @@
         </is>
       </c>
       <c r="HS42">
-        <v>1752671520</v>
+        <v>1752628320</v>
       </c>
       <c r="HT42" t="inlineStr">
         <is>
@@ -21105,10 +21266,10 @@
         <v>164.450019734722</v>
       </c>
       <c r="HW42">
-        <v>16.59778041809964</v>
+        <v>0.06024901973697124</v>
       </c>
       <c r="HX42">
-        <v>8.222500986736099</v>
+        <v>0.121617498327227</v>
       </c>
       <c r="HY42" t="inlineStr">
         <is>
@@ -21116,7 +21277,7 @@
         </is>
       </c>
       <c r="HZ42">
-        <v>31.2</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="IA42">
         <v>2</v>
@@ -21130,17 +21291,20 @@
         <v>0</v>
       </c>
       <c r="ID42">
+        <v>5.557973333333334</v>
+      </c>
+      <c r="IE42">
         <v>4.418038292131671</v>
       </c>
-      <c r="IE42">
+      <c r="IF42">
         <v>0.6450592630039791</v>
       </c>
-      <c r="IF42" t="inlineStr">
+      <c r="IG42" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG42" t="inlineStr">
+      <c r="IH42" t="inlineStr">
         <is>
           <t>compromised</t>
         </is>
@@ -21188,7 +21352,7 @@
         </is>
       </c>
       <c r="K43" s="2">
-        <v>45854.5375</v>
+        <v>45854.0375</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -21526,7 +21690,7 @@
         </is>
       </c>
       <c r="HS43">
-        <v>1752670440</v>
+        <v>1752627240</v>
       </c>
       <c r="HT43" t="inlineStr">
         <is>
@@ -21540,10 +21704,10 @@
         <v>180.302636624781</v>
       </c>
       <c r="HW43">
-        <v>21.0891039081872</v>
+        <v>0.04741785162392701</v>
       </c>
       <c r="HX43">
-        <v>9.015131831239049</v>
+        <v>0.1109246119435348</v>
       </c>
       <c r="HY43" t="inlineStr">
         <is>
@@ -21551,7 +21715,7 @@
         </is>
       </c>
       <c r="HZ43">
-        <v>26.4</v>
+        <v>4.4</v>
       </c>
       <c r="IA43">
         <v>2</v>
@@ -21565,17 +21729,20 @@
         <v>1</v>
       </c>
       <c r="ID43">
+        <v>4.4</v>
+      </c>
+      <c r="IE43">
         <v>4.418038292131671</v>
       </c>
-      <c r="IE43">
+      <c r="IF43">
         <v>0.6450592630039791</v>
       </c>
-      <c r="IF43" t="inlineStr">
+      <c r="IG43" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG43" t="inlineStr">
+      <c r="IH43" t="inlineStr">
         <is>
           <t>compromised</t>
         </is>
@@ -21623,7 +21790,7 @@
         </is>
       </c>
       <c r="K44" s="2">
-        <v>45854.47083333333</v>
+        <v>45853.97083333333</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -21958,7 +22125,7 @@
         </is>
       </c>
       <c r="HM44" s="3">
-        <v>45854</v>
+        <v>45853</v>
       </c>
       <c r="HN44" t="inlineStr">
         <is>
@@ -21982,7 +22149,7 @@
         </is>
       </c>
       <c r="HS44">
-        <v>1752664680</v>
+        <v>1752621480</v>
       </c>
       <c r="HT44" t="inlineStr">
         <is>
@@ -21996,10 +22163,10 @@
         <v>1429.22107248619</v>
       </c>
       <c r="HW44">
-        <v>15.02060854953934</v>
+        <v>0.06657519878118842</v>
       </c>
       <c r="HX44">
-        <v>71.4610536243095</v>
+        <v>0.01399363638349465</v>
       </c>
       <c r="HY44" t="inlineStr">
         <is>
@@ -22007,7 +22174,7 @@
         </is>
       </c>
       <c r="HZ44">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="IA44">
         <v>2</v>
@@ -22021,17 +22188,20 @@
         <v>0</v>
       </c>
       <c r="ID44">
-        <v>4.418038292131671</v>
+        <v>3.22144</v>
       </c>
       <c r="IE44">
-        <v>0.6450592630039791</v>
-      </c>
-      <c r="IF44" t="inlineStr">
+        <v>4.205269581746207</v>
+      </c>
+      <c r="IF44">
+        <v>0.7428305979649599</v>
+      </c>
+      <c r="IG44" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG44" t="inlineStr">
+      <c r="IH44" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -22079,7 +22249,7 @@
         </is>
       </c>
       <c r="K45" s="2">
-        <v>45854.46180555555</v>
+        <v>45853.96180555555</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -22414,7 +22584,7 @@
         </is>
       </c>
       <c r="HM45" s="3">
-        <v>45854</v>
+        <v>45853</v>
       </c>
       <c r="HN45" t="inlineStr">
         <is>
@@ -22438,7 +22608,7 @@
         </is>
       </c>
       <c r="HS45">
-        <v>1752663900</v>
+        <v>1752620700</v>
       </c>
       <c r="HT45" t="inlineStr">
         <is>
@@ -22452,10 +22622,10 @@
         <v>1435.7027457702</v>
       </c>
       <c r="HW45">
-        <v>14.62128427785038</v>
+        <v>0.06839344485729539</v>
       </c>
       <c r="HX45">
-        <v>71.78513728851</v>
+        <v>0.01393046022856964</v>
       </c>
       <c r="HY45" t="inlineStr">
         <is>
@@ -22463,7 +22633,7 @@
         </is>
       </c>
       <c r="HZ45">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="IA45">
         <v>2</v>
@@ -22477,17 +22647,20 @@
         <v>0</v>
       </c>
       <c r="ID45">
-        <v>4.418038292131671</v>
+        <v>3</v>
       </c>
       <c r="IE45">
-        <v>0.6450592630039791</v>
-      </c>
-      <c r="IF45" t="inlineStr">
+        <v>4.205269581746207</v>
+      </c>
+      <c r="IF45">
+        <v>0.7428305979649599</v>
+      </c>
+      <c r="IG45" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG45" t="inlineStr">
+      <c r="IH45" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -22535,7 +22708,7 @@
         </is>
       </c>
       <c r="K46" s="2">
-        <v>45854.44305555556</v>
+        <v>45853.94305555556</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -22826,7 +22999,7 @@
         </is>
       </c>
       <c r="HM46" s="3">
-        <v>45854</v>
+        <v>45853</v>
       </c>
       <c r="HN46" t="inlineStr">
         <is>
@@ -22850,7 +23023,7 @@
         </is>
       </c>
       <c r="HS46">
-        <v>1752662280</v>
+        <v>1752619080</v>
       </c>
       <c r="HT46" t="inlineStr">
         <is>
@@ -22864,10 +23037,10 @@
         <v>1689.68543182272</v>
       </c>
       <c r="HW46">
-        <v>53.510285413158</v>
+        <v>0.01868799600448596</v>
       </c>
       <c r="HX46">
-        <v>84.48427159113599</v>
+        <v>0.0118365227179744</v>
       </c>
       <c r="HY46" t="inlineStr">
         <is>
@@ -22875,7 +23048,7 @@
         </is>
       </c>
       <c r="HZ46">
-        <v>14.4</v>
+        <v>2.4</v>
       </c>
       <c r="IA46">
         <v>2</v>
@@ -22889,17 +23062,20 @@
         <v>1</v>
       </c>
       <c r="ID46">
-        <v>4.418038292131671</v>
+        <v>2.66496</v>
       </c>
       <c r="IE46">
-        <v>0.6450592630039791</v>
-      </c>
-      <c r="IF46" t="inlineStr">
+        <v>4.205269581746207</v>
+      </c>
+      <c r="IF46">
+        <v>0.7428305979649599</v>
+      </c>
+      <c r="IG46" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG46" t="inlineStr">
+      <c r="IH46" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -22947,7 +23123,7 @@
         </is>
       </c>
       <c r="K47" s="2">
-        <v>45854.43402777778</v>
+        <v>45853.93402777778</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -23247,7 +23423,7 @@
         </is>
       </c>
       <c r="HM47" s="3">
-        <v>45854</v>
+        <v>45853</v>
       </c>
       <c r="HN47" t="inlineStr">
         <is>
@@ -23271,7 +23447,7 @@
         </is>
       </c>
       <c r="HS47">
-        <v>1752661500</v>
+        <v>1752618300</v>
       </c>
       <c r="HT47" t="inlineStr">
         <is>
@@ -23285,18 +23461,18 @@
         <v>1741.06263130931</v>
       </c>
       <c r="HW47">
-        <v>44.1049746442002</v>
+        <v>0.022673179342401</v>
       </c>
       <c r="HX47">
-        <v>87.05313156546551</v>
+        <v>0.0114872375297376</v>
       </c>
       <c r="HY47" t="inlineStr">
         <is>
-          <t>Emergent Macrophyte</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="HZ47">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="IA47">
         <v>2</v>
@@ -23310,17 +23486,20 @@
         <v>0</v>
       </c>
       <c r="ID47">
-        <v>4.418038292131671</v>
+        <v>3</v>
       </c>
       <c r="IE47">
-        <v>0.6450592630039791</v>
-      </c>
-      <c r="IF47" t="inlineStr">
+        <v>4.205269581746207</v>
+      </c>
+      <c r="IF47">
+        <v>0.7428305979649599</v>
+      </c>
+      <c r="IG47" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG47" t="inlineStr">
+      <c r="IH47" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -23368,7 +23547,7 @@
         </is>
       </c>
       <c r="K48" s="2">
-        <v>45854.50208333333</v>
+        <v>45854.00208333333</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -23722,7 +23901,7 @@
         </is>
       </c>
       <c r="HS48">
-        <v>1752667380</v>
+        <v>1752624180</v>
       </c>
       <c r="HT48" t="inlineStr">
         <is>
@@ -23736,10 +23915,10 @@
         <v>334.104864132139</v>
       </c>
       <c r="HW48">
-        <v>26.1356496959392</v>
+        <v>0.03826191472697057</v>
       </c>
       <c r="HX48">
-        <v>16.70524320660695</v>
+        <v>0.05986144515420753</v>
       </c>
       <c r="HY48" t="inlineStr">
         <is>
@@ -23747,7 +23926,7 @@
         </is>
       </c>
       <c r="HZ48">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="IA48">
         <v>2</v>
@@ -23761,17 +23940,20 @@
         <v>1</v>
       </c>
       <c r="ID48">
+        <v>3.203733333333333</v>
+      </c>
+      <c r="IE48">
         <v>4.418038292131671</v>
       </c>
-      <c r="IE48">
+      <c r="IF48">
         <v>0.6450592630039791</v>
       </c>
-      <c r="IF48" t="inlineStr">
+      <c r="IG48" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG48" t="inlineStr">
+      <c r="IH48" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -23819,7 +24001,7 @@
         </is>
       </c>
       <c r="K49" s="2">
-        <v>45854.5</v>
+        <v>45854</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -24122,7 +24304,7 @@
         </is>
       </c>
       <c r="HS49">
-        <v>1752667200</v>
+        <v>1752624000</v>
       </c>
       <c r="HT49" t="inlineStr">
         <is>
@@ -24136,10 +24318,10 @@
         <v>381.61439291614</v>
       </c>
       <c r="HW49">
-        <v>13.90163680253436</v>
+        <v>0.07193397541631165</v>
       </c>
       <c r="HX49">
-        <v>19.080719645807</v>
+        <v>0.05240892474512882</v>
       </c>
       <c r="HY49" t="inlineStr">
         <is>
@@ -24147,7 +24329,7 @@
         </is>
       </c>
       <c r="HZ49">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="IA49">
         <v>2</v>
@@ -24161,17 +24343,20 @@
         <v>0</v>
       </c>
       <c r="ID49">
+        <v>3</v>
+      </c>
+      <c r="IE49">
         <v>4.418038292131671</v>
       </c>
-      <c r="IE49">
+      <c r="IF49">
         <v>0.6450592630039791</v>
       </c>
-      <c r="IF49" t="inlineStr">
+      <c r="IG49" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG49" t="inlineStr">
+      <c r="IH49" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -24219,7 +24404,7 @@
         </is>
       </c>
       <c r="K50" s="2">
-        <v>45854.40694444445</v>
+        <v>45853.90694444445</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -24574,7 +24759,7 @@
         </is>
       </c>
       <c r="HM50" s="3">
-        <v>45854</v>
+        <v>45853</v>
       </c>
       <c r="HN50" t="inlineStr">
         <is>
@@ -24598,7 +24783,7 @@
         </is>
       </c>
       <c r="HS50">
-        <v>1752659160</v>
+        <v>1752615960</v>
       </c>
       <c r="HT50" t="inlineStr">
         <is>
@@ -24612,18 +24797,18 @@
         <v>259.826404337621</v>
       </c>
       <c r="HW50">
-        <v>33.667898204025</v>
+        <v>0.02970188379268801</v>
       </c>
       <c r="HX50">
-        <v>12.99132021688105</v>
+        <v>0.07697447090100898</v>
       </c>
       <c r="HY50" t="inlineStr">
         <is>
-          <t>Rocky</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="HZ50">
-        <v>20.1</v>
+        <v>3.35</v>
       </c>
       <c r="IA50">
         <v>2</v>
@@ -24637,17 +24822,20 @@
         <v>1</v>
       </c>
       <c r="ID50">
-        <v>4.418038292131671</v>
+        <v>3.613893333333333</v>
       </c>
       <c r="IE50">
-        <v>0.6450592630039791</v>
-      </c>
-      <c r="IF50" t="inlineStr">
+        <v>4.205269581746207</v>
+      </c>
+      <c r="IF50">
+        <v>0.7428305979649599</v>
+      </c>
+      <c r="IG50" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG50" t="inlineStr">
+      <c r="IH50" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -24695,7 +24883,7 @@
         </is>
       </c>
       <c r="K51" s="2">
-        <v>45854.40972222222</v>
+        <v>45853.90972222222</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -25025,7 +25213,7 @@
         </is>
       </c>
       <c r="HM51" s="3">
-        <v>45854</v>
+        <v>45853</v>
       </c>
       <c r="HN51" t="inlineStr">
         <is>
@@ -25049,7 +25237,7 @@
         </is>
       </c>
       <c r="HS51">
-        <v>1752659400</v>
+        <v>1752616200</v>
       </c>
       <c r="HT51" t="inlineStr">
         <is>
@@ -25063,10 +25251,10 @@
         <v>221.365381729161</v>
       </c>
       <c r="HW51">
-        <v>27.7244235402752</v>
+        <v>0.03606928016185089</v>
       </c>
       <c r="HX51">
-        <v>11.06826908645805</v>
+        <v>0.09034836361391801</v>
       </c>
       <c r="HY51" t="inlineStr">
         <is>
@@ -25074,7 +25262,7 @@
         </is>
       </c>
       <c r="HZ51">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="IA51">
         <v>2</v>
@@ -25088,17 +25276,20 @@
         <v>1</v>
       </c>
       <c r="ID51">
-        <v>4.418038292131671</v>
+        <v>5</v>
       </c>
       <c r="IE51">
-        <v>0.6450592630039791</v>
-      </c>
-      <c r="IF51" t="inlineStr">
+        <v>4.205269581746207</v>
+      </c>
+      <c r="IF51">
+        <v>0.7428305979649599</v>
+      </c>
+      <c r="IG51" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG51" t="inlineStr">
+      <c r="IH51" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -25146,7 +25337,7 @@
         </is>
       </c>
       <c r="K52" s="2">
-        <v>45869.5</v>
+        <v>45869</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -25530,7 +25721,7 @@
         </is>
       </c>
       <c r="HS52">
-        <v>1753963200</v>
+        <v>1753920000</v>
       </c>
       <c r="HT52" t="inlineStr">
         <is>
@@ -25544,10 +25735,10 @@
         <v>121.850769016352</v>
       </c>
       <c r="HW52">
-        <v>7.788448912465</v>
+        <v>0.1283952698719706</v>
       </c>
       <c r="HX52">
-        <v>6.0925384508176</v>
+        <v>0.1641351971879313</v>
       </c>
       <c r="HY52" t="inlineStr">
         <is>
@@ -25555,7 +25746,7 @@
         </is>
       </c>
       <c r="HZ52">
-        <v>39.6</v>
+        <v>6.600000000000001</v>
       </c>
       <c r="IA52">
         <v>2</v>
@@ -25569,17 +25760,20 @@
         <v>0</v>
       </c>
       <c r="ID52">
+        <v>6.600000000000001</v>
+      </c>
+      <c r="IE52">
         <v>1.32638364073583</v>
       </c>
-      <c r="IE52">
+      <c r="IF52">
         <v>0.3790067460938265</v>
       </c>
-      <c r="IF52" t="inlineStr">
+      <c r="IG52" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG52" t="inlineStr">
+      <c r="IH52" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -25627,7 +25821,7 @@
         </is>
       </c>
       <c r="K53" s="2">
-        <v>45869.49305555555</v>
+        <v>45868.99305555555</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -25981,7 +26175,7 @@
         </is>
       </c>
       <c r="HM53" s="3">
-        <v>45869</v>
+        <v>45868</v>
       </c>
       <c r="HN53" t="inlineStr">
         <is>
@@ -26005,7 +26199,7 @@
         </is>
       </c>
       <c r="HS53">
-        <v>1753962600</v>
+        <v>1753919400</v>
       </c>
       <c r="HT53" t="inlineStr">
         <is>
@@ -26019,10 +26213,10 @@
         <v>162.050124796368</v>
       </c>
       <c r="HW53">
-        <v>14.18372682915204</v>
+        <v>0.07050333188486711</v>
       </c>
       <c r="HX53">
-        <v>8.1025062398184</v>
+        <v>0.1234186028868042</v>
       </c>
       <c r="HY53" t="inlineStr">
         <is>
@@ -26030,7 +26224,7 @@
         </is>
       </c>
       <c r="HZ53">
-        <v>37.2</v>
+        <v>6.2</v>
       </c>
       <c r="IA53">
         <v>2</v>
@@ -26044,17 +26238,20 @@
         <v>1</v>
       </c>
       <c r="ID53">
-        <v>1.32638364073583</v>
+        <v>6.2</v>
       </c>
       <c r="IE53">
-        <v>0.3790067460938265</v>
-      </c>
-      <c r="IF53" t="inlineStr">
+        <v>1.113614930350366</v>
+      </c>
+      <c r="IF53">
+        <v>0.2792896349616143</v>
+      </c>
+      <c r="IG53" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG53" t="inlineStr">
+      <c r="IH53" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -26102,7 +26299,7 @@
         </is>
       </c>
       <c r="K54" s="2">
-        <v>45869.4375</v>
+        <v>45868.9375</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -26435,7 +26632,7 @@
         </is>
       </c>
       <c r="HM54" s="3">
-        <v>45869</v>
+        <v>45868</v>
       </c>
       <c r="HN54" t="inlineStr">
         <is>
@@ -26459,7 +26656,7 @@
         </is>
       </c>
       <c r="HS54">
-        <v>1753957800</v>
+        <v>1753914600</v>
       </c>
       <c r="HT54" t="inlineStr">
         <is>
@@ -26473,18 +26670,18 @@
         <v>218.544411001867</v>
       </c>
       <c r="HW54">
-        <v>12.66700316387234</v>
+        <v>0.07894527119501382</v>
       </c>
       <c r="HX54">
-        <v>10.92722055009335</v>
+        <v>0.09151458007237322</v>
       </c>
       <c r="HY54" t="inlineStr">
         <is>
-          <t>Rocky</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="HZ54">
-        <v>21.6</v>
+        <v>3.6</v>
       </c>
       <c r="IA54">
         <v>2</v>
@@ -26498,17 +26695,20 @@
         <v>1</v>
       </c>
       <c r="ID54">
-        <v>1.32638364073583</v>
+        <v>3.6</v>
       </c>
       <c r="IE54">
-        <v>0.3790067460938265</v>
-      </c>
-      <c r="IF54" t="inlineStr">
+        <v>1.113614930350366</v>
+      </c>
+      <c r="IF54">
+        <v>0.2792896349616143</v>
+      </c>
+      <c r="IG54" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG54" t="inlineStr">
+      <c r="IH54" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -26556,7 +26756,7 @@
         </is>
       </c>
       <c r="K55" s="2">
-        <v>45869.44444444445</v>
+        <v>45868.94444444445</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -26894,7 +27094,7 @@
         </is>
       </c>
       <c r="HM55" s="3">
-        <v>45869</v>
+        <v>45868</v>
       </c>
       <c r="HN55" t="inlineStr">
         <is>
@@ -26918,7 +27118,7 @@
         </is>
       </c>
       <c r="HS55">
-        <v>1753958400</v>
+        <v>1753915200</v>
       </c>
       <c r="HT55" t="inlineStr">
         <is>
@@ -26932,18 +27132,18 @@
         <v>183.129609879407</v>
       </c>
       <c r="HW55">
-        <v>11.9760957338734</v>
+        <v>0.08349966652083303</v>
       </c>
       <c r="HX55">
-        <v>9.156480493970351</v>
+        <v>0.1092122678204264</v>
       </c>
       <c r="HY55" t="inlineStr">
         <is>
-          <t>Rocky</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="HZ55">
-        <v>21</v>
+        <v>3.5</v>
       </c>
       <c r="IA55">
         <v>2</v>
@@ -26957,17 +27157,20 @@
         <v>0</v>
       </c>
       <c r="ID55">
-        <v>1.32638364073583</v>
+        <v>3.5</v>
       </c>
       <c r="IE55">
-        <v>0.3790067460938265</v>
-      </c>
-      <c r="IF55" t="inlineStr">
+        <v>1.113614930350366</v>
+      </c>
+      <c r="IF55">
+        <v>0.2792896349616143</v>
+      </c>
+      <c r="IG55" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG55" t="inlineStr">
+      <c r="IH55" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -27015,7 +27218,7 @@
         </is>
       </c>
       <c r="K56" s="2">
-        <v>45869.42708333333</v>
+        <v>45868.92708333333</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -27353,7 +27556,7 @@
         </is>
       </c>
       <c r="HM56" s="3">
-        <v>45869</v>
+        <v>45868</v>
       </c>
       <c r="HN56" t="inlineStr">
         <is>
@@ -27377,7 +27580,7 @@
         </is>
       </c>
       <c r="HS56">
-        <v>1753956900</v>
+        <v>1753913700</v>
       </c>
       <c r="HT56" t="inlineStr">
         <is>
@@ -27391,10 +27594,10 @@
         <v>639.033952746429</v>
       </c>
       <c r="HW56">
-        <v>11.58822586362554</v>
+        <v>0.08629448647000533</v>
       </c>
       <c r="HX56">
-        <v>31.95169763732145</v>
+        <v>0.03129724158480836</v>
       </c>
       <c r="HY56" t="inlineStr">
         <is>
@@ -27402,7 +27605,7 @@
         </is>
       </c>
       <c r="HZ56">
-        <v>31.2</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="IA56">
         <v>2</v>
@@ -27416,17 +27619,20 @@
         <v>1</v>
       </c>
       <c r="ID56">
-        <v>1.32638364073583</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="IE56">
-        <v>0.3790067460938265</v>
-      </c>
-      <c r="IF56" t="inlineStr">
+        <v>1.113614930350366</v>
+      </c>
+      <c r="IF56">
+        <v>0.2792896349616143</v>
+      </c>
+      <c r="IG56" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG56" t="inlineStr">
+      <c r="IH56" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -27474,7 +27680,7 @@
         </is>
       </c>
       <c r="K57" s="2">
-        <v>45869.41666666667</v>
+        <v>45868.91666666667</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -27747,7 +27953,7 @@
         </is>
       </c>
       <c r="HM57" s="3">
-        <v>45869</v>
+        <v>45868</v>
       </c>
       <c r="HN57" t="inlineStr">
         <is>
@@ -27771,7 +27977,7 @@
         </is>
       </c>
       <c r="HS57">
-        <v>1753956000</v>
+        <v>1753912800</v>
       </c>
       <c r="HT57" t="inlineStr">
         <is>
@@ -27785,10 +27991,10 @@
         <v>565.618637286375</v>
       </c>
       <c r="HW57">
-        <v>5.517255633815</v>
+        <v>0.1812495317184593</v>
       </c>
       <c r="HX57">
-        <v>28.28093186431875</v>
+        <v>0.03535951378114494</v>
       </c>
       <c r="HY57" t="inlineStr">
         <is>
@@ -27796,7 +28002,7 @@
         </is>
       </c>
       <c r="HZ57">
-        <v>31.2</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="IA57">
         <v>2</v>
@@ -27810,17 +28016,20 @@
         <v>0</v>
       </c>
       <c r="ID57">
-        <v>1.32638364073583</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="IE57">
-        <v>0.3790067460938265</v>
-      </c>
-      <c r="IF57" t="inlineStr">
+        <v>1.113614930350366</v>
+      </c>
+      <c r="IF57">
+        <v>0.2792896349616143</v>
+      </c>
+      <c r="IG57" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG57" t="inlineStr">
+      <c r="IH57" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -27868,7 +28077,7 @@
         </is>
       </c>
       <c r="K58" s="2">
-        <v>45869.45833333333</v>
+        <v>45868.95833333333</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -28231,7 +28440,7 @@
         </is>
       </c>
       <c r="HM58" s="3">
-        <v>45869</v>
+        <v>45868</v>
       </c>
       <c r="HN58" t="inlineStr">
         <is>
@@ -28255,7 +28464,7 @@
         </is>
       </c>
       <c r="HS58">
-        <v>1753959600</v>
+        <v>1753916400</v>
       </c>
       <c r="HT58" t="inlineStr">
         <is>
@@ -28269,10 +28478,10 @@
         <v>411.557104130868</v>
       </c>
       <c r="HW58">
-        <v>2.78311960706048</v>
+        <v>0.3593090277051356</v>
       </c>
       <c r="HX58">
-        <v>20.5778552065434</v>
+        <v>0.04859592945731377</v>
       </c>
       <c r="HY58" t="inlineStr">
         <is>
@@ -28280,7 +28489,7 @@
         </is>
       </c>
       <c r="HZ58">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="IA58">
         <v>2</v>
@@ -28294,17 +28503,20 @@
         <v>1</v>
       </c>
       <c r="ID58">
-        <v>1.32638364073583</v>
+        <v>5</v>
       </c>
       <c r="IE58">
-        <v>0.3790067460938265</v>
-      </c>
-      <c r="IF58" t="inlineStr">
+        <v>1.113614930350366</v>
+      </c>
+      <c r="IF58">
+        <v>0.2792896349616143</v>
+      </c>
+      <c r="IG58" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG58" t="inlineStr">
+      <c r="IH58" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -28352,7 +28564,7 @@
         </is>
       </c>
       <c r="K59" s="2">
-        <v>45869.46527777778</v>
+        <v>45868.96527777778</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -28685,7 +28897,7 @@
         </is>
       </c>
       <c r="HM59" s="3">
-        <v>45869</v>
+        <v>45868</v>
       </c>
       <c r="HN59" t="inlineStr">
         <is>
@@ -28709,7 +28921,7 @@
         </is>
       </c>
       <c r="HS59">
-        <v>1753960200</v>
+        <v>1753917000</v>
       </c>
       <c r="HT59" t="inlineStr">
         <is>
@@ -28723,10 +28935,10 @@
         <v>393.995431341253</v>
       </c>
       <c r="HW59">
-        <v>2.05165630733588</v>
+        <v>0.4874110719346174</v>
       </c>
       <c r="HX59">
-        <v>19.69977156706265</v>
+        <v>0.05076200993477336</v>
       </c>
       <c r="HY59" t="inlineStr">
         <is>
@@ -28734,7 +28946,7 @@
         </is>
       </c>
       <c r="HZ59">
-        <v>37.2</v>
+        <v>6.2</v>
       </c>
       <c r="IA59">
         <v>2</v>
@@ -28748,17 +28960,20 @@
         <v>0</v>
       </c>
       <c r="ID59">
-        <v>1.32638364073583</v>
+        <v>6.2</v>
       </c>
       <c r="IE59">
-        <v>0.3790067460938265</v>
-      </c>
-      <c r="IF59" t="inlineStr">
+        <v>1.113614930350366</v>
+      </c>
+      <c r="IF59">
+        <v>0.2792896349616143</v>
+      </c>
+      <c r="IG59" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG59" t="inlineStr">
+      <c r="IH59" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -28806,7 +29021,7 @@
         </is>
       </c>
       <c r="K60" s="2">
-        <v>45869.47222222222</v>
+        <v>45868.97222222222</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -29149,7 +29364,7 @@
         </is>
       </c>
       <c r="HM60" s="3">
-        <v>45869</v>
+        <v>45868</v>
       </c>
       <c r="HN60" t="inlineStr">
         <is>
@@ -29173,7 +29388,7 @@
         </is>
       </c>
       <c r="HS60">
-        <v>1753960800</v>
+        <v>1753917600</v>
       </c>
       <c r="HT60" t="inlineStr">
         <is>
@@ -29187,10 +29402,10 @@
         <v>187.90193049333</v>
       </c>
       <c r="HW60">
-        <v>28.5391286313226</v>
+        <v>0.03503961220814809</v>
       </c>
       <c r="HX60">
-        <v>9.395096524666501</v>
+        <v>0.1064385019754225</v>
       </c>
       <c r="HY60" t="inlineStr">
         <is>
@@ -29198,7 +29413,7 @@
         </is>
       </c>
       <c r="HZ60">
-        <v>34.2</v>
+        <v>5.699999999999999</v>
       </c>
       <c r="IA60">
         <v>2</v>
@@ -29212,17 +29427,20 @@
         <v>1</v>
       </c>
       <c r="ID60">
-        <v>1.32638364073583</v>
+        <v>5.699999999999999</v>
       </c>
       <c r="IE60">
-        <v>0.3790067460938265</v>
-      </c>
-      <c r="IF60" t="inlineStr">
+        <v>1.113614930350366</v>
+      </c>
+      <c r="IF60">
+        <v>0.2792896349616143</v>
+      </c>
+      <c r="IG60" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG60" t="inlineStr">
+      <c r="IH60" t="inlineStr">
         <is>
           <t>compromised</t>
         </is>
@@ -29270,7 +29488,7 @@
         </is>
       </c>
       <c r="K61" s="2">
-        <v>45869.47916666667</v>
+        <v>45868.97916666667</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -29604,7 +29822,7 @@
         </is>
       </c>
       <c r="HM61" s="3">
-        <v>45869</v>
+        <v>45868</v>
       </c>
       <c r="HN61" t="inlineStr">
         <is>
@@ -29628,7 +29846,7 @@
         </is>
       </c>
       <c r="HS61">
-        <v>1753961400</v>
+        <v>1753918200</v>
       </c>
       <c r="HT61" t="inlineStr">
         <is>
@@ -29642,10 +29860,10 @@
         <v>153.52894194799</v>
       </c>
       <c r="HW61">
-        <v>22.5304101069624</v>
+        <v>0.04438445617512207</v>
       </c>
       <c r="HX61">
-        <v>7.6764470973995</v>
+        <v>0.1302685978698093</v>
       </c>
       <c r="HY61" t="inlineStr">
         <is>
@@ -29653,7 +29871,7 @@
         </is>
       </c>
       <c r="HZ61">
-        <v>34.2</v>
+        <v>5.699999999999999</v>
       </c>
       <c r="IA61">
         <v>2</v>
@@ -29667,17 +29885,20 @@
         <v>1</v>
       </c>
       <c r="ID61">
-        <v>1.32638364073583</v>
+        <v>5.699999999999999</v>
       </c>
       <c r="IE61">
-        <v>0.3790067460938265</v>
-      </c>
-      <c r="IF61" t="inlineStr">
+        <v>1.113614930350366</v>
+      </c>
+      <c r="IF61">
+        <v>0.2792896349616143</v>
+      </c>
+      <c r="IG61" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG61" t="inlineStr">
+      <c r="IH61" t="inlineStr">
         <is>
           <t>compromised</t>
         </is>
@@ -29725,7 +29946,7 @@
         </is>
       </c>
       <c r="K62" s="2">
-        <v>45951.54027777778</v>
+        <v>45950.99861111111</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -29836,7 +30057,7 @@
         </is>
       </c>
       <c r="HM62" s="3">
-        <v>45951</v>
+        <v>45950</v>
       </c>
       <c r="HN62" t="inlineStr">
         <is>
@@ -29860,7 +30081,7 @@
         </is>
       </c>
       <c r="HS62">
-        <v>1761051480</v>
+        <v>1761004680</v>
       </c>
       <c r="HT62" t="inlineStr">
         <is>
@@ -29874,10 +30095,10 @@
         <v>164.450019734722</v>
       </c>
       <c r="HW62">
-        <v>16.59778041809964</v>
+        <v>0.06024901973697124</v>
       </c>
       <c r="HX62">
-        <v>8.222500986736099</v>
+        <v>0.121617498327227</v>
       </c>
       <c r="HY62" t="inlineStr">
         <is>
@@ -29885,7 +30106,7 @@
         </is>
       </c>
       <c r="HZ62">
-        <v>31.2</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="IA62">
         <v>3</v>
@@ -29896,17 +30117,20 @@
         </is>
       </c>
       <c r="ID62">
-        <v>6.207047277994345</v>
+        <v>5.557973333333334</v>
       </c>
       <c r="IE62">
-        <v>0.001448549898926232</v>
-      </c>
-      <c r="IF62" t="inlineStr">
+        <v>5.994278567608524</v>
+      </c>
+      <c r="IF62">
+        <v>0.02072203847629311</v>
+      </c>
+      <c r="IG62" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG62" t="inlineStr">
+      <c r="IH62" t="inlineStr">
         <is>
           <t>compromised</t>
         </is>
@@ -29954,7 +30178,7 @@
         </is>
       </c>
       <c r="K63" s="2">
-        <v>45951.55416666667</v>
+        <v>45951.0125</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -30094,7 +30318,7 @@
         </is>
       </c>
       <c r="HS63">
-        <v>1761052680</v>
+        <v>1761005880</v>
       </c>
       <c r="HT63" t="inlineStr">
         <is>
@@ -30108,10 +30332,10 @@
         <v>180.302636624781</v>
       </c>
       <c r="HW63">
-        <v>21.0891039081872</v>
+        <v>0.04741785162392701</v>
       </c>
       <c r="HX63">
-        <v>9.015131831239049</v>
+        <v>0.1109246119435348</v>
       </c>
       <c r="HY63" t="inlineStr">
         <is>
@@ -30119,7 +30343,7 @@
         </is>
       </c>
       <c r="HZ63">
-        <v>26.4</v>
+        <v>4.4</v>
       </c>
       <c r="IA63">
         <v>3</v>
@@ -30130,17 +30354,20 @@
         </is>
       </c>
       <c r="ID63">
+        <v>4.4</v>
+      </c>
+      <c r="IE63">
         <v>6.207047277994345</v>
       </c>
-      <c r="IE63">
+      <c r="IF63">
         <v>0.001448549898926232</v>
       </c>
-      <c r="IF63" t="inlineStr">
+      <c r="IG63" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG63" t="inlineStr">
+      <c r="IH63" t="inlineStr">
         <is>
           <t>compromised</t>
         </is>
@@ -30188,7 +30415,7 @@
         </is>
       </c>
       <c r="K64" s="2">
-        <v>45951.47986111111</v>
+        <v>45950.93819444445</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -30478,7 +30705,7 @@
         </is>
       </c>
       <c r="HM64" s="3">
-        <v>45951</v>
+        <v>45950</v>
       </c>
       <c r="HN64" t="inlineStr">
         <is>
@@ -30502,7 +30729,7 @@
         </is>
       </c>
       <c r="HS64">
-        <v>1761046260</v>
+        <v>1760999460</v>
       </c>
       <c r="HT64" t="inlineStr">
         <is>
@@ -30516,10 +30743,10 @@
         <v>1429.22107248619</v>
       </c>
       <c r="HW64">
-        <v>15.02060854953934</v>
+        <v>0.06657519878118842</v>
       </c>
       <c r="HX64">
-        <v>71.4610536243095</v>
+        <v>0.01399363638349465</v>
       </c>
       <c r="HY64" t="inlineStr">
         <is>
@@ -30527,7 +30754,7 @@
         </is>
       </c>
       <c r="HZ64">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="IA64">
         <v>3</v>
@@ -30541,17 +30768,20 @@
         <v>0</v>
       </c>
       <c r="ID64">
-        <v>6.207047277994345</v>
+        <v>3.22144</v>
       </c>
       <c r="IE64">
-        <v>0.001448549898926232</v>
-      </c>
-      <c r="IF64" t="inlineStr">
+        <v>5.994278567608524</v>
+      </c>
+      <c r="IF64">
+        <v>0.02072203847629311</v>
+      </c>
+      <c r="IG64" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG64" t="inlineStr">
+      <c r="IH64" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -30599,7 +30829,7 @@
         </is>
       </c>
       <c r="K65" s="2">
-        <v>45951.46736111111</v>
+        <v>45950.92569444445</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -30910,7 +31140,7 @@
         </is>
       </c>
       <c r="HM65" s="3">
-        <v>45951</v>
+        <v>45950</v>
       </c>
       <c r="HN65" t="inlineStr">
         <is>
@@ -30934,7 +31164,7 @@
         </is>
       </c>
       <c r="HS65">
-        <v>1761045180</v>
+        <v>1760998380</v>
       </c>
       <c r="HT65" t="inlineStr">
         <is>
@@ -30948,10 +31178,10 @@
         <v>1435.7027457702</v>
       </c>
       <c r="HW65">
-        <v>14.62128427785038</v>
+        <v>0.06839344485729539</v>
       </c>
       <c r="HX65">
-        <v>71.78513728851</v>
+        <v>0.01393046022856964</v>
       </c>
       <c r="HY65" t="inlineStr">
         <is>
@@ -30959,7 +31189,7 @@
         </is>
       </c>
       <c r="HZ65">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="IA65">
         <v>3</v>
@@ -30973,17 +31203,20 @@
         <v>0</v>
       </c>
       <c r="ID65">
-        <v>6.207047277994345</v>
+        <v>3</v>
       </c>
       <c r="IE65">
-        <v>0.001448549898926232</v>
-      </c>
-      <c r="IF65" t="inlineStr">
+        <v>5.994278567608524</v>
+      </c>
+      <c r="IF65">
+        <v>0.02072203847629311</v>
+      </c>
+      <c r="IG65" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG65" t="inlineStr">
+      <c r="IH65" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -31031,7 +31264,7 @@
         </is>
       </c>
       <c r="K66" s="2">
-        <v>45951.44861111111</v>
+        <v>45950.90694444445</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -31355,7 +31588,7 @@
         </is>
       </c>
       <c r="HM66" s="3">
-        <v>45951</v>
+        <v>45950</v>
       </c>
       <c r="HN66" t="inlineStr">
         <is>
@@ -31379,7 +31612,7 @@
         </is>
       </c>
       <c r="HS66">
-        <v>1761043560</v>
+        <v>1760996760</v>
       </c>
       <c r="HT66" t="inlineStr">
         <is>
@@ -31393,10 +31626,10 @@
         <v>1689.68543182272</v>
       </c>
       <c r="HW66">
-        <v>53.510285413158</v>
+        <v>0.01868799600448596</v>
       </c>
       <c r="HX66">
-        <v>84.48427159113599</v>
+        <v>0.0118365227179744</v>
       </c>
       <c r="HY66" t="inlineStr">
         <is>
@@ -31404,7 +31637,7 @@
         </is>
       </c>
       <c r="HZ66">
-        <v>14.4</v>
+        <v>2.4</v>
       </c>
       <c r="IA66">
         <v>3</v>
@@ -31418,17 +31651,20 @@
         <v>1</v>
       </c>
       <c r="ID66">
-        <v>6.207047277994345</v>
+        <v>2.66496</v>
       </c>
       <c r="IE66">
-        <v>0.001448549898926232</v>
-      </c>
-      <c r="IF66" t="inlineStr">
+        <v>5.994278567608524</v>
+      </c>
+      <c r="IF66">
+        <v>0.02072203847629311</v>
+      </c>
+      <c r="IG66" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG66" t="inlineStr">
+      <c r="IH66" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -31476,7 +31712,7 @@
         </is>
       </c>
       <c r="K67" s="2">
-        <v>45951.43819444445</v>
+        <v>45950.89652777778</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -31824,7 +32060,7 @@
         </is>
       </c>
       <c r="HM67" s="3">
-        <v>45951</v>
+        <v>45950</v>
       </c>
       <c r="HN67" t="inlineStr">
         <is>
@@ -31848,7 +32084,7 @@
         </is>
       </c>
       <c r="HS67">
-        <v>1761042660</v>
+        <v>1760995860</v>
       </c>
       <c r="HT67" t="inlineStr">
         <is>
@@ -31862,18 +32098,18 @@
         <v>1741.06263130931</v>
       </c>
       <c r="HW67">
-        <v>44.1049746442002</v>
+        <v>0.022673179342401</v>
       </c>
       <c r="HX67">
-        <v>87.05313156546551</v>
+        <v>0.0114872375297376</v>
       </c>
       <c r="HY67" t="inlineStr">
         <is>
-          <t>Emergent Macrophyte</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="HZ67">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="IA67">
         <v>3</v>
@@ -31887,17 +32123,20 @@
         <v>1</v>
       </c>
       <c r="ID67">
-        <v>6.207047277994345</v>
+        <v>3</v>
       </c>
       <c r="IE67">
-        <v>0.001448549898926232</v>
-      </c>
-      <c r="IF67" t="inlineStr">
+        <v>5.994278567608524</v>
+      </c>
+      <c r="IF67">
+        <v>0.02072203847629311</v>
+      </c>
+      <c r="IG67" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG67" t="inlineStr">
+      <c r="IH67" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -31945,7 +32184,7 @@
         </is>
       </c>
       <c r="K68" s="2">
-        <v>45951.51666666666</v>
+        <v>45950.975</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -32269,7 +32508,7 @@
         </is>
       </c>
       <c r="HM68" s="3">
-        <v>45951</v>
+        <v>45950</v>
       </c>
       <c r="HN68" t="inlineStr">
         <is>
@@ -32293,7 +32532,7 @@
         </is>
       </c>
       <c r="HS68">
-        <v>1761049440</v>
+        <v>1761002640</v>
       </c>
       <c r="HT68" t="inlineStr">
         <is>
@@ -32307,10 +32546,10 @@
         <v>334.104864132139</v>
       </c>
       <c r="HW68">
-        <v>26.1356496959392</v>
+        <v>0.03826191472697057</v>
       </c>
       <c r="HX68">
-        <v>16.70524320660695</v>
+        <v>0.05986144515420753</v>
       </c>
       <c r="HY68" t="inlineStr">
         <is>
@@ -32318,7 +32557,7 @@
         </is>
       </c>
       <c r="HZ68">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="IA68">
         <v>3</v>
@@ -32332,17 +32571,20 @@
         <v>1</v>
       </c>
       <c r="ID68">
-        <v>6.207047277994345</v>
+        <v>3.203733333333333</v>
       </c>
       <c r="IE68">
-        <v>0.001448549898926232</v>
-      </c>
-      <c r="IF68" t="inlineStr">
+        <v>5.994278567608524</v>
+      </c>
+      <c r="IF68">
+        <v>0.02072203847629311</v>
+      </c>
+      <c r="IG68" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG68" t="inlineStr">
+      <c r="IH68" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -32390,7 +32632,7 @@
         </is>
       </c>
       <c r="K69" s="2">
-        <v>45951.51319444444</v>
+        <v>45950.97152777778</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -32672,7 +32914,7 @@
         </is>
       </c>
       <c r="HM69" s="3">
-        <v>45951</v>
+        <v>45950</v>
       </c>
       <c r="HN69" t="inlineStr">
         <is>
@@ -32696,7 +32938,7 @@
         </is>
       </c>
       <c r="HS69">
-        <v>1761049140</v>
+        <v>1761002340</v>
       </c>
       <c r="HT69" t="inlineStr">
         <is>
@@ -32710,10 +32952,10 @@
         <v>381.61439291614</v>
       </c>
       <c r="HW69">
-        <v>13.90163680253436</v>
+        <v>0.07193397541631165</v>
       </c>
       <c r="HX69">
-        <v>19.080719645807</v>
+        <v>0.05240892474512882</v>
       </c>
       <c r="HY69" t="inlineStr">
         <is>
@@ -32721,7 +32963,7 @@
         </is>
       </c>
       <c r="HZ69">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="IA69">
         <v>3</v>
@@ -32735,17 +32977,20 @@
         <v>0</v>
       </c>
       <c r="ID69">
-        <v>6.207047277994345</v>
+        <v>3</v>
       </c>
       <c r="IE69">
-        <v>0.001448549898926232</v>
-      </c>
-      <c r="IF69" t="inlineStr">
+        <v>5.994278567608524</v>
+      </c>
+      <c r="IF69">
+        <v>0.02072203847629311</v>
+      </c>
+      <c r="IG69" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG69" t="inlineStr">
+      <c r="IH69" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -32793,7 +33038,7 @@
         </is>
       </c>
       <c r="K70" s="2">
-        <v>45951.40416666667</v>
+        <v>45950.8625</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -33112,7 +33357,7 @@
         </is>
       </c>
       <c r="HM70" s="3">
-        <v>45951</v>
+        <v>45950</v>
       </c>
       <c r="HN70" t="inlineStr">
         <is>
@@ -33136,7 +33381,7 @@
         </is>
       </c>
       <c r="HS70">
-        <v>1761039720</v>
+        <v>1760992920</v>
       </c>
       <c r="HT70" t="inlineStr">
         <is>
@@ -33150,18 +33395,18 @@
         <v>259.826404337621</v>
       </c>
       <c r="HW70">
-        <v>33.667898204025</v>
+        <v>0.02970188379268801</v>
       </c>
       <c r="HX70">
-        <v>12.99132021688105</v>
+        <v>0.07697447090100898</v>
       </c>
       <c r="HY70" t="inlineStr">
         <is>
-          <t>Rocky</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="HZ70">
-        <v>20.1</v>
+        <v>3.35</v>
       </c>
       <c r="IA70">
         <v>3</v>
@@ -33175,17 +33420,20 @@
         <v>1</v>
       </c>
       <c r="ID70">
-        <v>6.207047277994345</v>
+        <v>3.613893333333333</v>
       </c>
       <c r="IE70">
-        <v>0.001448549898926232</v>
-      </c>
-      <c r="IF70" t="inlineStr">
+        <v>5.994278567608524</v>
+      </c>
+      <c r="IF70">
+        <v>0.02072203847629311</v>
+      </c>
+      <c r="IG70" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG70" t="inlineStr">
+      <c r="IH70" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -33233,7 +33481,7 @@
         </is>
       </c>
       <c r="K71" s="2">
-        <v>45951.40416666667</v>
+        <v>45950.8625</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -33536,7 +33784,7 @@
         </is>
       </c>
       <c r="HM71" s="3">
-        <v>45951</v>
+        <v>45950</v>
       </c>
       <c r="HN71" t="inlineStr">
         <is>
@@ -33560,7 +33808,7 @@
         </is>
       </c>
       <c r="HS71">
-        <v>1761039720</v>
+        <v>1760992920</v>
       </c>
       <c r="HT71" t="inlineStr">
         <is>
@@ -33574,10 +33822,10 @@
         <v>221.365381729161</v>
       </c>
       <c r="HW71">
-        <v>27.7244235402752</v>
+        <v>0.03606928016185089</v>
       </c>
       <c r="HX71">
-        <v>11.06826908645805</v>
+        <v>0.09034836361391801</v>
       </c>
       <c r="HY71" t="inlineStr">
         <is>
@@ -33585,7 +33833,7 @@
         </is>
       </c>
       <c r="HZ71">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="IA71">
         <v>3</v>
@@ -33599,17 +33847,20 @@
         <v>1</v>
       </c>
       <c r="ID71">
-        <v>6.207047277994345</v>
+        <v>5</v>
       </c>
       <c r="IE71">
-        <v>0.001448549898926232</v>
-      </c>
-      <c r="IF71" t="inlineStr">
+        <v>5.994278567608524</v>
+      </c>
+      <c r="IF71">
+        <v>0.02072203847629311</v>
+      </c>
+      <c r="IG71" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG71" t="inlineStr">
+      <c r="IH71" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -33657,7 +33908,7 @@
         </is>
       </c>
       <c r="K72" s="2">
-        <v>45971.52708333333</v>
+        <v>45970.98541666666</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -34041,7 +34292,7 @@
         </is>
       </c>
       <c r="HM72" s="3">
-        <v>45971</v>
+        <v>45970</v>
       </c>
       <c r="HN72" t="inlineStr">
         <is>
@@ -34065,7 +34316,7 @@
         </is>
       </c>
       <c r="HS72">
-        <v>1762778340</v>
+        <v>1762731540</v>
       </c>
       <c r="HT72" t="inlineStr">
         <is>
@@ -34079,10 +34330,10 @@
         <v>121.850769016352</v>
       </c>
       <c r="HW72">
-        <v>7.788448912465</v>
+        <v>0.1283952698719706</v>
       </c>
       <c r="HX72">
-        <v>6.0925384508176</v>
+        <v>0.1641351971879313</v>
       </c>
       <c r="HY72" t="inlineStr">
         <is>
@@ -34090,7 +34341,7 @@
         </is>
       </c>
       <c r="HZ72">
-        <v>39.6</v>
+        <v>6.600000000000001</v>
       </c>
       <c r="IA72">
         <v>3</v>
@@ -34104,17 +34355,20 @@
         <v>1</v>
       </c>
       <c r="ID72">
-        <v>4.179236178526182</v>
+        <v>6.600000000000001</v>
       </c>
       <c r="IE72">
-        <v>0.7541255419473551</v>
-      </c>
-      <c r="IF72" t="inlineStr">
+        <v>3.966467468140717</v>
+      </c>
+      <c r="IF72">
+        <v>0.83932445750031</v>
+      </c>
+      <c r="IG72" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG72" t="inlineStr">
+      <c r="IH72" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -34162,7 +34416,7 @@
         </is>
       </c>
       <c r="K73" s="2">
-        <v>45971.52708333333</v>
+        <v>45970.98541666666</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -34525,7 +34779,7 @@
         </is>
       </c>
       <c r="HM73" s="3">
-        <v>45971</v>
+        <v>45970</v>
       </c>
       <c r="HN73" t="inlineStr">
         <is>
@@ -34549,7 +34803,7 @@
         </is>
       </c>
       <c r="HS73">
-        <v>1762778340</v>
+        <v>1762731540</v>
       </c>
       <c r="HT73" t="inlineStr">
         <is>
@@ -34563,10 +34817,10 @@
         <v>162.050124796368</v>
       </c>
       <c r="HW73">
-        <v>14.18372682915204</v>
+        <v>0.07050333188486711</v>
       </c>
       <c r="HX73">
-        <v>8.1025062398184</v>
+        <v>0.1234186028868042</v>
       </c>
       <c r="HY73" t="inlineStr">
         <is>
@@ -34574,7 +34828,7 @@
         </is>
       </c>
       <c r="HZ73">
-        <v>37.2</v>
+        <v>6.2</v>
       </c>
       <c r="IA73">
         <v>3</v>
@@ -34588,17 +34842,20 @@
         <v>0</v>
       </c>
       <c r="ID73">
-        <v>4.179236178526182</v>
+        <v>6.2</v>
       </c>
       <c r="IE73">
-        <v>0.7541255419473551</v>
-      </c>
-      <c r="IF73" t="inlineStr">
+        <v>3.966467468140717</v>
+      </c>
+      <c r="IF73">
+        <v>0.83932445750031</v>
+      </c>
+      <c r="IG73" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG73" t="inlineStr">
+      <c r="IH73" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -34646,7 +34903,7 @@
         </is>
       </c>
       <c r="K74" s="2">
-        <v>45971.46805555555</v>
+        <v>45970.92638888889</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -34970,7 +35227,7 @@
         </is>
       </c>
       <c r="HM74" s="3">
-        <v>45971</v>
+        <v>45970</v>
       </c>
       <c r="HN74" t="inlineStr">
         <is>
@@ -34994,7 +35251,7 @@
         </is>
       </c>
       <c r="HS74">
-        <v>1762773240</v>
+        <v>1762726440</v>
       </c>
       <c r="HT74" t="inlineStr">
         <is>
@@ -35008,18 +35265,18 @@
         <v>218.544411001867</v>
       </c>
       <c r="HW74">
-        <v>12.66700316387234</v>
+        <v>0.07894527119501382</v>
       </c>
       <c r="HX74">
-        <v>10.92722055009335</v>
+        <v>0.09151458007237322</v>
       </c>
       <c r="HY74" t="inlineStr">
         <is>
-          <t>Rocky</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="HZ74">
-        <v>21.6</v>
+        <v>3.6</v>
       </c>
       <c r="IA74">
         <v>3</v>
@@ -35033,17 +35290,20 @@
         <v>0</v>
       </c>
       <c r="ID74">
-        <v>4.179236178526182</v>
+        <v>3.6</v>
       </c>
       <c r="IE74">
-        <v>0.7541255419473551</v>
-      </c>
-      <c r="IF74" t="inlineStr">
+        <v>3.966467468140717</v>
+      </c>
+      <c r="IF74">
+        <v>0.83932445750031</v>
+      </c>
+      <c r="IG74" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG74" t="inlineStr">
+      <c r="IH74" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -35091,7 +35351,7 @@
         </is>
       </c>
       <c r="K75" s="2">
-        <v>45971.46805555555</v>
+        <v>45970.92638888889</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -35403,7 +35663,7 @@
         </is>
       </c>
       <c r="HM75" s="3">
-        <v>45971</v>
+        <v>45970</v>
       </c>
       <c r="HN75" t="inlineStr">
         <is>
@@ -35427,7 +35687,7 @@
         </is>
       </c>
       <c r="HS75">
-        <v>1762773240</v>
+        <v>1762726440</v>
       </c>
       <c r="HT75" t="inlineStr">
         <is>
@@ -35441,18 +35701,18 @@
         <v>183.129609879407</v>
       </c>
       <c r="HW75">
-        <v>11.9760957338734</v>
+        <v>0.08349966652083303</v>
       </c>
       <c r="HX75">
-        <v>9.156480493970351</v>
+        <v>0.1092122678204264</v>
       </c>
       <c r="HY75" t="inlineStr">
         <is>
-          <t>Rocky</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="HZ75">
-        <v>21</v>
+        <v>3.5</v>
       </c>
       <c r="IA75">
         <v>3</v>
@@ -35466,17 +35726,20 @@
         <v>0</v>
       </c>
       <c r="ID75">
-        <v>4.179236178526182</v>
+        <v>3.5</v>
       </c>
       <c r="IE75">
-        <v>0.7541255419473551</v>
-      </c>
-      <c r="IF75" t="inlineStr">
+        <v>3.966467468140717</v>
+      </c>
+      <c r="IF75">
+        <v>0.83932445750031</v>
+      </c>
+      <c r="IG75" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG75" t="inlineStr">
+      <c r="IH75" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -35524,7 +35787,7 @@
         </is>
       </c>
       <c r="K76" s="2">
-        <v>45971.54097222222</v>
+        <v>45970.99930555555</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -35853,7 +36116,7 @@
         </is>
       </c>
       <c r="HM76" s="3">
-        <v>45971</v>
+        <v>45970</v>
       </c>
       <c r="HN76" t="inlineStr">
         <is>
@@ -35877,7 +36140,7 @@
         </is>
       </c>
       <c r="HS76">
-        <v>1762779540</v>
+        <v>1762732740</v>
       </c>
       <c r="HT76" t="inlineStr">
         <is>
@@ -35891,10 +36154,10 @@
         <v>639.033952746429</v>
       </c>
       <c r="HW76">
-        <v>11.58822586362554</v>
+        <v>0.08629448647000533</v>
       </c>
       <c r="HX76">
-        <v>31.95169763732145</v>
+        <v>0.03129724158480836</v>
       </c>
       <c r="HY76" t="inlineStr">
         <is>
@@ -35902,7 +36165,7 @@
         </is>
       </c>
       <c r="HZ76">
-        <v>31.2</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="IA76">
         <v>3</v>
@@ -35916,17 +36179,20 @@
         <v>1</v>
       </c>
       <c r="ID76">
-        <v>4.179236178526182</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="IE76">
-        <v>0.7541255419473551</v>
-      </c>
-      <c r="IF76" t="inlineStr">
+        <v>3.966467468140717</v>
+      </c>
+      <c r="IF76">
+        <v>0.83932445750031</v>
+      </c>
+      <c r="IG76" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG76" t="inlineStr">
+      <c r="IH76" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -35974,7 +36240,7 @@
         </is>
       </c>
       <c r="K77" s="2">
-        <v>45971.54097222222</v>
+        <v>45970.99930555555</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -36298,7 +36564,7 @@
         </is>
       </c>
       <c r="HM77" s="3">
-        <v>45971</v>
+        <v>45970</v>
       </c>
       <c r="HN77" t="inlineStr">
         <is>
@@ -36322,7 +36588,7 @@
         </is>
       </c>
       <c r="HS77">
-        <v>1762779540</v>
+        <v>1762732740</v>
       </c>
       <c r="HT77" t="inlineStr">
         <is>
@@ -36336,10 +36602,10 @@
         <v>565.618637286375</v>
       </c>
       <c r="HW77">
-        <v>5.517255633815</v>
+        <v>0.1812495317184593</v>
       </c>
       <c r="HX77">
-        <v>28.28093186431875</v>
+        <v>0.03535951378114494</v>
       </c>
       <c r="HY77" t="inlineStr">
         <is>
@@ -36347,7 +36613,7 @@
         </is>
       </c>
       <c r="HZ77">
-        <v>31.2</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="IA77">
         <v>3</v>
@@ -36361,17 +36627,20 @@
         <v>1</v>
       </c>
       <c r="ID77">
-        <v>4.179236178526182</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="IE77">
-        <v>0.7541255419473551</v>
-      </c>
-      <c r="IF77" t="inlineStr">
+        <v>3.966467468140717</v>
+      </c>
+      <c r="IF77">
+        <v>0.83932445750031</v>
+      </c>
+      <c r="IG77" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG77" t="inlineStr">
+      <c r="IH77" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -36419,7 +36688,7 @@
         </is>
       </c>
       <c r="K78" s="2">
-        <v>45971.48194444444</v>
+        <v>45970.94027777778</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -36803,7 +37072,7 @@
         </is>
       </c>
       <c r="HM78" s="3">
-        <v>45971</v>
+        <v>45970</v>
       </c>
       <c r="HN78" t="inlineStr">
         <is>
@@ -36827,7 +37096,7 @@
         </is>
       </c>
       <c r="HS78">
-        <v>1762774440</v>
+        <v>1762727640</v>
       </c>
       <c r="HT78" t="inlineStr">
         <is>
@@ -36841,10 +37110,10 @@
         <v>411.557104130868</v>
       </c>
       <c r="HW78">
-        <v>2.78311960706048</v>
+        <v>0.3593090277051356</v>
       </c>
       <c r="HX78">
-        <v>20.5778552065434</v>
+        <v>0.04859592945731377</v>
       </c>
       <c r="HY78" t="inlineStr">
         <is>
@@ -36852,7 +37121,7 @@
         </is>
       </c>
       <c r="HZ78">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="IA78">
         <v>3</v>
@@ -36866,17 +37135,20 @@
         <v>1</v>
       </c>
       <c r="ID78">
-        <v>4.179236178526182</v>
+        <v>5</v>
       </c>
       <c r="IE78">
-        <v>0.7541255419473551</v>
-      </c>
-      <c r="IF78" t="inlineStr">
+        <v>3.966467468140717</v>
+      </c>
+      <c r="IF78">
+        <v>0.83932445750031</v>
+      </c>
+      <c r="IG78" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG78" t="inlineStr">
+      <c r="IH78" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -36924,7 +37196,7 @@
         </is>
       </c>
       <c r="K79" s="2">
-        <v>45971.48194444444</v>
+        <v>45970.94027777778</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -37236,7 +37508,7 @@
         </is>
       </c>
       <c r="HM79" s="3">
-        <v>45971</v>
+        <v>45970</v>
       </c>
       <c r="HN79" t="inlineStr">
         <is>
@@ -37260,7 +37532,7 @@
         </is>
       </c>
       <c r="HS79">
-        <v>1762774440</v>
+        <v>1762727640</v>
       </c>
       <c r="HT79" t="inlineStr">
         <is>
@@ -37274,10 +37546,10 @@
         <v>393.995431341253</v>
       </c>
       <c r="HW79">
-        <v>2.05165630733588</v>
+        <v>0.4874110719346174</v>
       </c>
       <c r="HX79">
-        <v>19.69977156706265</v>
+        <v>0.05076200993477336</v>
       </c>
       <c r="HY79" t="inlineStr">
         <is>
@@ -37285,7 +37557,7 @@
         </is>
       </c>
       <c r="HZ79">
-        <v>37.2</v>
+        <v>6.2</v>
       </c>
       <c r="IA79">
         <v>3</v>
@@ -37299,17 +37571,20 @@
         <v>1</v>
       </c>
       <c r="ID79">
-        <v>4.179236178526182</v>
+        <v>6.2</v>
       </c>
       <c r="IE79">
-        <v>0.7541255419473551</v>
-      </c>
-      <c r="IF79" t="inlineStr">
+        <v>3.966467468140717</v>
+      </c>
+      <c r="IF79">
+        <v>0.83932445750031</v>
+      </c>
+      <c r="IG79" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG79" t="inlineStr">
+      <c r="IH79" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -37357,7 +37632,7 @@
         </is>
       </c>
       <c r="K80" s="2">
-        <v>45971.51111111111</v>
+        <v>45970.96944444445</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -37695,7 +37970,7 @@
         </is>
       </c>
       <c r="HM80" s="3">
-        <v>45971</v>
+        <v>45970</v>
       </c>
       <c r="HN80" t="inlineStr">
         <is>
@@ -37719,7 +37994,7 @@
         </is>
       </c>
       <c r="HS80">
-        <v>1762776960</v>
+        <v>1762730160</v>
       </c>
       <c r="HT80" t="inlineStr">
         <is>
@@ -37733,10 +38008,10 @@
         <v>187.90193049333</v>
       </c>
       <c r="HW80">
-        <v>28.5391286313226</v>
+        <v>0.03503961220814809</v>
       </c>
       <c r="HX80">
-        <v>9.395096524666501</v>
+        <v>0.1064385019754225</v>
       </c>
       <c r="HY80" t="inlineStr">
         <is>
@@ -37744,7 +38019,7 @@
         </is>
       </c>
       <c r="HZ80">
-        <v>34.2</v>
+        <v>5.699999999999999</v>
       </c>
       <c r="IA80">
         <v>3</v>
@@ -37758,17 +38033,20 @@
         <v>1</v>
       </c>
       <c r="ID80">
-        <v>4.179236178526182</v>
+        <v>5.699999999999999</v>
       </c>
       <c r="IE80">
-        <v>0.7541255419473551</v>
-      </c>
-      <c r="IF80" t="inlineStr">
+        <v>3.966467468140717</v>
+      </c>
+      <c r="IF80">
+        <v>0.83932445750031</v>
+      </c>
+      <c r="IG80" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG80" t="inlineStr">
+      <c r="IH80" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -37816,7 +38094,7 @@
         </is>
       </c>
       <c r="K81" s="2">
-        <v>45971.51111111111</v>
+        <v>45970.96944444445</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -38154,7 +38432,7 @@
         </is>
       </c>
       <c r="HM81" s="3">
-        <v>45971</v>
+        <v>45970</v>
       </c>
       <c r="HN81" t="inlineStr">
         <is>
@@ -38178,7 +38456,7 @@
         </is>
       </c>
       <c r="HS81">
-        <v>1762776960</v>
+        <v>1762730160</v>
       </c>
       <c r="HT81" t="inlineStr">
         <is>
@@ -38192,10 +38470,10 @@
         <v>153.52894194799</v>
       </c>
       <c r="HW81">
-        <v>22.5304101069624</v>
+        <v>0.04438445617512207</v>
       </c>
       <c r="HX81">
-        <v>7.6764470973995</v>
+        <v>0.1302685978698093</v>
       </c>
       <c r="HY81" t="inlineStr">
         <is>
@@ -38203,7 +38481,7 @@
         </is>
       </c>
       <c r="HZ81">
-        <v>34.2</v>
+        <v>5.699999999999999</v>
       </c>
       <c r="IA81">
         <v>3</v>
@@ -38217,17 +38495,20 @@
         <v>1</v>
       </c>
       <c r="ID81">
-        <v>4.179236178526182</v>
+        <v>5.699999999999999</v>
       </c>
       <c r="IE81">
-        <v>0.7541255419473551</v>
-      </c>
-      <c r="IF81" t="inlineStr">
+        <v>3.966467468140717</v>
+      </c>
+      <c r="IF81">
+        <v>0.83932445750031</v>
+      </c>
+      <c r="IG81" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG81" t="inlineStr">
+      <c r="IH81" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -38275,7 +38556,7 @@
         </is>
       </c>
       <c r="K82" s="2">
-        <v>46034.50833333333</v>
+        <v>46033.96666666667</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -38615,7 +38896,7 @@
         </is>
       </c>
       <c r="HM82" s="3">
-        <v>46034</v>
+        <v>46033</v>
       </c>
       <c r="HN82" t="inlineStr">
         <is>
@@ -38639,7 +38920,7 @@
         </is>
       </c>
       <c r="HS82">
-        <v>1768219920</v>
+        <v>1768173120</v>
       </c>
       <c r="HT82" t="inlineStr">
         <is>
@@ -38653,10 +38934,10 @@
         <v>164.450019734722</v>
       </c>
       <c r="HW82">
-        <v>16.59778041809964</v>
+        <v>0.06024901973697124</v>
       </c>
       <c r="HX82">
-        <v>8.222500986736099</v>
+        <v>0.121617498327227</v>
       </c>
       <c r="HY82" t="inlineStr">
         <is>
@@ -38664,7 +38945,7 @@
         </is>
       </c>
       <c r="HZ82">
-        <v>31.2</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="IA82">
         <v>4</v>
@@ -38678,17 +38959,20 @@
         <v>1</v>
       </c>
       <c r="ID82">
-        <v>5.017294318458739</v>
+        <v>5.557973333333334</v>
       </c>
       <c r="IE82">
-        <v>0.3498985595628208</v>
-      </c>
-      <c r="IF82" t="inlineStr">
+        <v>4.804525608072918</v>
+      </c>
+      <c r="IF82">
+        <v>0.453996838695637</v>
+      </c>
+      <c r="IG82" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG82" t="inlineStr">
+      <c r="IH82" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -38736,7 +39020,7 @@
         </is>
       </c>
       <c r="K83" s="2">
-        <v>46034.50833333333</v>
+        <v>46033.96666666667</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -39072,7 +39356,7 @@
         </is>
       </c>
       <c r="HM83" s="3">
-        <v>46034</v>
+        <v>46033</v>
       </c>
       <c r="HN83" t="inlineStr">
         <is>
@@ -39096,7 +39380,7 @@
         </is>
       </c>
       <c r="HS83">
-        <v>1768219920</v>
+        <v>1768173120</v>
       </c>
       <c r="HT83" t="inlineStr">
         <is>
@@ -39110,10 +39394,10 @@
         <v>180.302636624781</v>
       </c>
       <c r="HW83">
-        <v>21.0891039081872</v>
+        <v>0.04741785162392701</v>
       </c>
       <c r="HX83">
-        <v>9.015131831239049</v>
+        <v>0.1109246119435348</v>
       </c>
       <c r="HY83" t="inlineStr">
         <is>
@@ -39121,7 +39405,7 @@
         </is>
       </c>
       <c r="HZ83">
-        <v>26.4</v>
+        <v>4.4</v>
       </c>
       <c r="IA83">
         <v>4</v>
@@ -39135,17 +39419,20 @@
         <v>1</v>
       </c>
       <c r="ID83">
-        <v>5.017294318458739</v>
+        <v>4.4</v>
       </c>
       <c r="IE83">
-        <v>0.3498985595628208</v>
-      </c>
-      <c r="IF83" t="inlineStr">
+        <v>4.804525608072918</v>
+      </c>
+      <c r="IF83">
+        <v>0.453996838695637</v>
+      </c>
+      <c r="IG83" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG83" t="inlineStr">
+      <c r="IH83" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -39193,7 +39480,7 @@
         </is>
       </c>
       <c r="K84" s="2">
-        <v>46034.46805555555</v>
+        <v>46033.92638888889</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -39483,7 +39770,7 @@
         </is>
       </c>
       <c r="HM84" s="3">
-        <v>46034</v>
+        <v>46033</v>
       </c>
       <c r="HN84" t="inlineStr">
         <is>
@@ -39507,7 +39794,7 @@
         </is>
       </c>
       <c r="HS84">
-        <v>1768216440</v>
+        <v>1768169640</v>
       </c>
       <c r="HT84" t="inlineStr">
         <is>
@@ -39521,10 +39808,10 @@
         <v>1429.22107248619</v>
       </c>
       <c r="HW84">
-        <v>15.02060854953934</v>
+        <v>0.06657519878118842</v>
       </c>
       <c r="HX84">
-        <v>71.4610536243095</v>
+        <v>0.01399363638349465</v>
       </c>
       <c r="HY84" t="inlineStr">
         <is>
@@ -39532,7 +39819,7 @@
         </is>
       </c>
       <c r="HZ84">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="IA84">
         <v>4</v>
@@ -39546,17 +39833,20 @@
         <v>0</v>
       </c>
       <c r="ID84">
-        <v>5.017294318458739</v>
+        <v>3.22144</v>
       </c>
       <c r="IE84">
-        <v>0.3498985595628208</v>
-      </c>
-      <c r="IF84" t="inlineStr">
+        <v>4.804525608072918</v>
+      </c>
+      <c r="IF84">
+        <v>0.453996838695637</v>
+      </c>
+      <c r="IG84" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG84" t="inlineStr">
+      <c r="IH84" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -39604,7 +39894,7 @@
         </is>
       </c>
       <c r="K85" s="2">
-        <v>46034.46805555555</v>
+        <v>46033.92638888889</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -39915,7 +40205,7 @@
         </is>
       </c>
       <c r="HM85" s="3">
-        <v>46034</v>
+        <v>46033</v>
       </c>
       <c r="HN85" t="inlineStr">
         <is>
@@ -39939,7 +40229,7 @@
         </is>
       </c>
       <c r="HS85">
-        <v>1768216440</v>
+        <v>1768169640</v>
       </c>
       <c r="HT85" t="inlineStr">
         <is>
@@ -39953,10 +40243,10 @@
         <v>1435.7027457702</v>
       </c>
       <c r="HW85">
-        <v>14.62128427785038</v>
+        <v>0.06839344485729539</v>
       </c>
       <c r="HX85">
-        <v>71.78513728851</v>
+        <v>0.01393046022856964</v>
       </c>
       <c r="HY85" t="inlineStr">
         <is>
@@ -39964,7 +40254,7 @@
         </is>
       </c>
       <c r="HZ85">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="IA85">
         <v>4</v>
@@ -39978,17 +40268,20 @@
         <v>0</v>
       </c>
       <c r="ID85">
-        <v>5.017294318458739</v>
+        <v>3</v>
       </c>
       <c r="IE85">
-        <v>0.3498985595628208</v>
-      </c>
-      <c r="IF85" t="inlineStr">
+        <v>4.804525608072918</v>
+      </c>
+      <c r="IF85">
+        <v>0.453996838695637</v>
+      </c>
+      <c r="IG85" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG85" t="inlineStr">
+      <c r="IH85" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -40036,7 +40329,7 @@
         </is>
       </c>
       <c r="K86" s="2">
-        <v>46034.43958333333</v>
+        <v>46033.89791666667</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -40387,7 +40680,7 @@
         </is>
       </c>
       <c r="HM86" s="3">
-        <v>46034</v>
+        <v>46033</v>
       </c>
       <c r="HN86" t="inlineStr">
         <is>
@@ -40411,7 +40704,7 @@
         </is>
       </c>
       <c r="HS86">
-        <v>1768213980</v>
+        <v>1768167180</v>
       </c>
       <c r="HT86" t="inlineStr">
         <is>
@@ -40425,10 +40718,10 @@
         <v>1689.68543182272</v>
       </c>
       <c r="HW86">
-        <v>53.510285413158</v>
+        <v>0.01868799600448596</v>
       </c>
       <c r="HX86">
-        <v>84.48427159113599</v>
+        <v>0.0118365227179744</v>
       </c>
       <c r="HY86" t="inlineStr">
         <is>
@@ -40436,7 +40729,7 @@
         </is>
       </c>
       <c r="HZ86">
-        <v>14.4</v>
+        <v>2.4</v>
       </c>
       <c r="IA86">
         <v>4</v>
@@ -40450,17 +40743,20 @@
         <v>1</v>
       </c>
       <c r="ID86">
-        <v>5.017294318458739</v>
+        <v>2.66496</v>
       </c>
       <c r="IE86">
-        <v>0.3498985595628208</v>
-      </c>
-      <c r="IF86" t="inlineStr">
+        <v>4.804525608072918</v>
+      </c>
+      <c r="IF86">
+        <v>0.453996838695637</v>
+      </c>
+      <c r="IG86" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG86" t="inlineStr">
+      <c r="IH86" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -40508,7 +40804,7 @@
         </is>
       </c>
       <c r="K87" s="2">
-        <v>46034.43958333333</v>
+        <v>46033.89791666667</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -40859,7 +41155,7 @@
         </is>
       </c>
       <c r="HM87" s="3">
-        <v>46034</v>
+        <v>46033</v>
       </c>
       <c r="HN87" t="inlineStr">
         <is>
@@ -40883,7 +41179,7 @@
         </is>
       </c>
       <c r="HS87">
-        <v>1768213980</v>
+        <v>1768167180</v>
       </c>
       <c r="HT87" t="inlineStr">
         <is>
@@ -40897,18 +41193,18 @@
         <v>1741.06263130931</v>
       </c>
       <c r="HW87">
-        <v>44.1049746442002</v>
+        <v>0.022673179342401</v>
       </c>
       <c r="HX87">
-        <v>87.05313156546551</v>
+        <v>0.0114872375297376</v>
       </c>
       <c r="HY87" t="inlineStr">
         <is>
-          <t>Emergent Macrophyte</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="HZ87">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="IA87">
         <v>4</v>
@@ -40922,17 +41218,20 @@
         <v>1</v>
       </c>
       <c r="ID87">
-        <v>5.017294318458739</v>
+        <v>3</v>
       </c>
       <c r="IE87">
-        <v>0.3498985595628208</v>
-      </c>
-      <c r="IF87" t="inlineStr">
+        <v>4.804525608072918</v>
+      </c>
+      <c r="IF87">
+        <v>0.453996838695637</v>
+      </c>
+      <c r="IG87" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG87" t="inlineStr">
+      <c r="IH87" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -40980,7 +41279,7 @@
         </is>
       </c>
       <c r="K88" s="2">
-        <v>46041.42777777778</v>
+        <v>46040.88611111111</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -41361,7 +41660,7 @@
         </is>
       </c>
       <c r="HM88" s="3">
-        <v>46041</v>
+        <v>46040</v>
       </c>
       <c r="HN88" t="inlineStr">
         <is>
@@ -41385,7 +41684,7 @@
         </is>
       </c>
       <c r="HS88">
-        <v>1768817760</v>
+        <v>1768770960</v>
       </c>
       <c r="HT88" t="inlineStr">
         <is>
@@ -41399,10 +41698,10 @@
         <v>334.104864132139</v>
       </c>
       <c r="HW88">
-        <v>26.1356496959392</v>
+        <v>0.03826191472697057</v>
       </c>
       <c r="HX88">
-        <v>16.70524320660695</v>
+        <v>0.05986144515420753</v>
       </c>
       <c r="HY88" t="inlineStr">
         <is>
@@ -41410,7 +41709,7 @@
         </is>
       </c>
       <c r="HZ88">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="IA88">
         <v>4</v>
@@ -41424,17 +41723,20 @@
         <v>1</v>
       </c>
       <c r="ID88">
-        <v>0.2234899839781147</v>
+        <v>3.203733333333333</v>
       </c>
       <c r="IE88">
-        <v>0.01243505510753767</v>
-      </c>
-      <c r="IF88" t="inlineStr">
+        <v>0.01072127359265074</v>
+      </c>
+      <c r="IF88">
+        <v>2.873615160242649E-05</v>
+      </c>
+      <c r="IG88" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG88" t="inlineStr">
+      <c r="IH88" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -41482,7 +41784,7 @@
         </is>
       </c>
       <c r="K89" s="2">
-        <v>46041.42777777778</v>
+        <v>46040.88611111111</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -41797,7 +42099,7 @@
         </is>
       </c>
       <c r="HM89" s="3">
-        <v>46041</v>
+        <v>46040</v>
       </c>
       <c r="HN89" t="inlineStr">
         <is>
@@ -41821,7 +42123,7 @@
         </is>
       </c>
       <c r="HS89">
-        <v>1768817760</v>
+        <v>1768770960</v>
       </c>
       <c r="HT89" t="inlineStr">
         <is>
@@ -41835,10 +42137,10 @@
         <v>381.61439291614</v>
       </c>
       <c r="HW89">
-        <v>13.90163680253436</v>
+        <v>0.07193397541631165</v>
       </c>
       <c r="HX89">
-        <v>19.080719645807</v>
+        <v>0.05240892474512882</v>
       </c>
       <c r="HY89" t="inlineStr">
         <is>
@@ -41846,7 +42148,7 @@
         </is>
       </c>
       <c r="HZ89">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="IA89">
         <v>4</v>
@@ -41860,17 +42162,20 @@
         <v>0</v>
       </c>
       <c r="ID89">
-        <v>0.2234899839781147</v>
+        <v>3</v>
       </c>
       <c r="IE89">
-        <v>0.01243505510753767</v>
-      </c>
-      <c r="IF89" t="inlineStr">
+        <v>0.01072127359265074</v>
+      </c>
+      <c r="IF89">
+        <v>2.873615160242649E-05</v>
+      </c>
+      <c r="IG89" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG89" t="inlineStr">
+      <c r="IH89" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -41918,7 +42223,7 @@
         </is>
       </c>
       <c r="K90" s="2">
-        <v>46034.39583333333</v>
+        <v>46033.85416666667</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -42243,7 +42548,7 @@
         </is>
       </c>
       <c r="HM90" s="3">
-        <v>46034</v>
+        <v>46033</v>
       </c>
       <c r="HN90" t="inlineStr">
         <is>
@@ -42267,7 +42572,7 @@
         </is>
       </c>
       <c r="HS90">
-        <v>1768210200</v>
+        <v>1768163400</v>
       </c>
       <c r="HT90" t="inlineStr">
         <is>
@@ -42281,18 +42586,18 @@
         <v>259.826404337621</v>
       </c>
       <c r="HW90">
-        <v>33.667898204025</v>
+        <v>0.02970188379268801</v>
       </c>
       <c r="HX90">
-        <v>12.99132021688105</v>
+        <v>0.07697447090100898</v>
       </c>
       <c r="HY90" t="inlineStr">
         <is>
-          <t>Rocky</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="HZ90">
-        <v>20.1</v>
+        <v>3.35</v>
       </c>
       <c r="IA90">
         <v>4</v>
@@ -42306,17 +42611,20 @@
         <v>1</v>
       </c>
       <c r="ID90">
-        <v>5.017294318458739</v>
+        <v>3.613893333333333</v>
       </c>
       <c r="IE90">
-        <v>0.3498985595628208</v>
-      </c>
-      <c r="IF90" t="inlineStr">
+        <v>4.804525608072918</v>
+      </c>
+      <c r="IF90">
+        <v>0.453996838695637</v>
+      </c>
+      <c r="IG90" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG90" t="inlineStr">
+      <c r="IH90" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -42364,7 +42672,7 @@
         </is>
       </c>
       <c r="K91" s="2">
-        <v>46034.39583333333</v>
+        <v>46033.85416666667</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -42700,7 +43008,7 @@
         </is>
       </c>
       <c r="HM91" s="3">
-        <v>46034</v>
+        <v>46033</v>
       </c>
       <c r="HN91" t="inlineStr">
         <is>
@@ -42724,7 +43032,7 @@
         </is>
       </c>
       <c r="HS91">
-        <v>1768210200</v>
+        <v>1768163400</v>
       </c>
       <c r="HT91" t="inlineStr">
         <is>
@@ -42738,10 +43046,10 @@
         <v>221.365381729161</v>
       </c>
       <c r="HW91">
-        <v>27.7244235402752</v>
+        <v>0.03606928016185089</v>
       </c>
       <c r="HX91">
-        <v>11.06826908645805</v>
+        <v>0.09034836361391801</v>
       </c>
       <c r="HY91" t="inlineStr">
         <is>
@@ -42749,7 +43057,7 @@
         </is>
       </c>
       <c r="HZ91">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="IA91">
         <v>4</v>
@@ -42763,17 +43071,20 @@
         <v>1</v>
       </c>
       <c r="ID91">
-        <v>5.017294318458739</v>
+        <v>5</v>
       </c>
       <c r="IE91">
-        <v>0.3498985595628208</v>
-      </c>
-      <c r="IF91" t="inlineStr">
+        <v>4.804525608072918</v>
+      </c>
+      <c r="IF91">
+        <v>0.453996838695637</v>
+      </c>
+      <c r="IG91" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG91" t="inlineStr">
+      <c r="IH91" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -42821,7 +43132,7 @@
         </is>
       </c>
       <c r="K92" s="2">
-        <v>46036.48472222222</v>
+        <v>46035.94305555556</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -43175,7 +43486,7 @@
         </is>
       </c>
       <c r="HM92" s="3">
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="HN92" t="inlineStr">
         <is>
@@ -43199,7 +43510,7 @@
         </is>
       </c>
       <c r="HS92">
-        <v>1768390680</v>
+        <v>1768343880</v>
       </c>
       <c r="HT92" t="inlineStr">
         <is>
@@ -43213,10 +43524,10 @@
         <v>121.850769016352</v>
       </c>
       <c r="HW92">
-        <v>7.788448912465</v>
+        <v>0.1283952698719706</v>
       </c>
       <c r="HX92">
-        <v>6.0925384508176</v>
+        <v>0.1641351971879313</v>
       </c>
       <c r="HY92" t="inlineStr">
         <is>
@@ -43224,7 +43535,7 @@
         </is>
       </c>
       <c r="HZ92">
-        <v>39.6</v>
+        <v>6.600000000000001</v>
       </c>
       <c r="IA92">
         <v>4</v>
@@ -43238,17 +43549,20 @@
         <v>1</v>
       </c>
       <c r="ID92">
-        <v>5.442831739229667</v>
+        <v>6.600000000000001</v>
       </c>
       <c r="IE92">
-        <v>0.1664002489072092</v>
-      </c>
-      <c r="IF92" t="inlineStr">
+        <v>5.230063028844203</v>
+      </c>
+      <c r="IF92">
+        <v>0.2525698548833967</v>
+      </c>
+      <c r="IG92" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG92" t="inlineStr">
+      <c r="IH92" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -43296,7 +43610,7 @@
         </is>
       </c>
       <c r="K93" s="2">
-        <v>46036.48472222222</v>
+        <v>46035.94305555556</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -43680,7 +43994,7 @@
         </is>
       </c>
       <c r="HM93" s="3">
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="HN93" t="inlineStr">
         <is>
@@ -43704,7 +44018,7 @@
         </is>
       </c>
       <c r="HS93">
-        <v>1768390680</v>
+        <v>1768343880</v>
       </c>
       <c r="HT93" t="inlineStr">
         <is>
@@ -43718,10 +44032,10 @@
         <v>162.050124796368</v>
       </c>
       <c r="HW93">
-        <v>14.18372682915204</v>
+        <v>0.07050333188486711</v>
       </c>
       <c r="HX93">
-        <v>8.1025062398184</v>
+        <v>0.1234186028868042</v>
       </c>
       <c r="HY93" t="inlineStr">
         <is>
@@ -43729,7 +44043,7 @@
         </is>
       </c>
       <c r="HZ93">
-        <v>37.2</v>
+        <v>6.2</v>
       </c>
       <c r="IA93">
         <v>4</v>
@@ -43743,17 +44057,20 @@
         <v>1</v>
       </c>
       <c r="ID93">
-        <v>5.442831739229667</v>
+        <v>6.2</v>
       </c>
       <c r="IE93">
-        <v>0.1664002489072092</v>
-      </c>
-      <c r="IF93" t="inlineStr">
+        <v>5.230063028844203</v>
+      </c>
+      <c r="IF93">
+        <v>0.2525698548833967</v>
+      </c>
+      <c r="IG93" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG93" t="inlineStr">
+      <c r="IH93" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -43801,7 +44118,7 @@
         </is>
       </c>
       <c r="K94" s="2">
-        <v>46036.43263888889</v>
+        <v>46035.89097222222</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -44113,7 +44430,7 @@
         </is>
       </c>
       <c r="HM94" s="3">
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="HN94" t="inlineStr">
         <is>
@@ -44137,7 +44454,7 @@
         </is>
       </c>
       <c r="HS94">
-        <v>1768386180</v>
+        <v>1768339380</v>
       </c>
       <c r="HT94" t="inlineStr">
         <is>
@@ -44151,18 +44468,18 @@
         <v>218.544411001867</v>
       </c>
       <c r="HW94">
-        <v>12.66700316387234</v>
+        <v>0.07894527119501382</v>
       </c>
       <c r="HX94">
-        <v>10.92722055009335</v>
+        <v>0.09151458007237322</v>
       </c>
       <c r="HY94" t="inlineStr">
         <is>
-          <t>Rocky</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="HZ94">
-        <v>21.6</v>
+        <v>3.6</v>
       </c>
       <c r="IA94">
         <v>4</v>
@@ -44176,17 +44493,20 @@
         <v>0</v>
       </c>
       <c r="ID94">
-        <v>5.442831739229667</v>
+        <v>3.6</v>
       </c>
       <c r="IE94">
-        <v>0.1664002489072092</v>
-      </c>
-      <c r="IF94" t="inlineStr">
+        <v>5.230063028844203</v>
+      </c>
+      <c r="IF94">
+        <v>0.2525698548833967</v>
+      </c>
+      <c r="IG94" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG94" t="inlineStr">
+      <c r="IH94" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -44234,7 +44554,7 @@
         </is>
       </c>
       <c r="K95" s="2">
-        <v>46036.43263888889</v>
+        <v>46035.89097222222</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -44546,7 +44866,7 @@
         </is>
       </c>
       <c r="HM95" s="3">
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="HN95" t="inlineStr">
         <is>
@@ -44570,7 +44890,7 @@
         </is>
       </c>
       <c r="HS95">
-        <v>1768386180</v>
+        <v>1768339380</v>
       </c>
       <c r="HT95" t="inlineStr">
         <is>
@@ -44584,18 +44904,18 @@
         <v>183.129609879407</v>
       </c>
       <c r="HW95">
-        <v>11.9760957338734</v>
+        <v>0.08349966652083303</v>
       </c>
       <c r="HX95">
-        <v>9.156480493970351</v>
+        <v>0.1092122678204264</v>
       </c>
       <c r="HY95" t="inlineStr">
         <is>
-          <t>Rocky</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="HZ95">
-        <v>21</v>
+        <v>3.5</v>
       </c>
       <c r="IA95">
         <v>4</v>
@@ -44609,17 +44929,20 @@
         <v>1</v>
       </c>
       <c r="ID95">
-        <v>5.442831739229667</v>
+        <v>3.5</v>
       </c>
       <c r="IE95">
-        <v>0.1664002489072092</v>
-      </c>
-      <c r="IF95" t="inlineStr">
+        <v>5.230063028844203</v>
+      </c>
+      <c r="IF95">
+        <v>0.2525698548833967</v>
+      </c>
+      <c r="IG95" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG95" t="inlineStr">
+      <c r="IH95" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -44667,7 +44990,7 @@
         </is>
       </c>
       <c r="K96" s="2">
-        <v>46036.41388888888</v>
+        <v>46035.87222222222</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -45005,7 +45328,7 @@
         </is>
       </c>
       <c r="HM96" s="3">
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="HN96" t="inlineStr">
         <is>
@@ -45029,7 +45352,7 @@
         </is>
       </c>
       <c r="HS96">
-        <v>1768384560</v>
+        <v>1768337760</v>
       </c>
       <c r="HT96" t="inlineStr">
         <is>
@@ -45043,10 +45366,10 @@
         <v>639.033952746429</v>
       </c>
       <c r="HW96">
-        <v>11.58822586362554</v>
+        <v>0.08629448647000533</v>
       </c>
       <c r="HX96">
-        <v>31.95169763732145</v>
+        <v>0.03129724158480836</v>
       </c>
       <c r="HY96" t="inlineStr">
         <is>
@@ -45054,7 +45377,7 @@
         </is>
       </c>
       <c r="HZ96">
-        <v>31.2</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="IA96">
         <v>4</v>
@@ -45068,17 +45391,20 @@
         <v>1</v>
       </c>
       <c r="ID96">
-        <v>5.442831739229667</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="IE96">
-        <v>0.1664002489072092</v>
-      </c>
-      <c r="IF96" t="inlineStr">
+        <v>5.230063028844203</v>
+      </c>
+      <c r="IF96">
+        <v>0.2525698548833967</v>
+      </c>
+      <c r="IG96" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG96" t="inlineStr">
+      <c r="IH96" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -45126,7 +45452,7 @@
         </is>
       </c>
       <c r="K97" s="2">
-        <v>46036.41388888888</v>
+        <v>46035.87222222222</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -45525,7 +45851,7 @@
         </is>
       </c>
       <c r="HM97" s="3">
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="HN97" t="inlineStr">
         <is>
@@ -45549,7 +45875,7 @@
         </is>
       </c>
       <c r="HS97">
-        <v>1768384560</v>
+        <v>1768337760</v>
       </c>
       <c r="HT97" t="inlineStr">
         <is>
@@ -45563,10 +45889,10 @@
         <v>565.618637286375</v>
       </c>
       <c r="HW97">
-        <v>5.517255633815</v>
+        <v>0.1812495317184593</v>
       </c>
       <c r="HX97">
-        <v>28.28093186431875</v>
+        <v>0.03535951378114494</v>
       </c>
       <c r="HY97" t="inlineStr">
         <is>
@@ -45574,7 +45900,7 @@
         </is>
       </c>
       <c r="HZ97">
-        <v>31.2</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="IA97">
         <v>4</v>
@@ -45588,17 +45914,20 @@
         <v>1</v>
       </c>
       <c r="ID97">
-        <v>5.442831739229667</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="IE97">
-        <v>0.1664002489072092</v>
-      </c>
-      <c r="IF97" t="inlineStr">
+        <v>5.230063028844203</v>
+      </c>
+      <c r="IF97">
+        <v>0.2525698548833967</v>
+      </c>
+      <c r="IG97" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG97" t="inlineStr">
+      <c r="IH97" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -45646,7 +45975,7 @@
         </is>
       </c>
       <c r="K98" s="2">
-        <v>46036.45486111111</v>
+        <v>46035.91319444445</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -45988,7 +46317,7 @@
         </is>
       </c>
       <c r="HM98" s="3">
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="HN98" t="inlineStr">
         <is>
@@ -46012,7 +46341,7 @@
         </is>
       </c>
       <c r="HS98">
-        <v>1768388100</v>
+        <v>1768341300</v>
       </c>
       <c r="HT98" t="inlineStr">
         <is>
@@ -46026,10 +46355,10 @@
         <v>411.557104130868</v>
       </c>
       <c r="HW98">
-        <v>2.78311960706048</v>
+        <v>0.3593090277051356</v>
       </c>
       <c r="HX98">
-        <v>20.5778552065434</v>
+        <v>0.04859592945731377</v>
       </c>
       <c r="HY98" t="inlineStr">
         <is>
@@ -46037,7 +46366,7 @@
         </is>
       </c>
       <c r="HZ98">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="IA98">
         <v>4</v>
@@ -46051,17 +46380,20 @@
         <v>1</v>
       </c>
       <c r="ID98">
-        <v>5.442831739229667</v>
+        <v>5</v>
       </c>
       <c r="IE98">
-        <v>0.1664002489072092</v>
-      </c>
-      <c r="IF98" t="inlineStr">
+        <v>5.230063028844203</v>
+      </c>
+      <c r="IF98">
+        <v>0.2525698548833967</v>
+      </c>
+      <c r="IG98" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG98" t="inlineStr">
+      <c r="IH98" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -46109,7 +46441,7 @@
         </is>
       </c>
       <c r="K99" s="2">
-        <v>46036.45486111111</v>
+        <v>46035.91319444445</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -46451,7 +46783,7 @@
         </is>
       </c>
       <c r="HM99" s="3">
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="HN99" t="inlineStr">
         <is>
@@ -46475,7 +46807,7 @@
         </is>
       </c>
       <c r="HS99">
-        <v>1768388100</v>
+        <v>1768341300</v>
       </c>
       <c r="HT99" t="inlineStr">
         <is>
@@ -46489,10 +46821,10 @@
         <v>393.995431341253</v>
       </c>
       <c r="HW99">
-        <v>2.05165630733588</v>
+        <v>0.4874110719346174</v>
       </c>
       <c r="HX99">
-        <v>19.69977156706265</v>
+        <v>0.05076200993477336</v>
       </c>
       <c r="HY99" t="inlineStr">
         <is>
@@ -46500,7 +46832,7 @@
         </is>
       </c>
       <c r="HZ99">
-        <v>37.2</v>
+        <v>6.2</v>
       </c>
       <c r="IA99">
         <v>4</v>
@@ -46514,17 +46846,20 @@
         <v>1</v>
       </c>
       <c r="ID99">
-        <v>5.442831739229667</v>
+        <v>6.2</v>
       </c>
       <c r="IE99">
-        <v>0.1664002489072092</v>
-      </c>
-      <c r="IF99" t="inlineStr">
+        <v>5.230063028844203</v>
+      </c>
+      <c r="IF99">
+        <v>0.2525698548833967</v>
+      </c>
+      <c r="IG99" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG99" t="inlineStr">
+      <c r="IH99" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -46572,7 +46907,7 @@
         </is>
       </c>
       <c r="K100" s="2">
-        <v>46036.47708333333</v>
+        <v>46035.93541666667</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -46901,7 +47236,7 @@
         </is>
       </c>
       <c r="HM100" s="3">
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="HN100" t="inlineStr">
         <is>
@@ -46925,7 +47260,7 @@
         </is>
       </c>
       <c r="HS100">
-        <v>1768390020</v>
+        <v>1768343220</v>
       </c>
       <c r="HT100" t="inlineStr">
         <is>
@@ -46939,10 +47274,10 @@
         <v>187.90193049333</v>
       </c>
       <c r="HW100">
-        <v>28.5391286313226</v>
+        <v>0.03503961220814809</v>
       </c>
       <c r="HX100">
-        <v>9.395096524666501</v>
+        <v>0.1064385019754225</v>
       </c>
       <c r="HY100" t="inlineStr">
         <is>
@@ -46950,7 +47285,7 @@
         </is>
       </c>
       <c r="HZ100">
-        <v>34.2</v>
+        <v>5.699999999999999</v>
       </c>
       <c r="IA100">
         <v>4</v>
@@ -46964,17 +47299,20 @@
         <v>1</v>
       </c>
       <c r="ID100">
-        <v>5.442831739229667</v>
+        <v>5.699999999999999</v>
       </c>
       <c r="IE100">
-        <v>0.1664002489072092</v>
-      </c>
-      <c r="IF100" t="inlineStr">
+        <v>5.230063028844203</v>
+      </c>
+      <c r="IF100">
+        <v>0.2525698548833967</v>
+      </c>
+      <c r="IG100" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG100" t="inlineStr">
+      <c r="IH100" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -47022,7 +47360,7 @@
         </is>
       </c>
       <c r="K101" s="2">
-        <v>46036.47708333333</v>
+        <v>46035.93541666667</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -47321,7 +47659,7 @@
         </is>
       </c>
       <c r="HM101" s="3">
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="HN101" t="inlineStr">
         <is>
@@ -47345,7 +47683,7 @@
         </is>
       </c>
       <c r="HS101">
-        <v>1768390020</v>
+        <v>1768343220</v>
       </c>
       <c r="HT101" t="inlineStr">
         <is>
@@ -47359,10 +47697,10 @@
         <v>153.52894194799</v>
       </c>
       <c r="HW101">
-        <v>22.5304101069624</v>
+        <v>0.04438445617512207</v>
       </c>
       <c r="HX101">
-        <v>7.6764470973995</v>
+        <v>0.1302685978698093</v>
       </c>
       <c r="HY101" t="inlineStr">
         <is>
@@ -47370,7 +47708,7 @@
         </is>
       </c>
       <c r="HZ101">
-        <v>34.2</v>
+        <v>5.699999999999999</v>
       </c>
       <c r="IA101">
         <v>4</v>
@@ -47384,17 +47722,20 @@
         <v>1</v>
       </c>
       <c r="ID101">
-        <v>5.442831739229667</v>
+        <v>5.699999999999999</v>
       </c>
       <c r="IE101">
-        <v>0.1664002489072092</v>
-      </c>
-      <c r="IF101" t="inlineStr">
+        <v>5.230063028844203</v>
+      </c>
+      <c r="IF101">
+        <v>0.2525698548833967</v>
+      </c>
+      <c r="IG101" t="inlineStr">
         <is>
           <t>Waning</t>
         </is>
       </c>
-      <c r="IG101" t="inlineStr">
+      <c r="IH101" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -47442,7 +47783,7 @@
         </is>
       </c>
       <c r="K102" s="2">
-        <v>46134.57638888889</v>
+        <v>46134.07638888889</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -47782,7 +48123,7 @@
         </is>
       </c>
       <c r="HS102">
-        <v>1776865800</v>
+        <v>1776822600</v>
       </c>
       <c r="HT102" t="inlineStr">
         <is>
@@ -47796,10 +48137,10 @@
         <v>164.450019734722</v>
       </c>
       <c r="HW102">
-        <v>16.59778041809964</v>
+        <v>0.06024901973697124</v>
       </c>
       <c r="HX102">
-        <v>8.222500986736099</v>
+        <v>0.121617498327227</v>
       </c>
       <c r="HY102" t="inlineStr">
         <is>
@@ -47807,7 +48148,7 @@
         </is>
       </c>
       <c r="HZ102">
-        <v>31.2</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="IA102">
         <v>5</v>
@@ -47821,17 +48162,20 @@
         <v>1</v>
       </c>
       <c r="ID102">
+        <v>5.557973333333334</v>
+      </c>
+      <c r="IE102">
         <v>1.161424128298219</v>
       </c>
-      <c r="IE102">
+      <c r="IF102">
         <v>0.3009832601809674</v>
       </c>
-      <c r="IF102" t="inlineStr">
+      <c r="IG102" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG102" t="inlineStr">
+      <c r="IH102" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -47879,7 +48223,7 @@
         </is>
       </c>
       <c r="K103" s="2">
-        <v>46134.57638888889</v>
+        <v>46134.07638888889</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -48209,7 +48553,7 @@
         </is>
       </c>
       <c r="HS103">
-        <v>1776865800</v>
+        <v>1776822600</v>
       </c>
       <c r="HT103" t="inlineStr">
         <is>
@@ -48223,10 +48567,10 @@
         <v>180.302636624781</v>
       </c>
       <c r="HW103">
-        <v>21.0891039081872</v>
+        <v>0.04741785162392701</v>
       </c>
       <c r="HX103">
-        <v>9.015131831239049</v>
+        <v>0.1109246119435348</v>
       </c>
       <c r="HY103" t="inlineStr">
         <is>
@@ -48234,7 +48578,7 @@
         </is>
       </c>
       <c r="HZ103">
-        <v>26.4</v>
+        <v>4.4</v>
       </c>
       <c r="IA103">
         <v>5</v>
@@ -48248,17 +48592,20 @@
         <v>0</v>
       </c>
       <c r="ID103">
+        <v>4.4</v>
+      </c>
+      <c r="IE103">
         <v>1.161424128298219</v>
       </c>
-      <c r="IE103">
+      <c r="IF103">
         <v>0.3009832601809674</v>
       </c>
-      <c r="IF103" t="inlineStr">
+      <c r="IG103" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG103" t="inlineStr">
+      <c r="IH103" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -48306,7 +48653,7 @@
         </is>
       </c>
       <c r="K104" s="2">
-        <v>46134.50555555556</v>
+        <v>46134.00555555556</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -48686,7 +49033,7 @@
         </is>
       </c>
       <c r="HS104">
-        <v>1776859680</v>
+        <v>1776816480</v>
       </c>
       <c r="HT104" t="inlineStr">
         <is>
@@ -48700,10 +49047,10 @@
         <v>1429.22107248619</v>
       </c>
       <c r="HW104">
-        <v>15.02060854953934</v>
+        <v>0.06657519878118842</v>
       </c>
       <c r="HX104">
-        <v>71.4610536243095</v>
+        <v>0.01399363638349465</v>
       </c>
       <c r="HY104" t="inlineStr">
         <is>
@@ -48711,7 +49058,7 @@
         </is>
       </c>
       <c r="HZ104">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="IA104">
         <v>5</v>
@@ -48725,17 +49072,20 @@
         <v>1</v>
       </c>
       <c r="ID104">
+        <v>3.22144</v>
+      </c>
+      <c r="IE104">
         <v>1.161424128298219</v>
       </c>
-      <c r="IE104">
+      <c r="IF104">
         <v>0.3009832601809674</v>
       </c>
-      <c r="IF104" t="inlineStr">
+      <c r="IG104" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG104" t="inlineStr">
+      <c r="IH104" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -48783,7 +49133,7 @@
         </is>
       </c>
       <c r="K105" s="2">
-        <v>46134.50555555556</v>
+        <v>46134.00555555556</v>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -49133,7 +49483,7 @@
         </is>
       </c>
       <c r="HS105">
-        <v>1776859680</v>
+        <v>1776816480</v>
       </c>
       <c r="HT105" t="inlineStr">
         <is>
@@ -49147,10 +49497,10 @@
         <v>1435.7027457702</v>
       </c>
       <c r="HW105">
-        <v>14.62128427785038</v>
+        <v>0.06839344485729539</v>
       </c>
       <c r="HX105">
-        <v>71.78513728851</v>
+        <v>0.01393046022856964</v>
       </c>
       <c r="HY105" t="inlineStr">
         <is>
@@ -49158,7 +49508,7 @@
         </is>
       </c>
       <c r="HZ105">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="IA105">
         <v>5</v>
@@ -49172,17 +49522,20 @@
         <v>1</v>
       </c>
       <c r="ID105">
+        <v>3</v>
+      </c>
+      <c r="IE105">
         <v>1.161424128298219</v>
       </c>
-      <c r="IE105">
+      <c r="IF105">
         <v>0.3009832601809674</v>
       </c>
-      <c r="IF105" t="inlineStr">
+      <c r="IG105" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG105" t="inlineStr">
+      <c r="IH105" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -49230,7 +49583,7 @@
         </is>
       </c>
       <c r="K106" s="2">
-        <v>46134.47013888889</v>
+        <v>46133.97013888889</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -49581,7 +49934,7 @@
         </is>
       </c>
       <c r="HM106" s="3">
-        <v>46134</v>
+        <v>46133</v>
       </c>
       <c r="HN106" t="inlineStr">
         <is>
@@ -49605,7 +49958,7 @@
         </is>
       </c>
       <c r="HS106">
-        <v>1776856620</v>
+        <v>1776813420</v>
       </c>
       <c r="HT106" t="inlineStr">
         <is>
@@ -49619,10 +49972,10 @@
         <v>1689.68543182272</v>
       </c>
       <c r="HW106">
-        <v>53.510285413158</v>
+        <v>0.01868799600448596</v>
       </c>
       <c r="HX106">
-        <v>84.48427159113599</v>
+        <v>0.0118365227179744</v>
       </c>
       <c r="HY106" t="inlineStr">
         <is>
@@ -49630,7 +49983,7 @@
         </is>
       </c>
       <c r="HZ106">
-        <v>14.4</v>
+        <v>2.4</v>
       </c>
       <c r="IA106">
         <v>5</v>
@@ -49644,17 +49997,20 @@
         <v>1</v>
       </c>
       <c r="ID106">
-        <v>1.161424128298219</v>
+        <v>2.66496</v>
       </c>
       <c r="IE106">
-        <v>0.3009832601809674</v>
-      </c>
-      <c r="IF106" t="inlineStr">
+        <v>0.9486554179127552</v>
+      </c>
+      <c r="IF106">
+        <v>0.2086118663805391</v>
+      </c>
+      <c r="IG106" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG106" t="inlineStr">
+      <c r="IH106" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -49702,7 +50058,7 @@
         </is>
       </c>
       <c r="K107" s="2">
-        <v>46134.47013888889</v>
+        <v>46133.97013888889</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -49998,7 +50354,7 @@
         </is>
       </c>
       <c r="HM107" s="3">
-        <v>46134</v>
+        <v>46133</v>
       </c>
       <c r="HN107" t="inlineStr">
         <is>
@@ -50022,7 +50378,7 @@
         </is>
       </c>
       <c r="HS107">
-        <v>1776856620</v>
+        <v>1776813420</v>
       </c>
       <c r="HT107" t="inlineStr">
         <is>
@@ -50036,18 +50392,18 @@
         <v>1741.06263130931</v>
       </c>
       <c r="HW107">
-        <v>44.1049746442002</v>
+        <v>0.022673179342401</v>
       </c>
       <c r="HX107">
-        <v>87.05313156546551</v>
+        <v>0.0114872375297376</v>
       </c>
       <c r="HY107" t="inlineStr">
         <is>
-          <t>Emergent Macrophyte</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="HZ107">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="IA107">
         <v>5</v>
@@ -50061,17 +50417,20 @@
         <v>0</v>
       </c>
       <c r="ID107">
-        <v>1.161424128298219</v>
+        <v>3</v>
       </c>
       <c r="IE107">
-        <v>0.3009832601809674</v>
-      </c>
-      <c r="IF107" t="inlineStr">
+        <v>0.9486554179127552</v>
+      </c>
+      <c r="IF107">
+        <v>0.2086118663805391</v>
+      </c>
+      <c r="IG107" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG107" t="inlineStr">
+      <c r="IH107" t="inlineStr">
         <is>
           <t>compromised</t>
         </is>
@@ -50119,7 +50478,7 @@
         </is>
       </c>
       <c r="K108" s="2">
-        <v>46134.53888888888</v>
+        <v>46134.03888888888</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -50494,7 +50853,7 @@
         </is>
       </c>
       <c r="HS108">
-        <v>1776862560</v>
+        <v>1776819360</v>
       </c>
       <c r="HT108" t="inlineStr">
         <is>
@@ -50508,10 +50867,10 @@
         <v>334.104864132139</v>
       </c>
       <c r="HW108">
-        <v>26.1356496959392</v>
+        <v>0.03826191472697057</v>
       </c>
       <c r="HX108">
-        <v>16.70524320660695</v>
+        <v>0.05986144515420753</v>
       </c>
       <c r="HY108" t="inlineStr">
         <is>
@@ -50519,7 +50878,7 @@
         </is>
       </c>
       <c r="HZ108">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="IA108">
         <v>5</v>
@@ -50533,17 +50892,20 @@
         <v>1</v>
       </c>
       <c r="ID108">
+        <v>3.203733333333333</v>
+      </c>
+      <c r="IE108">
         <v>1.161424128298219</v>
       </c>
-      <c r="IE108">
+      <c r="IF108">
         <v>0.3009832601809674</v>
       </c>
-      <c r="IF108" t="inlineStr">
+      <c r="IG108" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG108" t="inlineStr">
+      <c r="IH108" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -50591,7 +50953,7 @@
         </is>
       </c>
       <c r="K109" s="2">
-        <v>46134.53888888888</v>
+        <v>46134.03888888888</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -50900,7 +51262,7 @@
         </is>
       </c>
       <c r="HS109">
-        <v>1776862560</v>
+        <v>1776819360</v>
       </c>
       <c r="HT109" t="inlineStr">
         <is>
@@ -50914,10 +51276,10 @@
         <v>381.61439291614</v>
       </c>
       <c r="HW109">
-        <v>13.90163680253436</v>
+        <v>0.07193397541631165</v>
       </c>
       <c r="HX109">
-        <v>19.080719645807</v>
+        <v>0.05240892474512882</v>
       </c>
       <c r="HY109" t="inlineStr">
         <is>
@@ -50925,7 +51287,7 @@
         </is>
       </c>
       <c r="HZ109">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="IA109">
         <v>5</v>
@@ -50939,17 +51301,20 @@
         <v>0</v>
       </c>
       <c r="ID109">
+        <v>3</v>
+      </c>
+      <c r="IE109">
         <v>1.161424128298219</v>
       </c>
-      <c r="IE109">
+      <c r="IF109">
         <v>0.3009832601809674</v>
       </c>
-      <c r="IF109" t="inlineStr">
+      <c r="IG109" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG109" t="inlineStr">
+      <c r="IH109" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -50997,7 +51362,7 @@
         </is>
       </c>
       <c r="K110" s="2">
-        <v>46134.42569444445</v>
+        <v>46133.92569444445</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -51343,7 +51708,7 @@
         </is>
       </c>
       <c r="HM110" s="3">
-        <v>46134</v>
+        <v>46133</v>
       </c>
       <c r="HN110" t="inlineStr">
         <is>
@@ -51367,7 +51732,7 @@
         </is>
       </c>
       <c r="HS110">
-        <v>1776852780</v>
+        <v>1776809580</v>
       </c>
       <c r="HT110" t="inlineStr">
         <is>
@@ -51381,18 +51746,18 @@
         <v>259.826404337621</v>
       </c>
       <c r="HW110">
-        <v>33.667898204025</v>
+        <v>0.02970188379268801</v>
       </c>
       <c r="HX110">
-        <v>12.99132021688105</v>
+        <v>0.07697447090100898</v>
       </c>
       <c r="HY110" t="inlineStr">
         <is>
-          <t>Rocky</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="HZ110">
-        <v>20.1</v>
+        <v>3.35</v>
       </c>
       <c r="IA110">
         <v>5</v>
@@ -51406,17 +51771,20 @@
         <v>1</v>
       </c>
       <c r="ID110">
-        <v>1.161424128298219</v>
+        <v>3.613893333333333</v>
       </c>
       <c r="IE110">
-        <v>0.3009832601809674</v>
-      </c>
-      <c r="IF110" t="inlineStr">
+        <v>0.9486554179127552</v>
+      </c>
+      <c r="IF110">
+        <v>0.2086118663805391</v>
+      </c>
+      <c r="IG110" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG110" t="inlineStr">
+      <c r="IH110" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -51464,7 +51832,7 @@
         </is>
       </c>
       <c r="K111" s="2">
-        <v>46134.42569444445</v>
+        <v>46133.92569444445</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -51785,7 +52153,7 @@
         </is>
       </c>
       <c r="HM111" s="3">
-        <v>46134</v>
+        <v>46133</v>
       </c>
       <c r="HN111" t="inlineStr">
         <is>
@@ -51809,7 +52177,7 @@
         </is>
       </c>
       <c r="HS111">
-        <v>1776852780</v>
+        <v>1776809580</v>
       </c>
       <c r="HT111" t="inlineStr">
         <is>
@@ -51823,10 +52191,10 @@
         <v>221.365381729161</v>
       </c>
       <c r="HW111">
-        <v>27.7244235402752</v>
+        <v>0.03606928016185089</v>
       </c>
       <c r="HX111">
-        <v>11.06826908645805</v>
+        <v>0.09034836361391801</v>
       </c>
       <c r="HY111" t="inlineStr">
         <is>
@@ -51834,7 +52202,7 @@
         </is>
       </c>
       <c r="HZ111">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="IA111">
         <v>5</v>
@@ -51848,17 +52216,20 @@
         <v>1</v>
       </c>
       <c r="ID111">
-        <v>1.161424128298219</v>
+        <v>5</v>
       </c>
       <c r="IE111">
-        <v>0.3009832601809674</v>
-      </c>
-      <c r="IF111" t="inlineStr">
+        <v>0.9486554179127552</v>
+      </c>
+      <c r="IF111">
+        <v>0.2086118663805391</v>
+      </c>
+      <c r="IG111" t="inlineStr">
         <is>
           <t>Waxing</t>
         </is>
       </c>
-      <c r="IG111" t="inlineStr">
+      <c r="IH111" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -51906,7 +52277,7 @@
         </is>
       </c>
       <c r="K112" s="2">
-        <v>46132.62430555555</v>
+        <v>46132.12430555555</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -52323,7 +52694,7 @@
         </is>
       </c>
       <c r="HS112">
-        <v>1776697140</v>
+        <v>1776653940</v>
       </c>
       <c r="HT112" t="inlineStr">
         <is>
@@ -52337,10 +52708,10 @@
         <v>121.850769016352</v>
       </c>
       <c r="HW112">
-        <v>7.788448912465</v>
+        <v>0.1283952698719706</v>
       </c>
       <c r="HX112">
-        <v>6.0925384508176</v>
+        <v>0.1641351971879313</v>
       </c>
       <c r="HY112" t="inlineStr">
         <is>
@@ -52348,7 +52719,7 @@
         </is>
       </c>
       <c r="HZ112">
-        <v>39.6</v>
+        <v>6.600000000000001</v>
       </c>
       <c r="IA112">
         <v>5</v>
@@ -52362,17 +52733,20 @@
         <v>1</v>
       </c>
       <c r="ID112">
+        <v>6.600000000000001</v>
+      </c>
+      <c r="IE112">
         <v>0.7358867075269341</v>
       </c>
-      <c r="IE112">
+      <c r="IF112">
         <v>0.1293820764152031</v>
       </c>
-      <c r="IF112" t="inlineStr">
+      <c r="IG112" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG112" t="inlineStr">
+      <c r="IH112" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -52420,7 +52794,7 @@
         </is>
       </c>
       <c r="K113" s="2">
-        <v>46132.62430555555</v>
+        <v>46132.12430555555</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -52807,7 +53181,7 @@
         </is>
       </c>
       <c r="HS113">
-        <v>1776697140</v>
+        <v>1776653940</v>
       </c>
       <c r="HT113" t="inlineStr">
         <is>
@@ -52821,10 +53195,10 @@
         <v>162.050124796368</v>
       </c>
       <c r="HW113">
-        <v>14.18372682915204</v>
+        <v>0.07050333188486711</v>
       </c>
       <c r="HX113">
-        <v>8.1025062398184</v>
+        <v>0.1234186028868042</v>
       </c>
       <c r="HY113" t="inlineStr">
         <is>
@@ -52832,7 +53206,7 @@
         </is>
       </c>
       <c r="HZ113">
-        <v>37.2</v>
+        <v>6.2</v>
       </c>
       <c r="IA113">
         <v>5</v>
@@ -52846,17 +53220,20 @@
         <v>1</v>
       </c>
       <c r="ID113">
+        <v>6.2</v>
+      </c>
+      <c r="IE113">
         <v>0.7358867075269341</v>
       </c>
-      <c r="IE113">
+      <c r="IF113">
         <v>0.1293820764152031</v>
       </c>
-      <c r="IF113" t="inlineStr">
+      <c r="IG113" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG113" t="inlineStr">
+      <c r="IH113" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -52904,7 +53281,7 @@
         </is>
       </c>
       <c r="K114" s="2">
-        <v>46132.58125</v>
+        <v>46132.08125</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -53222,7 +53599,7 @@
         </is>
       </c>
       <c r="HS114">
-        <v>1776693420</v>
+        <v>1776650220</v>
       </c>
       <c r="HT114" t="inlineStr">
         <is>
@@ -53236,18 +53613,18 @@
         <v>218.544411001867</v>
       </c>
       <c r="HW114">
-        <v>12.66700316387234</v>
+        <v>0.07894527119501382</v>
       </c>
       <c r="HX114">
-        <v>10.92722055009335</v>
+        <v>0.09151458007237322</v>
       </c>
       <c r="HY114" t="inlineStr">
         <is>
-          <t>Rocky</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="HZ114">
-        <v>21.6</v>
+        <v>3.6</v>
       </c>
       <c r="IA114">
         <v>5</v>
@@ -53261,17 +53638,20 @@
         <v>0</v>
       </c>
       <c r="ID114">
+        <v>3.6</v>
+      </c>
+      <c r="IE114">
         <v>0.7358867075269341</v>
       </c>
-      <c r="IE114">
+      <c r="IF114">
         <v>0.1293820764152031</v>
       </c>
-      <c r="IF114" t="inlineStr">
+      <c r="IG114" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG114" t="inlineStr">
+      <c r="IH114" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -53319,7 +53699,7 @@
         </is>
       </c>
       <c r="K115" s="2">
-        <v>46132.58125</v>
+        <v>46132.08125</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -53637,7 +54017,7 @@
         </is>
       </c>
       <c r="HS115">
-        <v>1776693420</v>
+        <v>1776650220</v>
       </c>
       <c r="HT115" t="inlineStr">
         <is>
@@ -53651,18 +54031,18 @@
         <v>183.129609879407</v>
       </c>
       <c r="HW115">
-        <v>11.9760957338734</v>
+        <v>0.08349966652083303</v>
       </c>
       <c r="HX115">
-        <v>9.156480493970351</v>
+        <v>0.1092122678204264</v>
       </c>
       <c r="HY115" t="inlineStr">
         <is>
-          <t>Rocky</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="HZ115">
-        <v>21</v>
+        <v>3.5</v>
       </c>
       <c r="IA115">
         <v>5</v>
@@ -53676,17 +54056,20 @@
         <v>0</v>
       </c>
       <c r="ID115">
+        <v>3.5</v>
+      </c>
+      <c r="IE115">
         <v>0.7358867075269341</v>
       </c>
-      <c r="IE115">
+      <c r="IF115">
         <v>0.1293820764152031</v>
       </c>
-      <c r="IF115" t="inlineStr">
+      <c r="IG115" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG115" t="inlineStr">
+      <c r="IH115" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -53734,7 +54117,7 @@
         </is>
       </c>
       <c r="K116" s="2">
-        <v>46132.56875</v>
+        <v>46132.06875</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -54117,7 +54500,7 @@
         </is>
       </c>
       <c r="HS116">
-        <v>1776692340</v>
+        <v>1776649140</v>
       </c>
       <c r="HT116" t="inlineStr">
         <is>
@@ -54131,10 +54514,10 @@
         <v>639.033952746429</v>
       </c>
       <c r="HW116">
-        <v>11.58822586362554</v>
+        <v>0.08629448647000533</v>
       </c>
       <c r="HX116">
-        <v>31.95169763732145</v>
+        <v>0.03129724158480836</v>
       </c>
       <c r="HY116" t="inlineStr">
         <is>
@@ -54142,7 +54525,7 @@
         </is>
       </c>
       <c r="HZ116">
-        <v>31.2</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="IA116">
         <v>5</v>
@@ -54156,17 +54539,20 @@
         <v>1</v>
       </c>
       <c r="ID116">
+        <v>5.199999999999999</v>
+      </c>
+      <c r="IE116">
         <v>0.7358867075269341</v>
       </c>
-      <c r="IE116">
+      <c r="IF116">
         <v>0.1293820764152031</v>
       </c>
-      <c r="IF116" t="inlineStr">
+      <c r="IG116" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG116" t="inlineStr">
+      <c r="IH116" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -54214,7 +54600,7 @@
         </is>
       </c>
       <c r="K117" s="2">
-        <v>46132.56875</v>
+        <v>46132.06875</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
@@ -54592,7 +54978,7 @@
         </is>
       </c>
       <c r="HS117">
-        <v>1776692340</v>
+        <v>1776649140</v>
       </c>
       <c r="HT117" t="inlineStr">
         <is>
@@ -54606,10 +54992,10 @@
         <v>565.618637286375</v>
       </c>
       <c r="HW117">
-        <v>5.517255633815</v>
+        <v>0.1812495317184593</v>
       </c>
       <c r="HX117">
-        <v>28.28093186431875</v>
+        <v>0.03535951378114494</v>
       </c>
       <c r="HY117" t="inlineStr">
         <is>
@@ -54617,7 +55003,7 @@
         </is>
       </c>
       <c r="HZ117">
-        <v>31.2</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="IA117">
         <v>5</v>
@@ -54631,17 +55017,20 @@
         <v>0</v>
       </c>
       <c r="ID117">
+        <v>5.199999999999999</v>
+      </c>
+      <c r="IE117">
         <v>0.7358867075269341</v>
       </c>
-      <c r="IE117">
+      <c r="IF117">
         <v>0.1293820764152031</v>
       </c>
-      <c r="IF117" t="inlineStr">
+      <c r="IG117" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG117" t="inlineStr">
+      <c r="IH117" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -54689,7 +55078,7 @@
         </is>
       </c>
       <c r="K118" s="2">
-        <v>46132.6</v>
+        <v>46132.1</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -55079,7 +55468,7 @@
         </is>
       </c>
       <c r="HS118">
-        <v>1776695040</v>
+        <v>1776651840</v>
       </c>
       <c r="HT118" t="inlineStr">
         <is>
@@ -55093,10 +55482,10 @@
         <v>411.557104130868</v>
       </c>
       <c r="HW118">
-        <v>2.78311960706048</v>
+        <v>0.3593090277051356</v>
       </c>
       <c r="HX118">
-        <v>20.5778552065434</v>
+        <v>0.04859592945731377</v>
       </c>
       <c r="HY118" t="inlineStr">
         <is>
@@ -55104,7 +55493,7 @@
         </is>
       </c>
       <c r="HZ118">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="IA118">
         <v>5</v>
@@ -55118,17 +55507,20 @@
         <v>1</v>
       </c>
       <c r="ID118">
+        <v>5</v>
+      </c>
+      <c r="IE118">
         <v>0.7358867075269341</v>
       </c>
-      <c r="IE118">
+      <c r="IF118">
         <v>0.1293820764152031</v>
       </c>
-      <c r="IF118" t="inlineStr">
+      <c r="IG118" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG118" t="inlineStr">
+      <c r="IH118" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -55176,7 +55568,7 @@
         </is>
       </c>
       <c r="K119" s="2">
-        <v>46132.6</v>
+        <v>46132.1</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -55545,7 +55937,7 @@
         </is>
       </c>
       <c r="HS119">
-        <v>1776695040</v>
+        <v>1776651840</v>
       </c>
       <c r="HT119" t="inlineStr">
         <is>
@@ -55559,10 +55951,10 @@
         <v>393.995431341253</v>
       </c>
       <c r="HW119">
-        <v>2.05165630733588</v>
+        <v>0.4874110719346174</v>
       </c>
       <c r="HX119">
-        <v>19.69977156706265</v>
+        <v>0.05076200993477336</v>
       </c>
       <c r="HY119" t="inlineStr">
         <is>
@@ -55570,7 +55962,7 @@
         </is>
       </c>
       <c r="HZ119">
-        <v>37.2</v>
+        <v>6.2</v>
       </c>
       <c r="IA119">
         <v>5</v>
@@ -55584,17 +55976,20 @@
         <v>1</v>
       </c>
       <c r="ID119">
+        <v>6.2</v>
+      </c>
+      <c r="IE119">
         <v>0.7358867075269341</v>
       </c>
-      <c r="IE119">
+      <c r="IF119">
         <v>0.1293820764152031</v>
       </c>
-      <c r="IF119" t="inlineStr">
+      <c r="IG119" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG119" t="inlineStr">
+      <c r="IH119" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -55642,7 +56037,7 @@
         </is>
       </c>
       <c r="K120" s="2">
-        <v>46132.6125</v>
+        <v>46132.1125</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -56004,7 +56399,7 @@
         </is>
       </c>
       <c r="HS120">
-        <v>1776696120</v>
+        <v>1776652920</v>
       </c>
       <c r="HT120" t="inlineStr">
         <is>
@@ -56018,10 +56413,10 @@
         <v>187.90193049333</v>
       </c>
       <c r="HW120">
-        <v>28.5391286313226</v>
+        <v>0.03503961220814809</v>
       </c>
       <c r="HX120">
-        <v>9.395096524666501</v>
+        <v>0.1064385019754225</v>
       </c>
       <c r="HY120" t="inlineStr">
         <is>
@@ -56029,7 +56424,7 @@
         </is>
       </c>
       <c r="HZ120">
-        <v>34.2</v>
+        <v>5.699999999999999</v>
       </c>
       <c r="IA120">
         <v>5</v>
@@ -56043,17 +56438,20 @@
         <v>1</v>
       </c>
       <c r="ID120">
+        <v>5.699999999999999</v>
+      </c>
+      <c r="IE120">
         <v>0.7358867075269341</v>
       </c>
-      <c r="IE120">
+      <c r="IF120">
         <v>0.1293820764152031</v>
       </c>
-      <c r="IF120" t="inlineStr">
+      <c r="IG120" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG120" t="inlineStr">
+      <c r="IH120" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
@@ -56101,7 +56499,7 @@
         </is>
       </c>
       <c r="K121" s="2">
-        <v>46132.6125</v>
+        <v>46132.1125</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -56454,7 +56852,7 @@
         </is>
       </c>
       <c r="HS121">
-        <v>1776696120</v>
+        <v>1776652920</v>
       </c>
       <c r="HT121" t="inlineStr">
         <is>
@@ -56468,10 +56866,10 @@
         <v>153.52894194799</v>
       </c>
       <c r="HW121">
-        <v>22.5304101069624</v>
+        <v>0.04438445617512207</v>
       </c>
       <c r="HX121">
-        <v>7.6764470973995</v>
+        <v>0.1302685978698093</v>
       </c>
       <c r="HY121" t="inlineStr">
         <is>
@@ -56479,7 +56877,7 @@
         </is>
       </c>
       <c r="HZ121">
-        <v>34.2</v>
+        <v>5.699999999999999</v>
       </c>
       <c r="IA121">
         <v>5</v>
@@ -56493,17 +56891,20 @@
         <v>1</v>
       </c>
       <c r="ID121">
+        <v>5.699999999999999</v>
+      </c>
+      <c r="IE121">
         <v>0.7358867075269341</v>
       </c>
-      <c r="IE121">
+      <c r="IF121">
         <v>0.1293820764152031</v>
       </c>
-      <c r="IF121" t="inlineStr">
+      <c r="IG121" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="IG121" t="inlineStr">
+      <c r="IH121" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
